--- a/बजेट माग estimate/वडा बजेट estimate/ukhu kheti/valuation ukhu kheti.xlsx
+++ b/बजेट माग estimate/वडा बजेट estimate/ukhu kheti/valuation ukhu kheti.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1920F364-AF7B-4996-8116-9CE5BE177768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B624F5A-D265-47C2-95AE-ABBF63B02D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$70</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">V!$A$1:$K$70</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">V!$A$1:$K$79</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">V!$1:$8</definedName>
   </definedNames>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="74">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -270,6 +270,33 @@
   </si>
   <si>
     <t>Total Valuated</t>
+  </si>
+  <si>
+    <t>-MS square pipe of 3" * 3" of 1.6mm thickness for vertical post</t>
+  </si>
+  <si>
+    <t>-MS square pipe of 66mm*33mm of 1.4mm thickness for vertical post</t>
+  </si>
+  <si>
+    <t>-MS square pipe of 2" * 2" of 1.4mm thickness for vertical post</t>
+  </si>
+  <si>
+    <t>-MS square pipe of 2" * 2" of 1.4mm thickness for purlins</t>
+  </si>
+  <si>
+    <t>-MS square pipe of 3" * 3" of 1.6mm thickness for vertical post for cooking area</t>
+  </si>
+  <si>
+    <t>-MS square pipe of 1.5" * 1.5" of 1.2mm thickness for purlins</t>
+  </si>
+  <si>
+    <t>-MS square pipe of 1.5" * 1.5" of 1.2mm thickness for horizontal support in mid-height section</t>
+  </si>
+  <si>
+    <t>-MS square pipe of 2" * 2" of 1.4mm thickness for horizontal support of roof</t>
+  </si>
+  <si>
+    <t>-cooking area</t>
   </si>
 </sst>
 </file>
@@ -362,7 +389,7 @@
       <name val="Preeti"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -372,6 +399,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -443,7 +476,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -556,24 +589,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -592,6 +607,45 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1138,113 +1192,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
     </row>
     <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
     </row>
     <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -2513,11 +2567,11 @@
       <c r="B65" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C65" s="50">
+      <c r="C65" s="44">
         <f>J63</f>
         <v>234835.07491669987</v>
       </c>
-      <c r="D65" s="51"/>
+      <c r="D65" s="45"/>
       <c r="E65" s="9">
         <v>100</v>
       </c>
@@ -2539,21 +2593,21 @@
       <c r="B66" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="54">
+      <c r="C66" s="48">
         <v>200000</v>
       </c>
-      <c r="D66" s="55"/>
+      <c r="D66" s="49"/>
       <c r="E66" s="9"/>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B67" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="54">
+      <c r="C67" s="48">
         <f>C66-C69-C70</f>
         <v>190000</v>
       </c>
-      <c r="D67" s="55"/>
+      <c r="D67" s="49"/>
       <c r="E67" s="9">
         <f>C67/C65*100</f>
         <v>80.907845673137345</v>
@@ -2563,11 +2617,11 @@
       <c r="B68" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C68" s="56">
+      <c r="C68" s="50">
         <f>C65-C67</f>
         <v>44835.074916699872</v>
       </c>
-      <c r="D68" s="56"/>
+      <c r="D68" s="50"/>
       <c r="E68" s="9">
         <f>100-E67</f>
         <v>19.092154326862655</v>
@@ -2577,11 +2631,11 @@
       <c r="B69" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="50">
+      <c r="C69" s="44">
         <f>C66*0.03</f>
         <v>6000</v>
       </c>
-      <c r="D69" s="51"/>
+      <c r="D69" s="45"/>
       <c r="E69" s="9">
         <v>3</v>
       </c>
@@ -2590,17 +2644,24 @@
       <c r="B70" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C70" s="50">
+      <c r="C70" s="44">
         <f>C66*0.02</f>
         <v>4000</v>
       </c>
-      <c r="D70" s="51"/>
+      <c r="D70" s="45"/>
       <c r="E70" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C69:D69"/>
     <mergeCell ref="C70:D70"/>
     <mergeCell ref="A7:F7"/>
@@ -2609,13 +2670,6 @@
     <mergeCell ref="C66:D66"/>
     <mergeCell ref="C67:D67"/>
     <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -2630,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD9D6B52-0BCE-4A59-BC99-2ABBFC24DADE}">
-  <dimension ref="A1:S70"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
@@ -2648,116 +2702,116 @@
     <col min="17" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-    </row>
-    <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-    </row>
-    <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="49" t="s">
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-    </row>
-    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-    </row>
-    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
@@ -2792,7 +2846,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -2817,433 +2871,457 @@
       <c r="J9" s="39"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:18" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="41">
-        <f>2*3</f>
-        <v>6</v>
-      </c>
-      <c r="D10" s="9">
-        <f>(11+1+2)/3.281</f>
-        <v>4.2669917708015843</v>
-      </c>
-      <c r="E10" s="9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F10" s="9">
-        <f t="shared" ref="F10:F16" si="0">PRODUCT(C10:E10)</f>
-        <v>112.64858274916183</v>
-      </c>
-      <c r="G10" s="9">
-        <f t="shared" ref="G10:G16" si="1">F10</f>
-        <v>112.64858274916183</v>
+        <v>65</v>
+      </c>
+      <c r="C10" s="63">
+        <v>2</v>
+      </c>
+      <c r="D10" s="64">
+        <f>(15.5+1)/3.281</f>
+        <v>5.0289545870161536</v>
+      </c>
+      <c r="E10" s="64">
+        <v>3.54</v>
+      </c>
+      <c r="F10" s="64">
+        <f t="shared" ref="F10" si="0">PRODUCT(C10:E10)</f>
+        <v>35.604998476074371</v>
+      </c>
+      <c r="G10" s="64">
+        <f t="shared" ref="G10" si="1">F10</f>
+        <v>35.604998476074371</v>
       </c>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
       <c r="J10" s="39"/>
       <c r="K10" s="27"/>
     </row>
-    <row r="11" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="40"/>
-      <c r="C11" s="41">
-        <f>2*3</f>
-        <v>6</v>
-      </c>
-      <c r="D11" s="9">
-        <f>(11+1+1+2)/3.281</f>
-        <v>4.5717768972874122</v>
-      </c>
-      <c r="E11" s="9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F11" s="9">
-        <f t="shared" si="0"/>
-        <v>120.69491008838769</v>
-      </c>
-      <c r="G11" s="9">
-        <f t="shared" si="1"/>
-        <v>120.69491008838769</v>
+      <c r="C11" s="63">
+        <v>2</v>
+      </c>
+      <c r="D11" s="64">
+        <f>(15.5-1.5+2)/3.281</f>
+        <v>4.8765620237732392</v>
+      </c>
+      <c r="E11" s="64">
+        <v>3.54</v>
+      </c>
+      <c r="F11" s="64">
+        <f t="shared" ref="F11" si="2">PRODUCT(C11:E11)</f>
+        <v>34.526059128314536</v>
+      </c>
+      <c r="G11" s="64">
+        <f t="shared" ref="G11" si="3">F11</f>
+        <v>34.526059128314536</v>
       </c>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
       <c r="J11" s="39"/>
       <c r="K11" s="27"/>
     </row>
-    <row r="12" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41">
-        <f>2</f>
+      <c r="B12" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="63">
         <v>2</v>
       </c>
-      <c r="D12" s="9">
-        <f>(11+1+2)/3.281</f>
-        <v>4.2669917708015843</v>
-      </c>
-      <c r="E12" s="9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F12" s="9">
-        <f t="shared" si="0"/>
-        <v>37.549527583053944</v>
-      </c>
-      <c r="G12" s="9">
-        <f t="shared" si="1"/>
-        <v>37.549527583053944</v>
+      <c r="D12" s="64">
+        <v>3.9</v>
+      </c>
+      <c r="E12" s="64">
+        <v>2.14</v>
+      </c>
+      <c r="F12" s="64">
+        <f>PRODUCT(C12:E12)</f>
+        <v>16.692</v>
+      </c>
+      <c r="G12" s="64">
+        <f>F12</f>
+        <v>16.692</v>
       </c>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
       <c r="J12" s="39"/>
       <c r="K12" s="27"/>
     </row>
-    <row r="13" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="41">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="D13" s="9">
-        <f>(11+1+1+2)/3.281</f>
-        <v>4.5717768972874122</v>
-      </c>
-      <c r="E13" s="9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F13" s="9">
-        <f t="shared" si="0"/>
-        <v>40.231636696129229</v>
-      </c>
-      <c r="G13" s="9">
-        <f t="shared" si="1"/>
-        <v>40.231636696129229</v>
+      <c r="B13" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="63">
+        <v>9</v>
+      </c>
+      <c r="D13" s="64">
+        <v>3.09</v>
+      </c>
+      <c r="E13" s="64">
+        <v>2.14</v>
+      </c>
+      <c r="F13" s="64">
+        <f t="shared" ref="F13" si="4">PRODUCT(C13:E13)</f>
+        <v>59.513399999999997</v>
+      </c>
+      <c r="G13" s="64">
+        <f t="shared" ref="G13" si="5">F13</f>
+        <v>59.513399999999997</v>
       </c>
       <c r="H13" s="39"/>
       <c r="I13" s="39"/>
       <c r="J13" s="39"/>
       <c r="K13" s="27"/>
     </row>
-    <row r="14" spans="1:18" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="41">
-        <f>2*(2+1)</f>
-        <v>6</v>
-      </c>
-      <c r="D14" s="9">
-        <f>(12+3)/3.281</f>
-        <v>4.5717768972874122</v>
-      </c>
-      <c r="E14" s="9">
-        <v>3.01</v>
-      </c>
-      <c r="F14" s="9">
-        <f t="shared" si="0"/>
-        <v>82.566290765010663</v>
-      </c>
-      <c r="G14" s="9">
-        <f t="shared" si="1"/>
-        <v>82.566290765010663</v>
+        <v>66</v>
+      </c>
+      <c r="C14" s="63">
+        <v>1</v>
+      </c>
+      <c r="D14" s="64">
+        <v>3.9</v>
+      </c>
+      <c r="E14" s="64">
+        <v>2.35</v>
+      </c>
+      <c r="F14" s="64">
+        <f t="shared" ref="F14" si="6">PRODUCT(C14:E14)</f>
+        <v>9.1650000000000009</v>
+      </c>
+      <c r="G14" s="64">
+        <f t="shared" ref="G14" si="7">F14</f>
+        <v>9.1650000000000009</v>
       </c>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
       <c r="J14" s="39"/>
       <c r="K14" s="27"/>
-      <c r="Q14" s="35">
-        <f>PRODUCT(C14:D14)</f>
-        <v>27.430661383724473</v>
-      </c>
-      <c r="R14" s="35">
-        <f>CONVERT(Q14,"m","ft")</f>
-        <v>89.995608214319134</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="41">
-        <f>2*(2+1)</f>
-        <v>6</v>
-      </c>
-      <c r="D15" s="9">
-        <f>(10+3)/3.281</f>
-        <v>3.9622066443157573</v>
-      </c>
-      <c r="E15" s="9">
-        <v>3.01</v>
-      </c>
-      <c r="F15" s="9">
-        <f t="shared" si="0"/>
-        <v>71.557451996342579</v>
-      </c>
-      <c r="G15" s="9">
-        <f t="shared" si="1"/>
-        <v>71.557451996342579</v>
+      <c r="B15" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="63">
+        <v>3</v>
+      </c>
+      <c r="D15" s="64">
+        <f>(7+1)/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E15" s="64">
+        <v>3.54</v>
+      </c>
+      <c r="F15" s="64">
+        <f t="shared" ref="F15" si="8">PRODUCT(C15:E15)</f>
+        <v>25.8945443462359</v>
+      </c>
+      <c r="G15" s="64">
+        <f t="shared" ref="G15" si="9">F15</f>
+        <v>25.8945443462359</v>
       </c>
       <c r="H15" s="39"/>
       <c r="I15" s="39"/>
       <c r="J15" s="39"/>
       <c r="K15" s="27"/>
     </row>
-    <row r="16" spans="1:18" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
-      <c r="B16" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="41">
-        <f>2*2</f>
-        <v>4</v>
-      </c>
-      <c r="D16" s="9">
-        <f>(12+3)/3.281</f>
-        <v>4.5717768972874122</v>
-      </c>
-      <c r="E16" s="9">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" si="0"/>
-        <v>41.328863151478203</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="1"/>
-        <v>41.328863151478203</v>
+      <c r="B16" s="40"/>
+      <c r="C16" s="63">
+        <v>3</v>
+      </c>
+      <c r="D16" s="64">
+        <v>2.6</v>
+      </c>
+      <c r="E16" s="64">
+        <v>3.54</v>
+      </c>
+      <c r="F16" s="64">
+        <f t="shared" ref="F16:F17" si="10">PRODUCT(C16:E16)</f>
+        <v>27.612000000000002</v>
+      </c>
+      <c r="G16" s="64">
+        <f t="shared" ref="G16:G17" si="11">F16</f>
+        <v>27.612000000000002</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="39"/>
       <c r="J16" s="39"/>
       <c r="K16" s="27"/>
     </row>
-    <row r="17" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
+    <row r="17" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
       <c r="B17" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="63">
+        <v>5</v>
+      </c>
+      <c r="D17" s="64">
+        <v>3.09</v>
+      </c>
+      <c r="E17" s="64">
+        <v>1.39</v>
+      </c>
+      <c r="F17" s="64">
+        <f t="shared" si="10"/>
+        <v>21.475499999999997</v>
+      </c>
+      <c r="G17" s="64">
+        <f t="shared" si="11"/>
+        <v>21.475499999999997</v>
+      </c>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="27"/>
+    </row>
+    <row r="18" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="63">
+        <v>5</v>
+      </c>
+      <c r="D18" s="64">
+        <f>1.8+1.9</f>
+        <v>3.7</v>
+      </c>
+      <c r="E18" s="64">
+        <v>1.39</v>
+      </c>
+      <c r="F18" s="64">
+        <f t="shared" ref="F18" si="12">PRODUCT(C18:E18)</f>
+        <v>25.715</v>
+      </c>
+      <c r="G18" s="64">
+        <f t="shared" ref="G18" si="13">F18</f>
+        <v>25.715</v>
+      </c>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="27"/>
+    </row>
+    <row r="19" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="63">
+        <v>3</v>
+      </c>
+      <c r="D19" s="64">
+        <f>13/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E19" s="64">
+        <v>1.39</v>
+      </c>
+      <c r="F19" s="64">
+        <f t="shared" ref="F19" si="14">PRODUCT(C19:E19)</f>
+        <v>16.522401706796707</v>
+      </c>
+      <c r="G19" s="64">
+        <f t="shared" ref="G19" si="15">F19</f>
+        <v>16.522401706796707</v>
+      </c>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="27"/>
+    </row>
+    <row r="20" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="40" t="s">
         <v>36</v>
-      </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="39">
-        <f>SUM(G10:G16)</f>
-        <v>506.57726302956416</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="6">
-        <v>182.51</v>
-      </c>
-      <c r="J17" s="39">
-        <f>G17*I17</f>
-        <v>92455.416275525757</v>
-      </c>
-      <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="39">
-        <f>0.13*G17*(1871.42/18.94)</f>
-        <v>6506.9929675418325</v>
-      </c>
-      <c r="K18" s="5"/>
-    </row>
-    <row r="19" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>2</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>62</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="4"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="39"/>
+      <c r="G20" s="39">
+        <f>SUM(G10:G19)</f>
+        <v>272.72090365742145</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="6">
+        <v>182.51</v>
+      </c>
+      <c r="J20" s="39">
+        <f>G20*I20</f>
+        <v>49774.292126515982</v>
+      </c>
       <c r="K20" s="5"/>
     </row>
     <row r="21" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="3">
-        <f>2*1</f>
-        <v>2</v>
-      </c>
-      <c r="D21" s="4">
-        <f>(10+3)/3.281</f>
-        <v>3.9622066443157573</v>
-      </c>
-      <c r="E21" s="5">
-        <f>(12+3)/3.281</f>
-        <v>4.5717768972874122</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="33">
-        <f t="shared" ref="G21:G22" si="2">PRODUCT(C21:F21)</f>
-        <v>36.228649597522924</v>
-      </c>
+      <c r="G21" s="39"/>
       <c r="H21" s="7"/>
       <c r="I21" s="6"/>
-      <c r="J21" s="39"/>
+      <c r="J21" s="39">
+        <f>0.13*G20*(1871.42/18.94)</f>
+        <v>3503.1043272404604</v>
+      </c>
       <c r="K21" s="5"/>
     </row>
     <row r="22" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="40"/>
-      <c r="C22" s="3">
-        <v>1</v>
-      </c>
-      <c r="D22" s="4">
-        <f>(10+3)/3.281</f>
-        <v>3.9622066443157573</v>
-      </c>
-      <c r="E22" s="5">
-        <f>(10+3)/3.281</f>
-        <v>3.9622066443157573</v>
-      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-      <c r="G22" s="33">
-        <f t="shared" si="2"/>
-        <v>15.699081492259934</v>
-      </c>
+      <c r="G22" s="39"/>
       <c r="H22" s="7"/>
       <c r="I22" s="6"/>
       <c r="J22" s="39"/>
       <c r="K22" s="5"/>
     </row>
-    <row r="23" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="40" t="s">
-        <v>36</v>
+    <row r="23" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>2</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>62</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="4"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="39">
-        <f>SUM(G21:G22)</f>
-        <v>51.92773108978286</v>
-      </c>
-      <c r="H23" s="7" t="s">
+      <c r="G23" s="39"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="60">
+        <f>2*1</f>
+        <v>2</v>
+      </c>
+      <c r="D24" s="61">
+        <f>(10+4)/3.281</f>
+        <v>4.2669917708015843</v>
+      </c>
+      <c r="E24" s="62">
+        <f>(7)/3.281</f>
+        <v>2.1334958854007922</v>
+      </c>
+      <c r="F24" s="62"/>
+      <c r="G24" s="58">
+        <f t="shared" ref="G24:G25" si="16">PRODUCT(C24:F24)</f>
+        <v>18.207218772088439</v>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="5"/>
+    </row>
+    <row r="25" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="60">
+        <v>1</v>
+      </c>
+      <c r="D25" s="61">
+        <f>(13.5)/3.281</f>
+        <v>4.1145992075586708</v>
+      </c>
+      <c r="E25" s="62">
+        <f>1.8+1.9</f>
+        <v>3.7</v>
+      </c>
+      <c r="F25" s="62"/>
+      <c r="G25" s="58">
+        <f t="shared" si="16"/>
+        <v>15.224017067967083</v>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="5"/>
+    </row>
+    <row r="26" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="60">
+        <v>1</v>
+      </c>
+      <c r="D26" s="61">
+        <f>(7)/3.281</f>
+        <v>2.1334958854007922</v>
+      </c>
+      <c r="E26" s="62">
+        <f>1.8+1.9</f>
+        <v>3.7</v>
+      </c>
+      <c r="F26" s="62"/>
+      <c r="G26" s="58">
+        <f t="shared" ref="G26" si="17">PRODUCT(C26:F26)</f>
+        <v>7.893934775982931</v>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="5"/>
+    </row>
+    <row r="27" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="39">
+        <f>SUM(G24:G26)</f>
+        <v>41.325170616038449</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I27" s="6">
         <v>1074.98</v>
       </c>
-      <c r="J23" s="39">
-        <f>G23*I23</f>
-        <v>55821.27236689478</v>
-      </c>
-      <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
-      <c r="B24" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="18">
-        <f>0.13*G23*6674.66/10</f>
-        <v>4505.7993447444915</v>
-      </c>
-      <c r="K24" s="17"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="16"/>
-      <c r="B25" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="18">
-        <f>0.13*G23*1023.75/10</f>
-        <v>691.09319114114771</v>
-      </c>
-      <c r="K25" s="17"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
-      <c r="B26" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="18">
-        <f>0.13*G23*348.21/10</f>
-        <v>235.06281815605274</v>
-      </c>
-      <c r="K26" s="17"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
-      <c r="B27" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="18">
-        <f>0.13*G23*165/10</f>
-        <v>111.38498318758425</v>
-      </c>
-      <c r="K27" s="17"/>
+      <c r="J27" s="39">
+        <f>G27*I27</f>
+        <v>44423.73190882901</v>
+      </c>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
-      <c r="B28" s="32"/>
+      <c r="B28" s="32" t="s">
+        <v>41</v>
+      </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
@@ -3251,15 +3329,16 @@
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
-      <c r="J28" s="18"/>
+      <c r="J28" s="18">
+        <f>0.13*G27*6674.66/10</f>
+        <v>3585.8090229526133</v>
+      </c>
       <c r="K28" s="17"/>
     </row>
-    <row r="29" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="16">
-        <v>3</v>
-      </c>
-      <c r="B29" s="43" t="s">
-        <v>49</v>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="16"/>
+      <c r="B29" s="32" t="s">
+        <v>42</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -3268,92 +3347,68 @@
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
-      <c r="J29" s="18"/>
+      <c r="J29" s="18">
+        <f>0.13*G27*1023.75/10</f>
+        <v>549.98636443620171</v>
+      </c>
       <c r="K29" s="17"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="17">
-        <f>2*2</f>
-        <v>4</v>
-      </c>
-      <c r="D30" s="33">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E30" s="17">
-        <v>0.45</v>
-      </c>
-      <c r="F30" s="17">
-        <v>0.9</v>
-      </c>
-      <c r="G30" s="33">
-        <f t="shared" ref="G30:G31" si="3">PRODUCT(C30:F30)</f>
-        <v>3.9500152392563237</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
       <c r="H30" s="17"/>
       <c r="I30" s="17"/>
-      <c r="J30" s="18"/>
+      <c r="J30" s="18">
+        <f>0.13*G27*348.21/10</f>
+        <v>187.06788958273972</v>
+      </c>
       <c r="K30" s="17"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="17">
-        <f>2*4</f>
-        <v>8</v>
-      </c>
-      <c r="D31" s="33">
-        <v>0.6</v>
-      </c>
-      <c r="E31" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="F31" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="G31" s="33">
-        <f t="shared" si="3"/>
-        <v>1.728</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
       <c r="H31" s="17"/>
       <c r="I31" s="17"/>
-      <c r="J31" s="18"/>
+      <c r="J31" s="18">
+        <f>0.13*G27*165/10</f>
+        <v>88.642490971402466</v>
+      </c>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="39">
-        <f>SUM(G30:G31)</f>
-        <v>5.6780152392563235</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I32" s="6">
-        <v>674.12</v>
-      </c>
-      <c r="J32" s="39">
-        <f>G32*I32</f>
-        <v>3827.6636330874726</v>
-      </c>
-      <c r="K32" s="5"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
-      <c r="B33" s="32"/>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="16"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="16">
+        <v>3</v>
+      </c>
+      <c r="B33" s="43" t="s">
+        <v>49</v>
+      </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
@@ -3364,18 +3419,28 @@
       <c r="J33" s="18"/>
       <c r="K33" s="17"/>
     </row>
-    <row r="34" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="16">
-        <v>4</v>
-      </c>
-      <c r="B34" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="16"/>
+      <c r="B34" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="57">
+        <v>2</v>
+      </c>
+      <c r="D34" s="58">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E34" s="57">
+        <v>0.45</v>
+      </c>
+      <c r="F34" s="57">
+        <v>0.9</v>
+      </c>
+      <c r="G34" s="58">
+        <f t="shared" ref="G34:G37" si="18">PRODUCT(C34:F34)</f>
+        <v>1.9750076196281618</v>
+      </c>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
       <c r="J34" s="18"/>
@@ -3383,28 +3448,23 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
-      <c r="B35" s="32" t="str">
-        <f>B31</f>
-        <v>-for footing of vertical post</v>
-      </c>
+      <c r="B35" s="32"/>
       <c r="C35" s="17">
-        <f>C31</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D35" s="33">
-        <f>D31</f>
-        <v>0.6</v>
-      </c>
-      <c r="E35" s="33">
-        <f>E31</f>
-        <v>0.6</v>
-      </c>
-      <c r="F35" s="33">
-        <v>0.15</v>
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E35" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F35" s="17">
+        <v>0.9</v>
       </c>
       <c r="G35" s="33">
-        <f t="shared" ref="G35:G37" si="4">PRODUCT(C35:F35)</f>
-        <v>0.432</v>
+        <f t="shared" ref="G35" si="19">PRODUCT(C35:F35)</f>
+        <v>0</v>
       </c>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
@@ -3414,26 +3474,24 @@
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="16"/>
       <c r="B36" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="17">
-        <f>2*1</f>
-        <v>2</v>
-      </c>
-      <c r="D36" s="33">
-        <f>10/3.281</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="E36" s="33">
-        <f>12/3.281</f>
-        <v>3.6574215178299299</v>
-      </c>
-      <c r="F36" s="33">
-        <v>0.15</v>
-      </c>
-      <c r="G36" s="33">
-        <f t="shared" si="4"/>
-        <v>3.3441830397713472</v>
+        <v>47</v>
+      </c>
+      <c r="C36" s="57">
+        <f>2*6</f>
+        <v>12</v>
+      </c>
+      <c r="D36" s="58">
+        <v>0.45</v>
+      </c>
+      <c r="E36" s="57">
+        <v>0.45</v>
+      </c>
+      <c r="F36" s="57">
+        <v>0.45</v>
+      </c>
+      <c r="G36" s="58">
+        <f t="shared" si="18"/>
+        <v>1.0935000000000001</v>
       </c>
       <c r="H36" s="17"/>
       <c r="I36" s="17"/>
@@ -3443,26 +3501,25 @@
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="17">
-        <f>2*-1</f>
-        <v>-2</v>
-      </c>
-      <c r="D37" s="33">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E37" s="33">
-        <f>0.6+0.45+0.45</f>
-        <v>1.5</v>
-      </c>
-      <c r="F37" s="33">
-        <v>0.15</v>
-      </c>
-      <c r="G37" s="33">
-        <f t="shared" si="4"/>
-        <v>-1.0972264553489788</v>
+        <v>55</v>
+      </c>
+      <c r="C37" s="57">
+        <v>1</v>
+      </c>
+      <c r="D37" s="58">
+        <f>13/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E37" s="58">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="F37" s="57">
+        <v>0.1</v>
+      </c>
+      <c r="G37" s="58">
+        <f t="shared" si="18"/>
+        <v>1.2076216532507642</v>
       </c>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
@@ -3479,26 +3536,24 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="39">
-        <f>SUM(G35:G37)</f>
-        <v>2.6789565844223686</v>
+        <f>SUM(G34:G37)</f>
+        <v>4.2761292728789257</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I38" s="6">
-        <v>4495.6400000000003</v>
+        <v>674.12</v>
       </c>
       <c r="J38" s="39">
         <f>G38*I38</f>
-        <v>12043.624379192579</v>
+        <v>2882.6242654331413</v>
       </c>
       <c r="K38" s="5"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
-      <c r="B39" s="32" t="s">
-        <v>51</v>
-      </c>
+      <c r="B39" s="32"/>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
@@ -3506,16 +3561,15 @@
       <c r="G39" s="17"/>
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
-      <c r="J39" s="18">
-        <f>0.13*G38*2577.63</f>
-        <v>897.69665189160207</v>
-      </c>
+      <c r="J39" s="18"/>
       <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="16"/>
-      <c r="B40" s="32" t="s">
-        <v>52</v>
+    <row r="40" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>4</v>
+      </c>
+      <c r="B40" s="43" t="s">
+        <v>50</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -3524,64 +3578,89 @@
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
-      <c r="J40" s="18">
-        <f>0.13*G38*515.52</f>
-        <v>179.53724079218455</v>
-      </c>
+      <c r="J40" s="18"/>
       <c r="K40" s="17"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
+      <c r="B41" s="32" t="str">
+        <f>B36</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C41" s="57">
+        <f>C36</f>
+        <v>12</v>
+      </c>
+      <c r="D41" s="58">
+        <f>D36</f>
+        <v>0.45</v>
+      </c>
+      <c r="E41" s="58">
+        <f>E36</f>
+        <v>0.45</v>
+      </c>
+      <c r="F41" s="58">
+        <v>0.15</v>
+      </c>
+      <c r="G41" s="58">
+        <f t="shared" ref="G41:G44" si="20">PRODUCT(C41:F41)</f>
+        <v>0.36449999999999999</v>
+      </c>
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
       <c r="J41" s="18"/>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="16">
-        <v>5</v>
-      </c>
-      <c r="B42" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="16"/>
+      <c r="B42" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="57">
+        <f>C52</f>
+        <v>1</v>
+      </c>
+      <c r="D42" s="58">
+        <f>D52</f>
+        <v>3.5</v>
+      </c>
+      <c r="E42" s="58">
+        <f>E52</f>
+        <v>3.9</v>
+      </c>
+      <c r="F42" s="58">
+        <v>0.15</v>
+      </c>
+      <c r="G42" s="58">
+        <f t="shared" si="20"/>
+        <v>2.0474999999999999</v>
+      </c>
       <c r="H42" s="17"/>
       <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
+      <c r="J42" s="18"/>
       <c r="K42" s="17"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
-      <c r="B43" s="32" t="str">
-        <f>B35</f>
-        <v>-for footing of vertical post</v>
-      </c>
-      <c r="C43" s="17">
-        <f>2*4</f>
-        <v>8</v>
-      </c>
-      <c r="D43" s="33">
-        <v>0.6</v>
-      </c>
-      <c r="E43" s="17">
-        <v>0.6</v>
-      </c>
-      <c r="F43" s="33">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G43" s="33">
-        <f t="shared" ref="G43:G46" si="5">PRODUCT(C43:F43)</f>
-        <v>0.216</v>
+      <c r="B43" s="65"/>
+      <c r="C43" s="57">
+        <f>C53</f>
+        <v>1</v>
+      </c>
+      <c r="D43" s="58">
+        <f>D53</f>
+        <v>4.2</v>
+      </c>
+      <c r="E43" s="58">
+        <f>E53</f>
+        <v>3.2</v>
+      </c>
+      <c r="F43" s="58">
+        <v>0.15</v>
+      </c>
+      <c r="G43" s="58">
+        <f t="shared" ref="G43" si="21">PRODUCT(C43:F43)</f>
+        <v>2.016</v>
       </c>
       <c r="H43" s="17"/>
       <c r="I43" s="17"/>
@@ -3590,118 +3669,97 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="17">
-        <f>2*4</f>
-        <v>8</v>
-      </c>
-      <c r="D44" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="E44" s="17">
-        <v>0.45</v>
-      </c>
-      <c r="F44" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="G44" s="33">
-        <f t="shared" si="5"/>
-        <v>0.72900000000000009</v>
+      <c r="B44" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="57">
+        <f>C54</f>
+        <v>-1</v>
+      </c>
+      <c r="D44" s="58">
+        <f>D54</f>
+        <v>3</v>
+      </c>
+      <c r="E44" s="58">
+        <f>E54</f>
+        <v>1.5</v>
+      </c>
+      <c r="F44" s="58">
+        <v>0.15</v>
+      </c>
+      <c r="G44" s="58">
+        <f t="shared" si="20"/>
+        <v>-0.67499999999999993</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="17"/>
       <c r="J44" s="18"/>
       <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="16"/>
-      <c r="B45" s="32" t="str">
-        <f>B36</f>
-        <v>-for flooring</v>
-      </c>
-      <c r="C45" s="17">
-        <f>C36</f>
-        <v>2</v>
-      </c>
-      <c r="D45" s="33">
-        <f>D36</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="E45" s="33">
-        <f>E36</f>
-        <v>3.6574215178299299</v>
-      </c>
-      <c r="F45" s="33">
-        <v>0.1</v>
-      </c>
-      <c r="G45" s="33">
-        <f t="shared" si="5"/>
-        <v>2.2294553598475648</v>
-      </c>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="17"/>
+    <row r="45" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="39">
+        <f>SUM(G41:G44)</f>
+        <v>3.7530000000000001</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I45" s="6">
+        <v>4495.6400000000003</v>
+      </c>
+      <c r="J45" s="39">
+        <f>G45*I45</f>
+        <v>16872.136920000001</v>
+      </c>
+      <c r="K45" s="5"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="17">
-        <f>C37</f>
-        <v>-2</v>
-      </c>
-      <c r="D46" s="33">
-        <f>12/3.281</f>
-        <v>3.6574215178299299</v>
-      </c>
-      <c r="E46" s="33">
-        <f>0.6+0.45+0.45</f>
-        <v>1.5</v>
-      </c>
-      <c r="F46" s="33">
-        <v>0.1</v>
-      </c>
-      <c r="G46" s="33">
-        <f t="shared" si="5"/>
-        <v>-1.097226455348979</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
       <c r="H46" s="17"/>
       <c r="I46" s="17"/>
-      <c r="J46" s="18"/>
+      <c r="J46" s="18">
+        <f>0.13*G45*2577.63</f>
+        <v>1257.5999007000003</v>
+      </c>
       <c r="K46" s="17"/>
     </row>
-    <row r="47" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="39">
-        <f>SUM(G43:G46)</f>
-        <v>2.0772289044985861</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I47" s="6">
-        <v>13351.1</v>
-      </c>
-      <c r="J47" s="39">
-        <f>G47*I47</f>
-        <v>27733.290826851073</v>
-      </c>
-      <c r="K47" s="5"/>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="18">
+        <f>0.13*G45*515.52</f>
+        <v>251.51705280000002</v>
+      </c>
+      <c r="K47" s="17"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
-      <c r="B48" s="32" t="s">
-        <v>26</v>
-      </c>
+      <c r="B48" s="42"/>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
@@ -3709,16 +3767,15 @@
       <c r="G48" s="17"/>
       <c r="H48" s="17"/>
       <c r="I48" s="17"/>
-      <c r="J48" s="18">
-        <f>0.13*G47*4169.92</f>
-        <v>1126.0441859480768</v>
-      </c>
+      <c r="J48" s="18"/>
       <c r="K48" s="17"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="16"/>
-      <c r="B49" s="32" t="s">
-        <v>27</v>
+    <row r="49" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="16">
+        <v>5</v>
+      </c>
+      <c r="B49" s="43" t="s">
+        <v>53</v>
       </c>
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
@@ -3727,148 +3784,168 @@
       <c r="G49" s="17"/>
       <c r="H49" s="17"/>
       <c r="I49" s="17"/>
-      <c r="J49" s="18">
-        <f>0.13*G47*1414.16</f>
-        <v>381.87942358614367</v>
-      </c>
+      <c r="J49" s="17"/>
       <c r="K49" s="17"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
-      <c r="B50" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
+      <c r="B50" s="32" t="str">
+        <f>B41</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C50" s="57">
+        <f>C36</f>
+        <v>12</v>
+      </c>
+      <c r="D50" s="58">
+        <v>0.45</v>
+      </c>
+      <c r="E50" s="57">
+        <v>0.45</v>
+      </c>
+      <c r="F50" s="58">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G50" s="58">
+        <f t="shared" ref="G50:G54" si="22">PRODUCT(C50:F50)</f>
+        <v>0.18225</v>
+      </c>
       <c r="H50" s="17"/>
       <c r="I50" s="17"/>
-      <c r="J50" s="18">
-        <f>0.13*G47*(1652.5+737.97+349.56)</f>
-        <v>739.91703697512401</v>
-      </c>
+      <c r="J50" s="18"/>
       <c r="K50" s="17"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="16"/>
-      <c r="B51" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="17">
+        <v>0</v>
+      </c>
+      <c r="D51" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E51" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F51" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="G51" s="33">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="H51" s="17"/>
       <c r="I51" s="17"/>
-      <c r="J51" s="18">
-        <f>0.13*G47*42</f>
-        <v>11.341669818562281</v>
-      </c>
+      <c r="J51" s="18"/>
       <c r="K51" s="17"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
-      <c r="B52" s="32"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
+      <c r="B52" s="32" t="str">
+        <f>B42</f>
+        <v>-for flooring</v>
+      </c>
+      <c r="C52" s="57">
+        <v>1</v>
+      </c>
+      <c r="D52" s="58">
+        <v>3.5</v>
+      </c>
+      <c r="E52" s="58">
+        <v>3.9</v>
+      </c>
+      <c r="F52" s="58">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G52" s="58">
+        <f t="shared" si="22"/>
+        <v>1.0237499999999999</v>
+      </c>
       <c r="H52" s="17"/>
       <c r="I52" s="17"/>
       <c r="J52" s="18"/>
       <c r="K52" s="17"/>
     </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="16">
-        <v>6</v>
-      </c>
-      <c r="B53" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="16"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="57">
+        <v>1</v>
+      </c>
+      <c r="D53" s="58">
+        <v>4.2</v>
+      </c>
+      <c r="E53" s="58">
+        <v>3.2</v>
+      </c>
+      <c r="F53" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G53" s="58">
+        <f t="shared" si="22"/>
+        <v>1.3440000000000003</v>
+      </c>
       <c r="H53" s="17"/>
       <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
+      <c r="J53" s="18"/>
       <c r="K53" s="17"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C54" s="17">
-        <f>2*2</f>
-        <v>4</v>
-      </c>
-      <c r="D54" s="33">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E54" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="F54" s="33">
-        <v>0.9</v>
-      </c>
-      <c r="G54" s="33">
-        <f>PRODUCT(C54:F54)</f>
-        <v>3.9500152392563237</v>
+        <v>56</v>
+      </c>
+      <c r="C54" s="57">
+        <v>-1</v>
+      </c>
+      <c r="D54" s="58">
+        <v>3</v>
+      </c>
+      <c r="E54" s="58">
+        <f>0.6+0.45+0.45</f>
+        <v>1.5</v>
+      </c>
+      <c r="F54" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G54" s="58">
+        <f t="shared" si="22"/>
+        <v>-0.45</v>
       </c>
       <c r="H54" s="17"/>
       <c r="I54" s="17"/>
-      <c r="J54" s="17"/>
+      <c r="J54" s="18"/>
       <c r="K54" s="17"/>
-      <c r="M54" s="33">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N54" s="33">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="O54" s="33"/>
-      <c r="P54" s="33">
-        <f>PI()*M54*SQRT(M54^2+N54^2)</f>
-        <v>160.09797821843054</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:16" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
-      <c r="B55" s="34" t="s">
-        <v>16</v>
+      <c r="B55" s="40" t="s">
+        <v>36</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="4"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
-      <c r="G55" s="6">
-        <f>SUM(G54:G54)</f>
-        <v>3.9500152392563237</v>
+      <c r="G55" s="39">
+        <f>SUM(G50:G54)</f>
+        <v>2.1</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>46</v>
       </c>
       <c r="I55" s="6">
-        <v>6337.3</v>
-      </c>
-      <c r="J55" s="18">
+        <v>13351.1</v>
+      </c>
+      <c r="J55" s="39">
         <f>G55*I55</f>
-        <v>25032.431575739101</v>
+        <v>28037.31</v>
       </c>
       <c r="K55" s="5"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
       <c r="B56" s="32" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
@@ -3878,15 +3955,15 @@
       <c r="H56" s="17"/>
       <c r="I56" s="17"/>
       <c r="J56" s="18">
-        <f>0.13*G55*2577.63</f>
-        <v>1323.6181115513564</v>
+        <f>0.13*G55*4169.92</f>
+        <v>1138.3881600000002</v>
       </c>
       <c r="K56" s="17"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="16"/>
       <c r="B57" s="32" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
@@ -3896,15 +3973,15 @@
       <c r="H57" s="17"/>
       <c r="I57" s="17"/>
       <c r="J57" s="18">
-        <f>0.13*G55*257.76</f>
-        <v>132.3602706491923</v>
+        <f>0.13*G55*1414.16</f>
+        <v>386.06568000000004</v>
       </c>
       <c r="K57" s="17"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="16"/>
       <c r="B58" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
@@ -3914,12 +3991,12 @@
       <c r="H58" s="17"/>
       <c r="I58" s="17"/>
       <c r="J58" s="18">
-        <f>0.13*G55*133.56</f>
-        <v>68.583324596159699</v>
+        <f>0.13*G55*(1652.5+737.97+349.56)</f>
+        <v>748.02819000000011</v>
       </c>
       <c r="K58" s="17"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="16"/>
       <c r="B59" s="32" t="s">
         <v>30</v>
@@ -3932,12 +4009,12 @@
       <c r="H59" s="17"/>
       <c r="I59" s="17"/>
       <c r="J59" s="18">
-        <f>0.13*G55*19.6</f>
-        <v>10.064638829625114</v>
+        <f>0.13*G55*42</f>
+        <v>11.466000000000001</v>
       </c>
       <c r="K59" s="17"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="16"/>
       <c r="B60" s="32"/>
       <c r="C60" s="17"/>
@@ -3950,183 +4027,377 @@
       <c r="J60" s="18"/>
       <c r="K60" s="17"/>
     </row>
-    <row r="61" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+    <row r="61" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="16">
+        <v>6</v>
+      </c>
+      <c r="B61" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="16"/>
+      <c r="B62" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="57">
+        <v>2</v>
+      </c>
+      <c r="D62" s="58">
+        <v>3</v>
+      </c>
+      <c r="E62" s="58">
+        <v>0.45</v>
+      </c>
+      <c r="F62" s="58">
+        <v>0.9</v>
+      </c>
+      <c r="G62" s="58">
+        <f>PRODUCT(C62:F62)</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
+      <c r="M62" s="33">
+        <f>7</f>
         <v>7</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="N62" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O62" s="33"/>
+      <c r="P62" s="33">
+        <f>PI()*M62*SQRT(M62^2+N62^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="16"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="17">
+        <v>0</v>
+      </c>
+      <c r="D63" s="33">
+        <v>3</v>
+      </c>
+      <c r="E63" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F63" s="33">
+        <v>0.9</v>
+      </c>
+      <c r="G63" s="33">
+        <f>PRODUCT(C63:F63)</f>
+        <v>0</v>
+      </c>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
+      <c r="M63" s="59"/>
+      <c r="N63" s="59"/>
+      <c r="O63" s="59"/>
+      <c r="P63" s="59"/>
+    </row>
+    <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2"/>
+      <c r="B64" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="3"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="6">
+        <f>SUM(G62:G62)</f>
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I64" s="6">
+        <v>6337.3</v>
+      </c>
+      <c r="J64" s="18">
+        <f>G64*I64</f>
+        <v>15399.639000000001</v>
+      </c>
+      <c r="K64" s="5"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65" s="16"/>
+      <c r="B65" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="18">
+        <f>0.13*G64*2577.63</f>
+        <v>814.27331700000002</v>
+      </c>
+      <c r="K65" s="17"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66" s="16"/>
+      <c r="B66" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="18">
+        <f>0.13*G64*257.76</f>
+        <v>81.426383999999999</v>
+      </c>
+      <c r="K66" s="17"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67" s="16"/>
+      <c r="B67" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="18">
+        <f>0.13*G64*133.56</f>
+        <v>42.191604000000005</v>
+      </c>
+      <c r="K67" s="17"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68" s="16"/>
+      <c r="B68" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="18">
+        <f>0.13*G64*19.6</f>
+        <v>6.1916400000000005</v>
+      </c>
+      <c r="K68" s="17"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69" s="16"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="17"/>
+    </row>
+    <row r="70" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>7</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C70" s="3">
         <v>1</v>
       </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="7">
-        <f t="shared" ref="G61" si="6">PRODUCT(C61:F61)</f>
+      <c r="D70" s="4"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="7">
+        <f t="shared" ref="G70" si="23">PRODUCT(C70:F70)</f>
         <v>1</v>
       </c>
-      <c r="H61" s="7" t="s">
+      <c r="H70" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I61" s="6">
+      <c r="I70" s="6">
         <v>1000</v>
       </c>
-      <c r="J61" s="7">
-        <f>G61*I61</f>
+      <c r="J70" s="7">
+        <f>G70*I70</f>
         <v>1000</v>
       </c>
-      <c r="K61" s="5"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="7"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="18"/>
-      <c r="K62" s="5"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" s="21"/>
-      <c r="B63" s="22" t="s">
+      <c r="K70" s="5"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="5"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72" s="21"/>
+      <c r="B72" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C63" s="23"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="18"/>
-      <c r="J63" s="18">
-        <f>SUM(J9:J61)</f>
-        <v>234835.07491669987</v>
-      </c>
-      <c r="K63" s="25"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="M64" s="20"/>
-      <c r="N64" s="20"/>
-      <c r="O64" s="20"/>
-      <c r="P64" s="20"/>
-      <c r="Q64" s="20"/>
-      <c r="R64" s="20"/>
-      <c r="S64" s="20"/>
-    </row>
-    <row r="65" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="26"/>
-      <c r="B65" s="27" t="s">
+      <c r="C72" s="23"/>
+      <c r="D72" s="24"/>
+      <c r="E72" s="24"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18">
+        <f>SUM(J9:J70)</f>
+        <v>171041.49224446158</v>
+      </c>
+      <c r="K72" s="25"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M73" s="20"/>
+      <c r="N73" s="20"/>
+      <c r="O73" s="20"/>
+      <c r="P73" s="20"/>
+      <c r="Q73" s="20"/>
+      <c r="R73" s="20"/>
+      <c r="S73" s="20"/>
+    </row>
+    <row r="74" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="26"/>
+      <c r="B74" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C65" s="50">
-        <f>J63</f>
-        <v>234835.07491669987</v>
-      </c>
-      <c r="D65" s="51"/>
-      <c r="E65" s="9">
+      <c r="C74" s="44">
+        <f>J72</f>
+        <v>171041.49224446158</v>
+      </c>
+      <c r="D74" s="45"/>
+      <c r="E74" s="9">
         <v>100</v>
       </c>
-      <c r="F65" s="26"/>
-      <c r="G65" s="28"/>
-      <c r="H65" s="26"/>
-      <c r="I65" s="29"/>
-      <c r="J65" s="30"/>
-      <c r="K65" s="31"/>
-      <c r="M65" s="19"/>
-      <c r="N65" s="19"/>
-      <c r="O65" s="19"/>
-      <c r="P65" s="19"/>
-      <c r="Q65" s="19"/>
-      <c r="R65" s="19"/>
-      <c r="S65" s="19"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B66" s="27" t="s">
+      <c r="F74" s="26"/>
+      <c r="G74" s="28"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="29"/>
+      <c r="J74" s="30"/>
+      <c r="K74" s="31"/>
+      <c r="M74" s="19"/>
+      <c r="N74" s="19"/>
+      <c r="O74" s="19"/>
+      <c r="P74" s="19"/>
+      <c r="Q74" s="19"/>
+      <c r="R74" s="19"/>
+      <c r="S74" s="19"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B75" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="54">
+      <c r="C75" s="48">
         <v>200000</v>
       </c>
-      <c r="D66" s="55"/>
-      <c r="E66" s="9"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B67" s="27" t="s">
+      <c r="D75" s="49"/>
+      <c r="E75" s="9"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B76" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="54">
-        <f>C66-C69-C70</f>
+      <c r="C76" s="48">
+        <f>C75-C78-C79</f>
         <v>190000</v>
       </c>
-      <c r="D67" s="55"/>
-      <c r="E67" s="9">
-        <f>C67/C65*100</f>
-        <v>80.907845673137345</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B68" s="27" t="s">
+      <c r="D76" s="49"/>
+      <c r="E76" s="9">
+        <f>C76/C74*100</f>
+        <v>111.08415712863516</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B77" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C68" s="56">
-        <f>C65-C67</f>
-        <v>44835.074916699872</v>
-      </c>
-      <c r="D68" s="56"/>
-      <c r="E68" s="9">
-        <f>100-E67</f>
-        <v>19.092154326862655</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B69" s="27" t="s">
+      <c r="C77" s="50">
+        <f>C74-C76</f>
+        <v>-18958.50775553842</v>
+      </c>
+      <c r="D77" s="50"/>
+      <c r="E77" s="9">
+        <f>100-E76</f>
+        <v>-11.084157128635155</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B78" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="50">
-        <f>C66*0.03</f>
+      <c r="C78" s="44">
+        <f>C75*0.03</f>
         <v>6000</v>
       </c>
-      <c r="D69" s="51"/>
-      <c r="E69" s="9">
+      <c r="D78" s="45"/>
+      <c r="E78" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B70" s="27" t="s">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B79" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C70" s="50">
-        <f>C66*0.02</f>
+      <c r="C79" s="44">
+        <f>C75*0.02</f>
         <v>4000</v>
       </c>
-      <c r="D70" s="51"/>
-      <c r="E70" s="9">
+      <c r="D79" s="45"/>
+      <c r="E79" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -4134,7 +4405,7 @@
     <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="45" max="10" man="1"/>
+    <brk id="53" max="10" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/बजेट माग estimate/वडा बजेट estimate/ukhu kheti/valuation ukhu kheti.xlsx
+++ b/बजेट माग estimate/वडा बजेट estimate/ukhu kheti/valuation ukhu kheti.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B624F5A-D265-47C2-95AE-ABBF63B02D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
     <sheet name="V" sheetId="13" r:id="rId2"/>
+    <sheet name="WCR" sheetId="14" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
     <definedName name="description_103">[1]Abstract!$B$16</definedName>
     <definedName name="description_124" localSheetId="0">#REF!</definedName>
     <definedName name="description_124" localSheetId="1">#REF!</definedName>
+    <definedName name="description_124" localSheetId="2">#REF!</definedName>
     <definedName name="description_124">#REF!</definedName>
     <definedName name="description_247">[1]Abstract!$B$22</definedName>
     <definedName name="description_248">[1]Abstract!$B$23</definedName>
@@ -29,26 +34,32 @@
     <definedName name="description_3">[1]Abstract!$B$169</definedName>
     <definedName name="description_310" localSheetId="0">#REF!</definedName>
     <definedName name="description_310" localSheetId="1">#REF!</definedName>
+    <definedName name="description_310" localSheetId="2">[5]Abstract!$B$60</definedName>
     <definedName name="description_310">#REF!</definedName>
     <definedName name="description_312" localSheetId="0">#REF!</definedName>
     <definedName name="description_312" localSheetId="1">#REF!</definedName>
+    <definedName name="description_312" localSheetId="2">[6]Abstract!$B$61</definedName>
     <definedName name="description_312">#REF!</definedName>
     <definedName name="description_5">[1]Abstract!$B$171</definedName>
     <definedName name="description_6" localSheetId="0">#REF!</definedName>
     <definedName name="description_6" localSheetId="1">#REF!</definedName>
+    <definedName name="description_6" localSheetId="2">[5]Abstract!$B$172</definedName>
     <definedName name="description_6">#REF!</definedName>
     <definedName name="description_759">[1]Abstract!$B$278</definedName>
     <definedName name="description_781" localSheetId="0">#REF!</definedName>
     <definedName name="description_781" localSheetId="1">#REF!</definedName>
+    <definedName name="description_781" localSheetId="2">[7]Abstract!$B$299</definedName>
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$70</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">V!$A$1:$K$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">V!$A$1:$K$94</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">WCR!$A$1:$K$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">V!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">WCR!$1:$12</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -66,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="91">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -298,16 +309,67 @@
   <si>
     <t>-cooking area</t>
   </si>
+  <si>
+    <t>Work Completion Report</t>
+  </si>
+  <si>
+    <t>Total Estimated Amount:</t>
+  </si>
+  <si>
+    <t>Total Valuated Amount :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Started : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Finished:           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">F.Y:2082/2083            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:2082/10/19       </t>
+  </si>
+  <si>
+    <t>S.No.</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Estimated</t>
+  </si>
+  <si>
+    <t>Valuated</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity </t>
+  </si>
+  <si>
+    <t>-MS square pipe of 66mm*33mm of 1.4mm thickness for horizontal member</t>
+  </si>
+  <si>
+    <t>-MS square pipe of 1.5" * 1.5" of 1.2mm thickness for horizontal support at walls</t>
+  </si>
+  <si>
+    <t>for tunnel</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,8 +450,64 @@
       <sz val="12"/>
       <name val="Preeti"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -405,6 +523,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,13 +594,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -484,7 +608,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -508,14 +632,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -534,7 +658,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -549,7 +673,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -580,7 +704,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -588,6 +712,45 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -608,53 +771,94 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2" xfId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="5"/>
+    <cellStyle name="Percent 2" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -670,7 +874,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -764,7 +968,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -823,7 +1027,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -886,10 +1090,228 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="estimate"/>
+      <sheetName val="valuation"/>
+      <sheetName val="WCR"/>
+      <sheetName val="m"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>Project:-तिनघरे बाटो स्तरोन्नति</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>Location:- Shankharapur Municipality 1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="12">
+          <cell r="G12">
+            <v>63.93</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="60">
+          <cell r="B60" t="str">
+            <v>Providing and laying of hand pack Stone soling with 150 to 200 mm thick stones and packing with smaller stone on prepared surface as per Drawing and Technical Specifications.</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="B172" t="str">
+            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications., RCC Grade M 20</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="61">
+          <cell r="B61" t="str">
+            <v>Providing and laying  granular sub-base   on prepared surface, mixing  at OMC, and compacting  to achieve the desired density, complete as per Drawing and Technical Specifications., By Mechanical means</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="299">
+          <cell r="B299" t="str">
+            <v>Random Rubble Masonry, Providing and laying of Stone Masonry Work in Cement Mortar 1:4 in Foundation complete as per Drawing and Technical Specifications.</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -927,9 +1349,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -964,7 +1386,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -999,7 +1421,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1172,135 +1594,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S70"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="19"/>
+    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" style="19" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="19"/>
+    <col min="9" max="9" width="9.5546875" style="19" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.109375" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="19"/>
+    <col min="17" max="16384" width="9.109375" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-    </row>
-    <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+    </row>
+    <row r="2" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-    </row>
-    <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="54" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+    </row>
+    <row r="5" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-    </row>
-    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="55" t="s">
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+    </row>
+    <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="56" t="s">
+      <c r="H6" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-    </row>
-    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+    </row>
+    <row r="7" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
@@ -1335,7 +1757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -1360,7 +1782,7 @@
       <c r="J9" s="39"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:18" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="16"/>
       <c r="B10" s="40" t="s">
         <v>57</v>
@@ -1389,7 +1811,7 @@
       <c r="J10" s="39"/>
       <c r="K10" s="27"/>
     </row>
-    <row r="11" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16"/>
       <c r="B11" s="40"/>
       <c r="C11" s="41">
@@ -1416,7 +1838,7 @@
       <c r="J11" s="39"/>
       <c r="K11" s="27"/>
     </row>
-    <row r="12" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
       <c r="B12" s="40"/>
       <c r="C12" s="41">
@@ -1443,7 +1865,7 @@
       <c r="J12" s="39"/>
       <c r="K12" s="27"/>
     </row>
-    <row r="13" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="16"/>
       <c r="B13" s="40"/>
       <c r="C13" s="41">
@@ -1470,7 +1892,7 @@
       <c r="J13" s="39"/>
       <c r="K13" s="27"/>
     </row>
-    <row r="14" spans="1:18" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A14" s="16"/>
       <c r="B14" s="40" t="s">
         <v>58</v>
@@ -1507,7 +1929,7 @@
         <v>89.995608214319134</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="16"/>
       <c r="B15" s="40"/>
       <c r="C15" s="41">
@@ -1534,7 +1956,7 @@
       <c r="J15" s="39"/>
       <c r="K15" s="27"/>
     </row>
-    <row r="16" spans="1:18" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="40" t="s">
         <v>59</v>
@@ -1563,7 +1985,7 @@
       <c r="J16" s="39"/>
       <c r="K16" s="27"/>
     </row>
-    <row r="17" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="40" t="s">
         <v>36</v>
@@ -1588,7 +2010,7 @@
       </c>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="40" t="s">
         <v>38</v>
@@ -1606,7 +2028,7 @@
       </c>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="40"/>
       <c r="C19" s="3"/>
@@ -1619,7 +2041,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>2</v>
       </c>
@@ -1636,7 +2058,7 @@
       <c r="J20" s="39"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="40" t="s">
         <v>39</v>
@@ -1663,7 +2085,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="40"/>
       <c r="C22" s="3">
@@ -1687,7 +2109,7 @@
       <c r="J22" s="39"/>
       <c r="K22" s="5"/>
     </row>
-    <row r="23" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="40" t="s">
         <v>36</v>
@@ -1712,7 +2134,7 @@
       </c>
       <c r="K23" s="5"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="16"/>
       <c r="B24" s="32" t="s">
         <v>41</v>
@@ -1730,7 +2152,7 @@
       </c>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="16"/>
       <c r="B25" s="32" t="s">
         <v>42</v>
@@ -1748,7 +2170,7 @@
       </c>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="16"/>
       <c r="B26" s="32" t="s">
         <v>43</v>
@@ -1766,7 +2188,7 @@
       </c>
       <c r="K26" s="17"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="16"/>
       <c r="B27" s="32" t="s">
         <v>44</v>
@@ -1784,7 +2206,7 @@
       </c>
       <c r="K27" s="17"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
       <c r="B28" s="32"/>
       <c r="C28" s="17"/>
@@ -1797,7 +2219,7 @@
       <c r="J28" s="18"/>
       <c r="K28" s="17"/>
     </row>
-    <row r="29" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A29" s="16">
         <v>3</v>
       </c>
@@ -1814,7 +2236,7 @@
       <c r="J29" s="18"/>
       <c r="K29" s="17"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="16"/>
       <c r="B30" s="32" t="s">
         <v>45</v>
@@ -1842,7 +2264,7 @@
       <c r="J30" s="18"/>
       <c r="K30" s="17"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="16"/>
       <c r="B31" s="32" t="s">
         <v>47</v>
@@ -1869,7 +2291,7 @@
       <c r="J31" s="18"/>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="40" t="s">
         <v>36</v>
@@ -1894,7 +2316,7 @@
       </c>
       <c r="K32" s="5"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="16"/>
       <c r="B33" s="32"/>
       <c r="C33" s="17"/>
@@ -1907,7 +2329,7 @@
       <c r="J33" s="18"/>
       <c r="K33" s="17"/>
     </row>
-    <row r="34" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A34" s="16">
         <v>4</v>
       </c>
@@ -1924,7 +2346,7 @@
       <c r="J34" s="18"/>
       <c r="K34" s="17"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="16"/>
       <c r="B35" s="32" t="str">
         <f>B31</f>
@@ -1954,7 +2376,7 @@
       <c r="J35" s="18"/>
       <c r="K35" s="17"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="16"/>
       <c r="B36" s="32" t="s">
         <v>55</v>
@@ -1983,7 +2405,7 @@
       <c r="J36" s="18"/>
       <c r="K36" s="17"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="32" t="s">
         <v>56</v>
@@ -2012,7 +2434,7 @@
       <c r="J37" s="18"/>
       <c r="K37" s="17"/>
     </row>
-    <row r="38" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="40" t="s">
         <v>36</v>
@@ -2037,7 +2459,7 @@
       </c>
       <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
       <c r="B39" s="32" t="s">
         <v>51</v>
@@ -2055,7 +2477,7 @@
       </c>
       <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="16"/>
       <c r="B40" s="32" t="s">
         <v>52</v>
@@ -2073,7 +2495,7 @@
       </c>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
       <c r="B41" s="42"/>
       <c r="C41" s="17"/>
@@ -2086,7 +2508,7 @@
       <c r="J41" s="18"/>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A42" s="16">
         <v>5</v>
       </c>
@@ -2103,7 +2525,7 @@
       <c r="J42" s="17"/>
       <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
       <c r="B43" s="32" t="str">
         <f>B35</f>
@@ -2131,7 +2553,7 @@
       <c r="J43" s="18"/>
       <c r="K43" s="17"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
       <c r="B44" s="32"/>
       <c r="C44" s="17">
@@ -2156,7 +2578,7 @@
       <c r="J44" s="18"/>
       <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="16"/>
       <c r="B45" s="32" t="str">
         <f>B36</f>
@@ -2186,7 +2608,7 @@
       <c r="J45" s="18"/>
       <c r="K45" s="17"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="32" t="s">
         <v>56</v>
@@ -2215,7 +2637,7 @@
       <c r="J46" s="18"/>
       <c r="K46" s="17"/>
     </row>
-    <row r="47" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="40" t="s">
         <v>36</v>
@@ -2240,7 +2662,7 @@
       </c>
       <c r="K47" s="5"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
       <c r="B48" s="32" t="s">
         <v>26</v>
@@ -2258,7 +2680,7 @@
       </c>
       <c r="K48" s="17"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
       <c r="B49" s="32" t="s">
         <v>27</v>
@@ -2276,7 +2698,7 @@
       </c>
       <c r="K49" s="17"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
       <c r="B50" s="32" t="s">
         <v>28</v>
@@ -2294,7 +2716,7 @@
       </c>
       <c r="K50" s="17"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="16"/>
       <c r="B51" s="32" t="s">
         <v>30</v>
@@ -2312,7 +2734,7 @@
       </c>
       <c r="K51" s="17"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="32"/>
       <c r="C52" s="17"/>
@@ -2325,7 +2747,7 @@
       <c r="J52" s="18"/>
       <c r="K52" s="17"/>
     </row>
-    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="16">
         <v>6</v>
       </c>
@@ -2342,7 +2764,7 @@
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
       <c r="B54" s="32" t="s">
         <v>45</v>
@@ -2383,7 +2805,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="34" t="s">
         <v>16</v>
@@ -2408,7 +2830,7 @@
       </c>
       <c r="K55" s="5"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
       <c r="B56" s="32" t="s">
         <v>51</v>
@@ -2426,7 +2848,7 @@
       </c>
       <c r="K56" s="17"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
       <c r="B57" s="32" t="s">
         <v>52</v>
@@ -2444,7 +2866,7 @@
       </c>
       <c r="K57" s="17"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="16"/>
       <c r="B58" s="32" t="s">
         <v>29</v>
@@ -2462,7 +2884,7 @@
       </c>
       <c r="K58" s="17"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="32" t="s">
         <v>30</v>
@@ -2480,7 +2902,7 @@
       </c>
       <c r="K59" s="17"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
       <c r="B60" s="32"/>
       <c r="C60" s="17"/>
@@ -2493,7 +2915,7 @@
       <c r="J60" s="18"/>
       <c r="K60" s="17"/>
     </row>
-    <row r="61" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>7</v>
       </c>
@@ -2522,7 +2944,7 @@
       </c>
       <c r="K61" s="5"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="2"/>
       <c r="B62" s="8"/>
       <c r="C62" s="3"/>
@@ -2535,7 +2957,7 @@
       <c r="J62" s="18"/>
       <c r="K62" s="5"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="21"/>
       <c r="B63" s="22" t="s">
         <v>20</v>
@@ -2553,7 +2975,7 @@
       </c>
       <c r="K63" s="25"/>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="M64" s="20"/>
       <c r="N64" s="20"/>
       <c r="O64" s="20"/>
@@ -2562,16 +2984,16 @@
       <c r="R64" s="20"/>
       <c r="S64" s="20"/>
     </row>
-    <row r="65" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="26"/>
       <c r="B65" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C65" s="44">
+      <c r="C65" s="59">
         <f>J63</f>
         <v>234835.07491669987</v>
       </c>
-      <c r="D65" s="45"/>
+      <c r="D65" s="60"/>
       <c r="E65" s="9">
         <v>100</v>
       </c>
@@ -2589,79 +3011,72 @@
       <c r="R65" s="19"/>
       <c r="S65" s="19"/>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B66" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="48">
+      <c r="C66" s="63">
         <v>200000</v>
       </c>
-      <c r="D66" s="49"/>
+      <c r="D66" s="64"/>
       <c r="E66" s="9"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B67" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="48">
+      <c r="C67" s="63">
         <f>C66-C69-C70</f>
         <v>190000</v>
       </c>
-      <c r="D67" s="49"/>
+      <c r="D67" s="64"/>
       <c r="E67" s="9">
         <f>C67/C65*100</f>
         <v>80.907845673137345</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B68" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C68" s="50">
+      <c r="C68" s="65">
         <f>C65-C67</f>
         <v>44835.074916699872</v>
       </c>
-      <c r="D68" s="50"/>
+      <c r="D68" s="65"/>
       <c r="E68" s="9">
         <f>100-E67</f>
         <v>19.092154326862655</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B69" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="44">
+      <c r="C69" s="59">
         <f>C66*0.03</f>
         <v>6000</v>
       </c>
-      <c r="D69" s="45"/>
+      <c r="D69" s="60"/>
       <c r="E69" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B70" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C70" s="44">
+      <c r="C70" s="59">
         <f>C66*0.02</f>
         <v>4000</v>
       </c>
-      <c r="D70" s="45"/>
+      <c r="D70" s="60"/>
       <c r="E70" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C69:D69"/>
     <mergeCell ref="C70:D70"/>
     <mergeCell ref="A7:F7"/>
@@ -2670,6 +3085,13 @@
     <mergeCell ref="C66:D66"/>
     <mergeCell ref="C67:D67"/>
     <mergeCell ref="C68:D68"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -2683,135 +3105,135 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD9D6B52-0BCE-4A59-BC99-2ABBFC24DADE}">
-  <dimension ref="A1:S79"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S94"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="19"/>
+    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" style="19" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="19"/>
+    <col min="9" max="9" width="9.5546875" style="19" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.109375" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="19"/>
+    <col min="17" max="16384" width="9.109375" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="54" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+    </row>
+    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="58" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="54"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="54"/>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="55" t="s">
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="56" t="s">
+      <c r="H6" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="46" t="s">
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
@@ -2846,7 +3268,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -2871,26 +3293,26 @@
       <c r="J9" s="39"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="16"/>
       <c r="B10" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="63">
+      <c r="C10" s="50">
         <v>2</v>
       </c>
-      <c r="D10" s="64">
+      <c r="D10" s="51">
         <f>(15.5+1)/3.281</f>
         <v>5.0289545870161536</v>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="51">
         <v>3.54</v>
       </c>
-      <c r="F10" s="64">
+      <c r="F10" s="51">
         <f t="shared" ref="F10" si="0">PRODUCT(C10:E10)</f>
         <v>35.604998476074371</v>
       </c>
-      <c r="G10" s="64">
+      <c r="G10" s="51">
         <f t="shared" ref="G10" si="1">F10</f>
         <v>35.604998476074371</v>
       </c>
@@ -2899,24 +3321,24 @@
       <c r="J10" s="39"/>
       <c r="K10" s="27"/>
     </row>
-    <row r="11" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16"/>
       <c r="B11" s="40"/>
-      <c r="C11" s="63">
+      <c r="C11" s="50">
         <v>2</v>
       </c>
-      <c r="D11" s="64">
+      <c r="D11" s="51">
         <f>(15.5-1.5+2)/3.281</f>
         <v>4.8765620237732392</v>
       </c>
-      <c r="E11" s="64">
+      <c r="E11" s="51">
         <v>3.54</v>
       </c>
-      <c r="F11" s="64">
+      <c r="F11" s="51">
         <f t="shared" ref="F11" si="2">PRODUCT(C11:E11)</f>
         <v>34.526059128314536</v>
       </c>
-      <c r="G11" s="64">
+      <c r="G11" s="51">
         <f t="shared" ref="G11" si="3">F11</f>
         <v>34.526059128314536</v>
       </c>
@@ -2925,25 +3347,25 @@
       <c r="J11" s="39"/>
       <c r="K11" s="27"/>
     </row>
-    <row r="12" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
       <c r="B12" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="63">
+      <c r="C12" s="50">
         <v>2</v>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="51">
         <v>3.9</v>
       </c>
-      <c r="E12" s="64">
+      <c r="E12" s="51">
         <v>2.14</v>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="51">
         <f>PRODUCT(C12:E12)</f>
         <v>16.692</v>
       </c>
-      <c r="G12" s="64">
+      <c r="G12" s="51">
         <f>F12</f>
         <v>16.692</v>
       </c>
@@ -2952,25 +3374,25 @@
       <c r="J12" s="39"/>
       <c r="K12" s="27"/>
     </row>
-    <row r="13" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="16"/>
       <c r="B13" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="63">
+      <c r="C13" s="50">
         <v>9</v>
       </c>
-      <c r="D13" s="64">
+      <c r="D13" s="51">
         <v>3.09</v>
       </c>
-      <c r="E13" s="64">
+      <c r="E13" s="51">
         <v>2.14</v>
       </c>
-      <c r="F13" s="64">
+      <c r="F13" s="51">
         <f t="shared" ref="F13" si="4">PRODUCT(C13:E13)</f>
         <v>59.513399999999997</v>
       </c>
-      <c r="G13" s="64">
+      <c r="G13" s="51">
         <f t="shared" ref="G13" si="5">F13</f>
         <v>59.513399999999997</v>
       </c>
@@ -2979,25 +3401,25 @@
       <c r="J13" s="39"/>
       <c r="K13" s="27"/>
     </row>
-    <row r="14" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="16"/>
       <c r="B14" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="63">
+      <c r="C14" s="50">
         <v>1</v>
       </c>
-      <c r="D14" s="64">
+      <c r="D14" s="51">
         <v>3.9</v>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="51">
         <v>2.35</v>
       </c>
-      <c r="F14" s="64">
+      <c r="F14" s="51">
         <f t="shared" ref="F14" si="6">PRODUCT(C14:E14)</f>
         <v>9.1650000000000009</v>
       </c>
-      <c r="G14" s="64">
+      <c r="G14" s="51">
         <f t="shared" ref="G14" si="7">F14</f>
         <v>9.1650000000000009</v>
       </c>
@@ -3006,26 +3428,26 @@
       <c r="J14" s="39"/>
       <c r="K14" s="27"/>
     </row>
-    <row r="15" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A15" s="16"/>
       <c r="B15" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="63">
+      <c r="C15" s="50">
         <v>3</v>
       </c>
-      <c r="D15" s="64">
+      <c r="D15" s="51">
         <f>(7+1)/3.281</f>
         <v>2.4382810118866196</v>
       </c>
-      <c r="E15" s="64">
+      <c r="E15" s="51">
         <v>3.54</v>
       </c>
-      <c r="F15" s="64">
+      <c r="F15" s="51">
         <f t="shared" ref="F15" si="8">PRODUCT(C15:E15)</f>
         <v>25.8945443462359</v>
       </c>
-      <c r="G15" s="64">
+      <c r="G15" s="51">
         <f t="shared" ref="G15" si="9">F15</f>
         <v>25.8945443462359</v>
       </c>
@@ -3034,23 +3456,23 @@
       <c r="J15" s="39"/>
       <c r="K15" s="27"/>
     </row>
-    <row r="16" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16" s="40"/>
-      <c r="C16" s="63">
+      <c r="C16" s="50">
         <v>3</v>
       </c>
-      <c r="D16" s="64">
+      <c r="D16" s="51">
         <v>2.6</v>
       </c>
-      <c r="E16" s="64">
+      <c r="E16" s="51">
         <v>3.54</v>
       </c>
-      <c r="F16" s="64">
+      <c r="F16" s="51">
         <f t="shared" ref="F16:F17" si="10">PRODUCT(C16:E16)</f>
         <v>27.612000000000002</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="51">
         <f t="shared" ref="G16:G17" si="11">F16</f>
         <v>27.612000000000002</v>
       </c>
@@ -3059,25 +3481,25 @@
       <c r="J16" s="39"/>
       <c r="K16" s="27"/>
     </row>
-    <row r="17" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A17" s="16"/>
       <c r="B17" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="50">
         <v>5</v>
       </c>
-      <c r="D17" s="64">
+      <c r="D17" s="51">
         <v>3.09</v>
       </c>
-      <c r="E17" s="64">
+      <c r="E17" s="51">
         <v>1.39</v>
       </c>
-      <c r="F17" s="64">
+      <c r="F17" s="51">
         <f t="shared" si="10"/>
         <v>21.475499999999997</v>
       </c>
-      <c r="G17" s="64">
+      <c r="G17" s="51">
         <f t="shared" si="11"/>
         <v>21.475499999999997</v>
       </c>
@@ -3086,26 +3508,26 @@
       <c r="J17" s="39"/>
       <c r="K17" s="27"/>
     </row>
-    <row r="18" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A18" s="16"/>
       <c r="B18" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="63">
+      <c r="C18" s="50">
         <v>5</v>
       </c>
-      <c r="D18" s="64">
+      <c r="D18" s="51">
         <f>1.8+1.9</f>
         <v>3.7</v>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="51">
         <v>1.39</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="51">
         <f t="shared" ref="F18" si="12">PRODUCT(C18:E18)</f>
         <v>25.715</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="51">
         <f t="shared" ref="G18" si="13">F18</f>
         <v>25.715</v>
       </c>
@@ -3114,27 +3536,27 @@
       <c r="J18" s="39"/>
       <c r="K18" s="27"/>
     </row>
-    <row r="19" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="16"/>
       <c r="B19" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="63">
+      <c r="C19" s="50">
         <v>3</v>
       </c>
-      <c r="D19" s="64">
+      <c r="D19" s="51">
         <f>13/3.281</f>
         <v>3.9622066443157573</v>
       </c>
-      <c r="E19" s="64">
+      <c r="E19" s="51">
         <v>1.39</v>
       </c>
-      <c r="F19" s="64">
-        <f t="shared" ref="F19" si="14">PRODUCT(C19:E19)</f>
+      <c r="F19" s="51">
+        <f t="shared" ref="F19:F20" si="14">PRODUCT(C19:E19)</f>
         <v>16.522401706796707</v>
       </c>
-      <c r="G19" s="64">
-        <f t="shared" ref="G19" si="15">F19</f>
+      <c r="G19" s="51">
+        <f t="shared" ref="G19:G20" si="15">F19</f>
         <v>16.522401706796707</v>
       </c>
       <c r="H19" s="39"/>
@@ -3142,418 +3564,448 @@
       <c r="J19" s="39"/>
       <c r="K19" s="27"/>
     </row>
-    <row r="20" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
+    <row r="20" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="16"/>
       <c r="B20" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="50">
+        <v>3</v>
+      </c>
+      <c r="D20" s="51">
+        <f>(13)/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E20" s="51">
+        <v>3.54</v>
+      </c>
+      <c r="F20" s="51">
+        <f t="shared" si="14"/>
+        <v>42.078634562633347</v>
+      </c>
+      <c r="G20" s="51">
+        <f t="shared" si="15"/>
+        <v>42.078634562633347</v>
+      </c>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="27"/>
+    </row>
+    <row r="21" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="16"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="50">
+        <v>3</v>
+      </c>
+      <c r="D21" s="51">
+        <f>(9)/3.281</f>
+        <v>2.7430661383724475</v>
+      </c>
+      <c r="E21" s="51">
+        <v>3.54</v>
+      </c>
+      <c r="F21" s="51">
+        <f t="shared" ref="F21:F24" si="16">PRODUCT(C21:E21)</f>
+        <v>29.131362389515388</v>
+      </c>
+      <c r="G21" s="51">
+        <f t="shared" ref="G21:G24" si="17">F21</f>
+        <v>29.131362389515388</v>
+      </c>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="27"/>
+    </row>
+    <row r="22" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="16"/>
+      <c r="B22" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="50">
+        <v>5</v>
+      </c>
+      <c r="D22" s="51">
+        <f>3.8+7-11.33/3.281+0.6</f>
+        <v>7.9467845169155744</v>
+      </c>
+      <c r="E22" s="51">
+        <v>1.39</v>
+      </c>
+      <c r="F22" s="51">
+        <f t="shared" si="16"/>
+        <v>55.230152392563234</v>
+      </c>
+      <c r="G22" s="51">
+        <f t="shared" si="17"/>
+        <v>55.230152392563234</v>
+      </c>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="27"/>
+    </row>
+    <row r="23" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="16"/>
+      <c r="B23" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="50">
+        <v>3</v>
+      </c>
+      <c r="D23" s="51">
+        <f>11.25/3.281</f>
+        <v>3.4288326729655592</v>
+      </c>
+      <c r="E23" s="51">
+        <v>2.35</v>
+      </c>
+      <c r="F23" s="51">
+        <f t="shared" si="16"/>
+        <v>24.173270344407193</v>
+      </c>
+      <c r="G23" s="51">
+        <f t="shared" si="17"/>
+        <v>24.173270344407193</v>
+      </c>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="27"/>
+    </row>
+    <row r="24" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="16"/>
+      <c r="B24" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="50">
+        <v>3</v>
+      </c>
+      <c r="D24" s="51">
+        <f>(11.667*2)/3.281</f>
+        <v>7.1118561414202981</v>
+      </c>
+      <c r="E24" s="51">
+        <v>1.39</v>
+      </c>
+      <c r="F24" s="51">
+        <f t="shared" si="16"/>
+        <v>29.656440109722642</v>
+      </c>
+      <c r="G24" s="51">
+        <f t="shared" si="17"/>
+        <v>29.656440109722642</v>
+      </c>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="27"/>
+    </row>
+    <row r="25" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="16"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="50">
+        <v>3</v>
+      </c>
+      <c r="D25" s="51">
+        <f>11.25/3.281</f>
+        <v>3.4288326729655592</v>
+      </c>
+      <c r="E25" s="51">
+        <v>1.39</v>
+      </c>
+      <c r="F25" s="51">
+        <f t="shared" ref="F25" si="18">PRODUCT(C25:E25)</f>
+        <v>14.298232246266382</v>
+      </c>
+      <c r="G25" s="51">
+        <f t="shared" ref="G25" si="19">F25</f>
+        <v>14.298232246266382</v>
+      </c>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="27"/>
+    </row>
+    <row r="26" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="16"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="50">
+        <v>6</v>
+      </c>
+      <c r="D26" s="51">
+        <f>11.25/3.281</f>
+        <v>3.4288326729655592</v>
+      </c>
+      <c r="E26" s="51">
+        <v>1.39</v>
+      </c>
+      <c r="F26" s="51">
+        <f t="shared" ref="F26" si="20">PRODUCT(C26:E26)</f>
+        <v>28.596464492532764</v>
+      </c>
+      <c r="G26" s="51">
+        <f t="shared" ref="G26" si="21">F26</f>
+        <v>28.596464492532764</v>
+      </c>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="27"/>
+    </row>
+    <row r="27" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="16"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="27"/>
+    </row>
+    <row r="28" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="39">
-        <f>SUM(G10:G19)</f>
-        <v>272.72090365742145</v>
-      </c>
-      <c r="H20" s="7" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="39">
+        <f>SUM(G10:G27)</f>
+        <v>495.88546019506242</v>
+      </c>
+      <c r="H28" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I28" s="6">
         <v>182.51</v>
       </c>
-      <c r="J20" s="39">
-        <f>G20*I20</f>
-        <v>49774.292126515982</v>
-      </c>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="21" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="40" t="s">
+      <c r="J28" s="39">
+        <f>G28*I28</f>
+        <v>90504.055340200837</v>
+      </c>
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="39">
-        <f>0.13*G20*(1871.42/18.94)</f>
-        <v>3503.1043272404604</v>
-      </c>
-      <c r="K21" s="5"/>
-    </row>
-    <row r="22" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="5"/>
-    </row>
-    <row r="23" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="39">
+        <f>0.13*G28*(1871.42/18.94)</f>
+        <v>6369.6565907799195</v>
+      </c>
+      <c r="K29" s="5"/>
+    </row>
+    <row r="30" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="5"/>
+    </row>
+    <row r="31" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
         <v>2</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B31" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2"/>
-      <c r="B24" s="40" t="s">
+      <c r="C31" s="3"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="5"/>
+    </row>
+    <row r="32" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="60">
-        <f>2*1</f>
-        <v>2</v>
-      </c>
-      <c r="D24" s="61">
-        <f>(10+4)/3.281</f>
-        <v>4.2669917708015843</v>
-      </c>
-      <c r="E24" s="62">
+      <c r="C32" s="47">
+        <v>1</v>
+      </c>
+      <c r="D32" s="48">
+        <f>(10+3)/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E32" s="49">
         <f>(7)/3.281</f>
         <v>2.1334958854007922</v>
       </c>
-      <c r="F24" s="62"/>
-      <c r="G24" s="58">
-        <f t="shared" ref="G24:G25" si="16">PRODUCT(C24:F24)</f>
-        <v>18.207218772088439</v>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="39"/>
-      <c r="K24" s="5"/>
-    </row>
-    <row r="25" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="40" t="s">
+      <c r="F32" s="49"/>
+      <c r="G32" s="45">
+        <f t="shared" ref="G32:G33" si="22">PRODUCT(C32:F32)</f>
+        <v>8.4533515727553485</v>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="60">
+      <c r="C33" s="47">
         <v>1</v>
       </c>
-      <c r="D25" s="61">
-        <f>(13.5)/3.281</f>
-        <v>4.1145992075586708</v>
-      </c>
-      <c r="E25" s="62">
-        <f>1.8+1.9</f>
-        <v>3.7</v>
-      </c>
-      <c r="F25" s="62"/>
-      <c r="G25" s="58">
-        <f t="shared" si="16"/>
-        <v>15.224017067967083</v>
-      </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="5"/>
-    </row>
-    <row r="26" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="60">
-        <v>1</v>
-      </c>
-      <c r="D26" s="61">
+      <c r="D33" s="48">
+        <f>(13)/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E33" s="49">
+        <f>1.75+1.75</f>
+        <v>3.5</v>
+      </c>
+      <c r="F33" s="49"/>
+      <c r="G33" s="45">
+        <f t="shared" si="22"/>
+        <v>13.867723255105151</v>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="5"/>
+    </row>
+    <row r="34" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="47">
+        <v>0</v>
+      </c>
+      <c r="D34" s="48">
         <f>(7)/3.281</f>
         <v>2.1334958854007922</v>
       </c>
-      <c r="E26" s="62">
-        <f>1.8+1.9</f>
-        <v>3.7</v>
-      </c>
-      <c r="F26" s="62"/>
-      <c r="G26" s="58">
-        <f t="shared" ref="G26" si="17">PRODUCT(C26:F26)</f>
-        <v>7.893934775982931</v>
-      </c>
-      <c r="H26" s="7"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="39"/>
-      <c r="K26" s="5"/>
-    </row>
-    <row r="27" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="40" t="s">
+      <c r="E34" s="49">
+        <f>1.75+1.9</f>
+        <v>3.65</v>
+      </c>
+      <c r="F34" s="49"/>
+      <c r="G34" s="45">
+        <f t="shared" ref="G34:G35" si="23">PRODUCT(C34:F34)</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="7"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="47">
+        <v>1</v>
+      </c>
+      <c r="D35" s="48">
+        <f>3.75+7-11.33/3.281</f>
+        <v>7.2967845169155741</v>
+      </c>
+      <c r="E35" s="49">
+        <f>14/3.281</f>
+        <v>4.2669917708015843</v>
+      </c>
+      <c r="F35" s="49"/>
+      <c r="G35" s="45">
+        <f t="shared" si="23"/>
+        <v>31.135319486991168</v>
+      </c>
+      <c r="H35" s="7"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="5"/>
+    </row>
+    <row r="36" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="39">
-        <f>SUM(G24:G26)</f>
-        <v>41.325170616038449</v>
-      </c>
-      <c r="H27" s="7" t="s">
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="39">
+        <f>SUM(G32:G35)</f>
+        <v>53.456394314851664</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I36" s="6">
         <v>1074.98</v>
       </c>
-      <c r="J27" s="39">
-        <f>G27*I27</f>
-        <v>44423.73190882901</v>
-      </c>
-      <c r="K27" s="5"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-      <c r="B28" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="18">
-        <f>0.13*G27*6674.66/10</f>
-        <v>3585.8090229526133</v>
-      </c>
-      <c r="K28" s="17"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="B29" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="18">
-        <f>0.13*G27*1023.75/10</f>
-        <v>549.98636443620171</v>
-      </c>
-      <c r="K29" s="17"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="16"/>
-      <c r="B30" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="18">
-        <f>0.13*G27*348.21/10</f>
-        <v>187.06788958273972</v>
-      </c>
-      <c r="K30" s="17"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
-      <c r="B31" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="18">
-        <f>0.13*G27*165/10</f>
-        <v>88.642490971402466</v>
-      </c>
-      <c r="K31" s="17"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="17"/>
-    </row>
-    <row r="33" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="16">
-        <v>3</v>
-      </c>
-      <c r="B33" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="17"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
-      <c r="B34" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="57">
-        <v>2</v>
-      </c>
-      <c r="D34" s="58">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E34" s="57">
-        <v>0.45</v>
-      </c>
-      <c r="F34" s="57">
-        <v>0.9</v>
-      </c>
-      <c r="G34" s="58">
-        <f t="shared" ref="G34:G37" si="18">PRODUCT(C34:F34)</f>
-        <v>1.9750076196281618</v>
-      </c>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="17"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="16"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="17">
-        <v>0</v>
-      </c>
-      <c r="D35" s="33">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E35" s="17">
-        <v>0.45</v>
-      </c>
-      <c r="F35" s="17">
-        <v>0.9</v>
-      </c>
-      <c r="G35" s="33">
-        <f t="shared" ref="G35" si="19">PRODUCT(C35:F35)</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="17"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C36" s="57">
-        <f>2*6</f>
-        <v>12</v>
-      </c>
-      <c r="D36" s="58">
-        <v>0.45</v>
-      </c>
-      <c r="E36" s="57">
-        <v>0.45</v>
-      </c>
-      <c r="F36" s="57">
-        <v>0.45</v>
-      </c>
-      <c r="G36" s="58">
-        <f t="shared" si="18"/>
-        <v>1.0935000000000001</v>
-      </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="17"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J36" s="39">
+        <f>G36*I36</f>
+        <v>57464.554760579245</v>
+      </c>
+      <c r="K36" s="5"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="16"/>
       <c r="B37" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="57">
-        <v>1</v>
-      </c>
-      <c r="D37" s="58">
-        <f>13/3.281</f>
-        <v>3.9622066443157573</v>
-      </c>
-      <c r="E37" s="58">
-        <f>10/3.281</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="F37" s="57">
-        <v>0.1</v>
-      </c>
-      <c r="G37" s="58">
-        <f t="shared" si="18"/>
-        <v>1.2076216532507642</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
-      <c r="J37" s="18"/>
+      <c r="J37" s="18">
+        <f>0.13*G36*6674.66/10</f>
+        <v>4638.4423394083815</v>
+      </c>
       <c r="K37" s="17"/>
     </row>
-    <row r="38" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="39">
-        <f>SUM(G34:G37)</f>
-        <v>4.2761292728789257</v>
-      </c>
-      <c r="H38" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I38" s="6">
-        <v>674.12</v>
-      </c>
-      <c r="J38" s="39">
-        <f>G38*I38</f>
-        <v>2882.6242654331413</v>
-      </c>
-      <c r="K38" s="5"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="16"/>
+      <c r="B38" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="18">
+        <f>0.13*G36*1023.75/10</f>
+        <v>711.43778783778214</v>
+      </c>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="16"/>
-      <c r="B39" s="32"/>
+      <c r="B39" s="32" t="s">
+        <v>43</v>
+      </c>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
@@ -3561,15 +4013,16 @@
       <c r="G39" s="17"/>
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
-      <c r="J39" s="18"/>
+      <c r="J39" s="18">
+        <f>0.13*G36*348.21/10</f>
+        <v>241.98266383686845</v>
+      </c>
       <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="16">
-        <v>4</v>
-      </c>
-      <c r="B40" s="43" t="s">
-        <v>50</v>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="16"/>
+      <c r="B40" s="32" t="s">
+        <v>44</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -3578,428 +4031,452 @@
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
-      <c r="J40" s="18"/>
+      <c r="J40" s="18">
+        <f>0.13*G36*165/10</f>
+        <v>114.66396580535684</v>
+      </c>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="16"/>
-      <c r="B41" s="32" t="str">
-        <f>B36</f>
-        <v>-for footing of vertical post</v>
-      </c>
-      <c r="C41" s="57">
-        <f>C36</f>
-        <v>12</v>
-      </c>
-      <c r="D41" s="58">
-        <f>D36</f>
-        <v>0.45</v>
-      </c>
-      <c r="E41" s="58">
-        <f>E36</f>
-        <v>0.45</v>
-      </c>
-      <c r="F41" s="58">
-        <v>0.15</v>
-      </c>
-      <c r="G41" s="58">
-        <f t="shared" ref="G41:G44" si="20">PRODUCT(C41:F41)</f>
-        <v>0.36449999999999999</v>
-      </c>
+      <c r="B41" s="32"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
       <c r="J41" s="18"/>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="16"/>
-      <c r="B42" s="65" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="57">
-        <f>C52</f>
-        <v>1</v>
-      </c>
-      <c r="D42" s="58">
-        <f>D52</f>
-        <v>3.5</v>
-      </c>
-      <c r="E42" s="58">
-        <f>E52</f>
-        <v>3.9</v>
-      </c>
-      <c r="F42" s="58">
-        <v>0.15</v>
-      </c>
-      <c r="G42" s="58">
-        <f t="shared" si="20"/>
-        <v>2.0474999999999999</v>
-      </c>
+    <row r="42" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="16">
+        <v>3</v>
+      </c>
+      <c r="B42" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
       <c r="H42" s="17"/>
       <c r="I42" s="17"/>
       <c r="J42" s="18"/>
       <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="16"/>
-      <c r="B43" s="65"/>
-      <c r="C43" s="57">
-        <f>C53</f>
-        <v>1</v>
-      </c>
-      <c r="D43" s="58">
-        <f>D53</f>
-        <v>4.2</v>
-      </c>
-      <c r="E43" s="58">
-        <f>E53</f>
-        <v>3.2</v>
-      </c>
-      <c r="F43" s="58">
-        <v>0.15</v>
-      </c>
-      <c r="G43" s="58">
-        <f t="shared" ref="G43" si="21">PRODUCT(C43:F43)</f>
-        <v>2.016</v>
+      <c r="B43" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="44">
+        <v>2</v>
+      </c>
+      <c r="D43" s="45">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E43" s="44">
+        <v>0.45</v>
+      </c>
+      <c r="F43" s="44">
+        <v>0.9</v>
+      </c>
+      <c r="G43" s="45">
+        <f t="shared" ref="G43:G48" si="24">PRODUCT(C43:F43)</f>
+        <v>1.9750076196281618</v>
       </c>
       <c r="H43" s="17"/>
       <c r="I43" s="17"/>
       <c r="J43" s="18"/>
       <c r="K43" s="17"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="16"/>
-      <c r="B44" s="65" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="57">
-        <f>C54</f>
-        <v>-1</v>
-      </c>
-      <c r="D44" s="58">
-        <f>D54</f>
-        <v>3</v>
-      </c>
-      <c r="E44" s="58">
-        <f>E54</f>
-        <v>1.5</v>
-      </c>
-      <c r="F44" s="58">
-        <v>0.15</v>
-      </c>
-      <c r="G44" s="58">
-        <f t="shared" si="20"/>
-        <v>-0.67499999999999993</v>
+      <c r="B44" s="32"/>
+      <c r="C44" s="17">
+        <v>0</v>
+      </c>
+      <c r="D44" s="33">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E44" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F44" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="G44" s="33">
+        <f t="shared" ref="G44" si="25">PRODUCT(C44:F44)</f>
+        <v>0</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="17"/>
       <c r="J44" s="18"/>
       <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="39">
-        <f>SUM(G41:G44)</f>
-        <v>3.7530000000000001</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I45" s="6">
-        <v>4495.6400000000003</v>
-      </c>
-      <c r="J45" s="39">
-        <f>G45*I45</f>
-        <v>16872.136920000001</v>
-      </c>
-      <c r="K45" s="5"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="16"/>
+      <c r="B45" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="44">
+        <f>2*6</f>
+        <v>12</v>
+      </c>
+      <c r="D45" s="45">
+        <v>0.45</v>
+      </c>
+      <c r="E45" s="44">
+        <v>0.45</v>
+      </c>
+      <c r="F45" s="44">
+        <v>0.45</v>
+      </c>
+      <c r="G45" s="45">
+        <f t="shared" si="24"/>
+        <v>1.0935000000000001</v>
+      </c>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="16"/>
       <c r="B46" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
+        <v>55</v>
+      </c>
+      <c r="C46" s="44">
+        <v>1</v>
+      </c>
+      <c r="D46" s="45">
+        <f>13/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E46" s="45">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="F46" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="G46" s="45">
+        <f t="shared" si="24"/>
+        <v>1.2076216532507642</v>
+      </c>
       <c r="H46" s="17"/>
       <c r="I46" s="17"/>
-      <c r="J46" s="18">
-        <f>0.13*G45*2577.63</f>
-        <v>1257.5999007000003</v>
-      </c>
+      <c r="J46" s="18"/>
       <c r="K46" s="17"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="16"/>
       <c r="B47" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
+        <v>47</v>
+      </c>
+      <c r="C47" s="44">
+        <v>6</v>
+      </c>
+      <c r="D47" s="45">
+        <f>0.3</f>
+        <v>0.3</v>
+      </c>
+      <c r="E47" s="45">
+        <v>0.3</v>
+      </c>
+      <c r="F47" s="44">
+        <v>0.3</v>
+      </c>
+      <c r="G47" s="45">
+        <f t="shared" si="24"/>
+        <v>0.16199999999999998</v>
+      </c>
       <c r="H47" s="17"/>
       <c r="I47" s="17"/>
-      <c r="J47" s="18">
-        <f>0.13*G45*515.52</f>
-        <v>251.51705280000002</v>
-      </c>
+      <c r="J47" s="18"/>
       <c r="K47" s="17"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="16"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
+      <c r="B48" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="44">
+        <v>1</v>
+      </c>
+      <c r="D48" s="45">
+        <f>9/3.281</f>
+        <v>2.7430661383724475</v>
+      </c>
+      <c r="E48" s="45">
+        <v>0.6</v>
+      </c>
+      <c r="F48" s="44">
+        <v>0.9</v>
+      </c>
+      <c r="G48" s="45">
+        <f t="shared" si="24"/>
+        <v>1.4812557147211216</v>
+      </c>
       <c r="H48" s="17"/>
       <c r="I48" s="17"/>
       <c r="J48" s="18"/>
       <c r="K48" s="17"/>
     </row>
-    <row r="49" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="16">
-        <v>5</v>
-      </c>
-      <c r="B49" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2"/>
+      <c r="B49" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="39">
+        <f>SUM(G43:G48)</f>
+        <v>5.9193849876000471</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I49" s="6">
+        <v>674.12</v>
+      </c>
+      <c r="J49" s="39">
+        <f>G49*I49</f>
+        <v>3990.3758078409437</v>
+      </c>
+      <c r="K49" s="5"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="16"/>
-      <c r="B50" s="32" t="str">
-        <f>B41</f>
-        <v>-for footing of vertical post</v>
-      </c>
-      <c r="C50" s="57">
-        <f>C36</f>
-        <v>12</v>
-      </c>
-      <c r="D50" s="58">
-        <v>0.45</v>
-      </c>
-      <c r="E50" s="57">
-        <v>0.45</v>
-      </c>
-      <c r="F50" s="58">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G50" s="58">
-        <f t="shared" ref="G50:G54" si="22">PRODUCT(C50:F50)</f>
-        <v>0.18225</v>
-      </c>
+      <c r="B50" s="32"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
       <c r="H50" s="17"/>
       <c r="I50" s="17"/>
       <c r="J50" s="18"/>
       <c r="K50" s="17"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="16"/>
-      <c r="B51" s="32"/>
-      <c r="C51" s="17">
-        <v>0</v>
-      </c>
-      <c r="D51" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="E51" s="17">
-        <v>0.45</v>
-      </c>
-      <c r="F51" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="G51" s="33">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
+    <row r="51" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="16">
+        <v>4</v>
+      </c>
+      <c r="B51" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
       <c r="H51" s="17"/>
       <c r="I51" s="17"/>
       <c r="J51" s="18"/>
       <c r="K51" s="17"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="16"/>
       <c r="B52" s="32" t="str">
-        <f>B42</f>
-        <v>-for flooring</v>
-      </c>
-      <c r="C52" s="57">
-        <v>1</v>
-      </c>
-      <c r="D52" s="58">
-        <v>3.5</v>
-      </c>
-      <c r="E52" s="58">
-        <v>3.9</v>
-      </c>
-      <c r="F52" s="58">
+        <f>B45</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C52" s="44">
+        <f>C45</f>
+        <v>12</v>
+      </c>
+      <c r="D52" s="45">
+        <f>D45</f>
+        <v>0.45</v>
+      </c>
+      <c r="E52" s="45">
+        <f>E45</f>
+        <v>0.45</v>
+      </c>
+      <c r="F52" s="45">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G52" s="58">
-        <f t="shared" si="22"/>
-        <v>1.0237499999999999</v>
+      <c r="G52" s="45">
+        <f t="shared" ref="G52:G55" si="26">PRODUCT(C52:F52)</f>
+        <v>0.18225</v>
       </c>
       <c r="H52" s="17"/>
       <c r="I52" s="17"/>
       <c r="J52" s="18"/>
       <c r="K52" s="17"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="16"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="57">
+      <c r="B53" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="44">
+        <f t="shared" ref="C53:E55" si="27">C65</f>
         <v>1</v>
       </c>
-      <c r="D53" s="58">
-        <v>4.2</v>
-      </c>
-      <c r="E53" s="58">
-        <v>3.2</v>
-      </c>
-      <c r="F53" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="G53" s="58">
-        <f t="shared" si="22"/>
-        <v>1.3440000000000003</v>
+      <c r="D53" s="45">
+        <f t="shared" si="27"/>
+        <v>3.5</v>
+      </c>
+      <c r="E53" s="45">
+        <f t="shared" si="27"/>
+        <v>3.5</v>
+      </c>
+      <c r="F53" s="45">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G53" s="45">
+        <f t="shared" si="26"/>
+        <v>0.91874999999999996</v>
       </c>
       <c r="H53" s="17"/>
       <c r="I53" s="17"/>
       <c r="J53" s="18"/>
       <c r="K53" s="17"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="16"/>
-      <c r="B54" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C54" s="57">
-        <v>-1</v>
-      </c>
-      <c r="D54" s="58">
-        <v>3</v>
-      </c>
-      <c r="E54" s="58">
-        <f>0.6+0.45+0.45</f>
-        <v>1.5</v>
-      </c>
-      <c r="F54" s="58">
-        <v>0.1</v>
-      </c>
-      <c r="G54" s="58">
-        <f t="shared" si="22"/>
-        <v>-0.45</v>
+      <c r="B54" s="52"/>
+      <c r="C54" s="44">
+        <f t="shared" si="27"/>
+        <v>1</v>
+      </c>
+      <c r="D54" s="45">
+        <f t="shared" si="27"/>
+        <v>4.2</v>
+      </c>
+      <c r="E54" s="45">
+        <f t="shared" si="27"/>
+        <v>3.2</v>
+      </c>
+      <c r="F54" s="45">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G54" s="45">
+        <f t="shared" ref="G54" si="28">PRODUCT(C54:F54)</f>
+        <v>1.008</v>
       </c>
       <c r="H54" s="17"/>
       <c r="I54" s="17"/>
       <c r="J54" s="18"/>
       <c r="K54" s="17"/>
     </row>
-    <row r="55" spans="1:16" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="39">
-        <f>SUM(G50:G54)</f>
-        <v>2.1</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I55" s="6">
-        <v>13351.1</v>
-      </c>
-      <c r="J55" s="39">
-        <f>G55*I55</f>
-        <v>28037.31</v>
-      </c>
-      <c r="K55" s="5"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="16"/>
+      <c r="B55" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="44">
+        <f t="shared" si="27"/>
+        <v>-1</v>
+      </c>
+      <c r="D55" s="45">
+        <f t="shared" si="27"/>
+        <v>3</v>
+      </c>
+      <c r="E55" s="45">
+        <f t="shared" si="27"/>
+        <v>1.5</v>
+      </c>
+      <c r="F55" s="45">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G55" s="45">
+        <f t="shared" si="26"/>
+        <v>-0.33749999999999997</v>
+      </c>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="17"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="16"/>
-      <c r="B56" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
+      <c r="B56" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="44">
+        <v>1</v>
+      </c>
+      <c r="D56" s="45">
+        <v>3.5</v>
+      </c>
+      <c r="E56" s="45">
+        <v>3.65</v>
+      </c>
+      <c r="F56" s="45">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G56" s="45">
+        <f t="shared" ref="G56:G57" si="29">PRODUCT(C56:F56)</f>
+        <v>0.958125</v>
+      </c>
       <c r="H56" s="17"/>
       <c r="I56" s="17"/>
-      <c r="J56" s="18">
-        <f>0.13*G55*4169.92</f>
-        <v>1138.3881600000002</v>
-      </c>
+      <c r="J56" s="18"/>
       <c r="K56" s="17"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="16"/>
-      <c r="B57" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="44">
+        <v>1</v>
+      </c>
+      <c r="D57" s="45">
+        <v>3.5</v>
+      </c>
+      <c r="E57" s="45">
+        <v>0.65</v>
+      </c>
+      <c r="F57" s="45">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G57" s="45">
+        <f t="shared" si="29"/>
+        <v>0.170625</v>
+      </c>
       <c r="H57" s="17"/>
       <c r="I57" s="17"/>
-      <c r="J57" s="18">
-        <f>0.13*G55*1414.16</f>
-        <v>386.06568000000004</v>
-      </c>
+      <c r="J57" s="18"/>
       <c r="K57" s="17"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="16"/>
-      <c r="B58" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="18">
-        <f>0.13*G55*(1652.5+737.97+349.56)</f>
-        <v>748.02819000000011</v>
-      </c>
-      <c r="K58" s="17"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2"/>
+      <c r="B58" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C58" s="3"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="39">
+        <f>SUM(G52:G57)</f>
+        <v>2.9002499999999998</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I58" s="6">
+        <v>4495.6400000000003</v>
+      </c>
+      <c r="J58" s="39">
+        <f>G58*I58</f>
+        <v>13038.47991</v>
+      </c>
+      <c r="K58" s="5"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="16"/>
       <c r="B59" s="32" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
@@ -4009,14 +4486,16 @@
       <c r="H59" s="17"/>
       <c r="I59" s="17"/>
       <c r="J59" s="18">
-        <f>0.13*G55*42</f>
-        <v>11.466000000000001</v>
+        <f>0.13*G58*2577.63</f>
+        <v>971.85028297500003</v>
       </c>
       <c r="K59" s="17"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="16"/>
-      <c r="B60" s="32"/>
+      <c r="B60" s="32" t="s">
+        <v>52</v>
+      </c>
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
       <c r="E60" s="17"/>
@@ -4024,16 +4503,15 @@
       <c r="G60" s="17"/>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
-      <c r="J60" s="18"/>
+      <c r="J60" s="18">
+        <f>0.13*G58*515.52</f>
+        <v>194.36779439999998</v>
+      </c>
       <c r="K60" s="17"/>
     </row>
-    <row r="61" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="16">
-        <v>6</v>
-      </c>
-      <c r="B61" s="43" t="s">
-        <v>54</v>
-      </c>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="16"/>
+      <c r="B61" s="42"/>
       <c r="C61" s="17"/>
       <c r="D61" s="17"/>
       <c r="E61" s="17"/>
@@ -4041,348 +4519,685 @@
       <c r="G61" s="17"/>
       <c r="H61" s="17"/>
       <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
+      <c r="J61" s="18"/>
       <c r="K61" s="17"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="16"/>
-      <c r="B62" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" s="57">
-        <v>2</v>
-      </c>
-      <c r="D62" s="58">
-        <v>3</v>
-      </c>
-      <c r="E62" s="58">
-        <v>0.45</v>
-      </c>
-      <c r="F62" s="58">
-        <v>0.9</v>
-      </c>
-      <c r="G62" s="58">
-        <f>PRODUCT(C62:F62)</f>
-        <v>2.4300000000000002</v>
-      </c>
+    <row r="62" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="16">
+        <v>5</v>
+      </c>
+      <c r="B62" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
       <c r="H62" s="17"/>
       <c r="I62" s="17"/>
       <c r="J62" s="17"/>
       <c r="K62" s="17"/>
-      <c r="M62" s="33">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="16"/>
+      <c r="B63" s="32" t="str">
+        <f>B52</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C63" s="44">
+        <f>C45</f>
+        <v>12</v>
+      </c>
+      <c r="D63" s="45">
+        <v>0.45</v>
+      </c>
+      <c r="E63" s="44">
+        <v>0.45</v>
+      </c>
+      <c r="F63" s="45">
+        <v>0.05</v>
+      </c>
+      <c r="G63" s="45">
+        <f t="shared" ref="G63:G68" si="30">PRODUCT(C63:F63)</f>
+        <v>0.12150000000000001</v>
+      </c>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="17"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="16"/>
+      <c r="B64" s="32"/>
+      <c r="C64" s="17">
+        <v>0</v>
+      </c>
+      <c r="D64" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E64" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F64" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="G64" s="33">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="17"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A65" s="16"/>
+      <c r="B65" s="32" t="str">
+        <f>B53</f>
+        <v>-for flooring</v>
+      </c>
+      <c r="C65" s="44">
+        <v>1</v>
+      </c>
+      <c r="D65" s="45">
+        <v>3.5</v>
+      </c>
+      <c r="E65" s="45">
+        <v>3.5</v>
+      </c>
+      <c r="F65" s="45">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G65" s="45">
+        <f t="shared" si="30"/>
+        <v>0.91874999999999996</v>
+      </c>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="17"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A66" s="16"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="44">
+        <v>1</v>
+      </c>
+      <c r="D66" s="45">
+        <v>4.2</v>
+      </c>
+      <c r="E66" s="45">
+        <v>3.2</v>
+      </c>
+      <c r="F66" s="45">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G66" s="45">
+        <f t="shared" si="30"/>
+        <v>1.008</v>
+      </c>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="17"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67" s="16"/>
+      <c r="B67" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" s="44">
+        <v>-1</v>
+      </c>
+      <c r="D67" s="45">
+        <v>3</v>
+      </c>
+      <c r="E67" s="45">
+        <f>0.6+0.45+0.45</f>
+        <v>1.5</v>
+      </c>
+      <c r="F67" s="45">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G67" s="45">
+        <f t="shared" si="30"/>
+        <v>-0.33749999999999997</v>
+      </c>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="17"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68" s="16"/>
+      <c r="B68" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="C68" s="44">
+        <v>1</v>
+      </c>
+      <c r="D68" s="45">
+        <v>3.5</v>
+      </c>
+      <c r="E68" s="45">
+        <v>3.65</v>
+      </c>
+      <c r="F68" s="45">
+        <v>0.05</v>
+      </c>
+      <c r="G68" s="45">
+        <f t="shared" si="30"/>
+        <v>0.63875000000000004</v>
+      </c>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="17"/>
+    </row>
+    <row r="69" spans="1:16" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2"/>
+      <c r="B69" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="39">
+        <f>SUM(G63:G68)</f>
+        <v>2.3494999999999999</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I69" s="6">
+        <v>13351.1</v>
+      </c>
+      <c r="J69" s="39">
+        <f>G69*I69</f>
+        <v>31368.409449999999</v>
+      </c>
+      <c r="K69" s="5"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70" s="16"/>
+      <c r="B70" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="18">
+        <f>0.13*G69*4169.92</f>
+        <v>1273.6395152</v>
+      </c>
+      <c r="K70" s="17"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71" s="16"/>
+      <c r="B71" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="18">
+        <f>0.13*G69*1414.16</f>
+        <v>431.93395960000004</v>
+      </c>
+      <c r="K71" s="17"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A72" s="16"/>
+      <c r="B72" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="18">
+        <f>0.13*G69*(1652.5+737.97+349.56)</f>
+        <v>836.90106305000006</v>
+      </c>
+      <c r="K72" s="17"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73" s="16"/>
+      <c r="B73" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="17"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="17"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="18">
+        <f>0.13*G69*42</f>
+        <v>12.82827</v>
+      </c>
+      <c r="K73" s="17"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A74" s="16"/>
+      <c r="B74" s="32"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+      <c r="G74" s="17"/>
+      <c r="H74" s="17"/>
+      <c r="I74" s="17"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="17"/>
+    </row>
+    <row r="75" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="16">
+        <v>6</v>
+      </c>
+      <c r="B75" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A76" s="16"/>
+      <c r="B76" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" s="44">
+        <v>2</v>
+      </c>
+      <c r="D76" s="45">
+        <v>3</v>
+      </c>
+      <c r="E76" s="45">
+        <v>0.45</v>
+      </c>
+      <c r="F76" s="45">
+        <v>0.8</v>
+      </c>
+      <c r="G76" s="45">
+        <f>PRODUCT(C76:F76)</f>
+        <v>2.16</v>
+      </c>
+      <c r="H76" s="17"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="17"/>
+      <c r="K76" s="17"/>
+      <c r="M76" s="33">
         <f>7</f>
         <v>7</v>
       </c>
-      <c r="N62" s="33">
+      <c r="N76" s="33">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="O62" s="33"/>
-      <c r="P62" s="33">
-        <f>PI()*M62*SQRT(M62^2+N62^2)</f>
+      <c r="O76" s="33"/>
+      <c r="P76" s="33">
+        <f>PI()*M76*SQRT(M76^2+N76^2)</f>
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="16"/>
-      <c r="B63" s="32"/>
-      <c r="C63" s="17">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77" s="16"/>
+      <c r="B77" s="32"/>
+      <c r="C77" s="17">
         <v>0</v>
       </c>
-      <c r="D63" s="33">
+      <c r="D77" s="33">
         <v>3</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E77" s="33">
         <v>0.45</v>
       </c>
-      <c r="F63" s="33">
-        <v>0.9</v>
-      </c>
-      <c r="G63" s="33">
-        <f>PRODUCT(C63:F63)</f>
+      <c r="F77" s="33">
+        <v>0.8</v>
+      </c>
+      <c r="G77" s="45">
+        <f t="shared" ref="G77:G78" si="31">PRODUCT(C77:F77)</f>
         <v>0</v>
       </c>
-      <c r="H63" s="17"/>
-      <c r="I63" s="17"/>
-      <c r="J63" s="17"/>
-      <c r="K63" s="17"/>
-      <c r="M63" s="59"/>
-      <c r="N63" s="59"/>
-      <c r="O63" s="59"/>
-      <c r="P63" s="59"/>
-    </row>
-    <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2"/>
-      <c r="B64" s="34" t="s">
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
+      <c r="M77" s="46"/>
+      <c r="N77" s="46"/>
+      <c r="O77" s="46"/>
+      <c r="P77" s="46"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78" s="16"/>
+      <c r="B78" s="32"/>
+      <c r="C78" s="17">
+        <v>2</v>
+      </c>
+      <c r="D78" s="33">
+        <f>9/3.281</f>
+        <v>2.7430661383724475</v>
+      </c>
+      <c r="E78" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F78" s="33">
+        <v>0.8</v>
+      </c>
+      <c r="G78" s="45">
+        <f t="shared" si="31"/>
+        <v>1.9750076196281623</v>
+      </c>
+      <c r="H78" s="17"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="17"/>
+      <c r="K78" s="17"/>
+      <c r="M78" s="46"/>
+      <c r="N78" s="46"/>
+      <c r="O78" s="46"/>
+      <c r="P78" s="46"/>
+    </row>
+    <row r="79" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2"/>
+      <c r="B79" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C64" s="3"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="6">
-        <f>SUM(G62:G62)</f>
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="H64" s="7" t="s">
+      <c r="C79" s="3"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="6">
+        <f>SUM(G76:G78)</f>
+        <v>4.135007619628162</v>
+      </c>
+      <c r="H79" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I64" s="6">
+      <c r="I79" s="6">
         <v>6337.3</v>
       </c>
-      <c r="J64" s="18">
-        <f>G64*I64</f>
-        <v>15399.639000000001</v>
-      </c>
-      <c r="K64" s="5"/>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65" s="16"/>
-      <c r="B65" s="32" t="s">
+      <c r="J79" s="18">
+        <f>G79*I79</f>
+        <v>26204.78378786955</v>
+      </c>
+      <c r="K79" s="5"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80" s="16"/>
+      <c r="B80" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="18">
-        <f>0.13*G64*2577.63</f>
-        <v>814.27331700000002</v>
-      </c>
-      <c r="K65" s="17"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A66" s="16"/>
-      <c r="B66" s="32" t="s">
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="17"/>
+      <c r="H80" s="17"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="18">
+        <f>0.13*G79*2577.63</f>
+        <v>1385.6075597756783</v>
+      </c>
+      <c r="K80" s="17"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A81" s="16"/>
+      <c r="B81" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="18">
-        <f>0.13*G64*257.76</f>
-        <v>81.426383999999999</v>
-      </c>
-      <c r="K66" s="17"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A67" s="16"/>
-      <c r="B67" s="32" t="s">
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="18">
+        <f>0.13*G79*257.76</f>
+        <v>138.55914332459616</v>
+      </c>
+      <c r="K81" s="17"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A82" s="16"/>
+      <c r="B82" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="17"/>
-      <c r="G67" s="17"/>
-      <c r="H67" s="17"/>
-      <c r="I67" s="17"/>
-      <c r="J67" s="18">
-        <f>0.13*G64*133.56</f>
-        <v>42.191604000000005</v>
-      </c>
-      <c r="K67" s="17"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A68" s="16"/>
-      <c r="B68" s="32" t="s">
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="17"/>
+      <c r="G82" s="17"/>
+      <c r="H82" s="17"/>
+      <c r="I82" s="17"/>
+      <c r="J82" s="18">
+        <f>0.13*G79*133.56</f>
+        <v>71.795310298079855</v>
+      </c>
+      <c r="K82" s="17"/>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A83" s="16"/>
+      <c r="B83" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="17"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="17"/>
-      <c r="I68" s="17"/>
-      <c r="J68" s="18">
-        <f>0.13*G64*19.6</f>
-        <v>6.1916400000000005</v>
-      </c>
-      <c r="K68" s="17"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A69" s="16"/>
-      <c r="B69" s="32"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="17"/>
-      <c r="G69" s="17"/>
-      <c r="H69" s="17"/>
-      <c r="I69" s="17"/>
-      <c r="J69" s="18"/>
-      <c r="K69" s="17"/>
-    </row>
-    <row r="70" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="17"/>
+      <c r="G83" s="17"/>
+      <c r="H83" s="17"/>
+      <c r="I83" s="17"/>
+      <c r="J83" s="18">
+        <f>0.13*G79*19.6</f>
+        <v>10.535999414812558</v>
+      </c>
+      <c r="K83" s="17"/>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A84" s="16"/>
+      <c r="B84" s="32"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="17"/>
+      <c r="G84" s="17"/>
+      <c r="H84" s="17"/>
+      <c r="I84" s="17"/>
+      <c r="J84" s="18"/>
+      <c r="K84" s="17"/>
+    </row>
+    <row r="85" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
         <v>7</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C85" s="3">
         <v>1</v>
       </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="7">
-        <f t="shared" ref="G70" si="23">PRODUCT(C70:F70)</f>
+      <c r="D85" s="4"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="7">
+        <f t="shared" ref="G85" si="32">PRODUCT(C85:F85)</f>
         <v>1</v>
       </c>
-      <c r="H70" s="7" t="s">
+      <c r="H85" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I70" s="6">
+      <c r="I85" s="6">
         <v>1000</v>
       </c>
-      <c r="J70" s="7">
-        <f>G70*I70</f>
+      <c r="J85" s="7">
+        <f>G85*I85</f>
         <v>1000</v>
       </c>
-      <c r="K70" s="5"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A71" s="2"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="7"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="5"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A72" s="21"/>
-      <c r="B72" s="22" t="s">
+      <c r="K85" s="5"/>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A86" s="2"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="18"/>
+      <c r="K86" s="5"/>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A87" s="21"/>
+      <c r="B87" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C72" s="23"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="24"/>
-      <c r="F72" s="24"/>
-      <c r="G72" s="18"/>
-      <c r="H72" s="18"/>
-      <c r="I72" s="18"/>
-      <c r="J72" s="18">
-        <f>SUM(J9:J70)</f>
-        <v>171041.49224446158</v>
-      </c>
-      <c r="K72" s="25"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="M73" s="20"/>
-      <c r="N73" s="20"/>
-      <c r="O73" s="20"/>
-      <c r="P73" s="20"/>
-      <c r="Q73" s="20"/>
-      <c r="R73" s="20"/>
-      <c r="S73" s="20"/>
-    </row>
-    <row r="74" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="26"/>
-      <c r="B74" s="27" t="s">
+      <c r="C87" s="23"/>
+      <c r="D87" s="24"/>
+      <c r="E87" s="24"/>
+      <c r="F87" s="24"/>
+      <c r="G87" s="18"/>
+      <c r="H87" s="18"/>
+      <c r="I87" s="18"/>
+      <c r="J87" s="18">
+        <f>SUM(J9:J85)</f>
+        <v>240974.86130219698</v>
+      </c>
+      <c r="K87" s="25"/>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="M88" s="20"/>
+      <c r="N88" s="20"/>
+      <c r="O88" s="20"/>
+      <c r="P88" s="20"/>
+      <c r="Q88" s="20"/>
+      <c r="R88" s="20"/>
+      <c r="S88" s="20"/>
+    </row>
+    <row r="89" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="26"/>
+      <c r="B89" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C74" s="44">
-        <f>J72</f>
-        <v>171041.49224446158</v>
-      </c>
-      <c r="D74" s="45"/>
-      <c r="E74" s="9">
+      <c r="C89" s="59">
+        <f>J87</f>
+        <v>240974.86130219698</v>
+      </c>
+      <c r="D89" s="60"/>
+      <c r="E89" s="9">
         <v>100</v>
       </c>
-      <c r="F74" s="26"/>
-      <c r="G74" s="28"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="29"/>
-      <c r="J74" s="30"/>
-      <c r="K74" s="31"/>
-      <c r="M74" s="19"/>
-      <c r="N74" s="19"/>
-      <c r="O74" s="19"/>
-      <c r="P74" s="19"/>
-      <c r="Q74" s="19"/>
-      <c r="R74" s="19"/>
-      <c r="S74" s="19"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B75" s="27" t="s">
+      <c r="F89" s="26"/>
+      <c r="G89" s="28"/>
+      <c r="H89" s="26"/>
+      <c r="I89" s="29"/>
+      <c r="J89" s="30"/>
+      <c r="K89" s="31"/>
+      <c r="M89" s="19"/>
+      <c r="N89" s="19"/>
+      <c r="O89" s="19"/>
+      <c r="P89" s="19"/>
+      <c r="Q89" s="19"/>
+      <c r="R89" s="19"/>
+      <c r="S89" s="19"/>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B90" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C75" s="48">
+      <c r="C90" s="63">
         <v>200000</v>
       </c>
-      <c r="D75" s="49"/>
-      <c r="E75" s="9"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B76" s="27" t="s">
+      <c r="D90" s="64"/>
+      <c r="E90" s="9"/>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B91" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C76" s="48">
-        <f>C75-C78-C79</f>
+      <c r="C91" s="63">
+        <f>C90-C93-C94</f>
         <v>190000</v>
       </c>
-      <c r="D76" s="49"/>
-      <c r="E76" s="9">
-        <f>C76/C74*100</f>
-        <v>111.08415712863516</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B77" s="27" t="s">
+      <c r="D91" s="64"/>
+      <c r="E91" s="9">
+        <f>C91/C89*100</f>
+        <v>78.846398737720847</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B92" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C77" s="50">
-        <f>C74-C76</f>
-        <v>-18958.50775553842</v>
-      </c>
-      <c r="D77" s="50"/>
-      <c r="E77" s="9">
-        <f>100-E76</f>
-        <v>-11.084157128635155</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B78" s="27" t="s">
+      <c r="C92" s="65">
+        <f>C89-C91</f>
+        <v>50974.86130219698</v>
+      </c>
+      <c r="D92" s="65"/>
+      <c r="E92" s="9">
+        <f>100-E91</f>
+        <v>21.153601262279153</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B93" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C78" s="44">
-        <f>C75*0.03</f>
+      <c r="C93" s="59">
+        <f>C90*0.03</f>
         <v>6000</v>
       </c>
-      <c r="D78" s="45"/>
-      <c r="E78" s="9">
+      <c r="D93" s="60"/>
+      <c r="E93" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B79" s="27" t="s">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B94" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C79" s="44">
-        <f>C75*0.02</f>
+      <c r="C94" s="59">
+        <f>C90*0.02</f>
         <v>4000</v>
       </c>
-      <c r="D79" s="45"/>
-      <c r="E79" s="9">
+      <c r="D94" s="60"/>
+      <c r="E94" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C92:D92"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -4390,14 +5205,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -4405,7 +5212,1133 @@
     <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="53" max="10" man="1"/>
+    <brk id="66" max="10" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.33203125" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+    </row>
+    <row r="2" spans="1:13" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="A2" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+    </row>
+    <row r="3" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+    </row>
+    <row r="4" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+    </row>
+    <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+    </row>
+    <row r="6" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="70"/>
+      <c r="C6" s="71">
+        <f>F42</f>
+        <v>234835.07491669987</v>
+      </c>
+      <c r="D6" s="72"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71">
+        <f>I42</f>
+        <v>240974.86130219698</v>
+      </c>
+      <c r="K6" s="72"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="I7" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="76"/>
+      <c r="K7" s="76"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="I8" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="77"/>
+      <c r="K8" s="77"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="78" t="str">
+        <f>[4]estimate!A7</f>
+        <v>Location:- Shankharapur Municipality 1</v>
+      </c>
+      <c r="B9" s="78"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="I9" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="79" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="79" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" s="81" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="79"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="79"/>
+      <c r="D12" s="82" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="82" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="82" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="79"/>
+      <c r="K12" s="81"/>
+    </row>
+    <row r="13" spans="1:13" s="35" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="83">
+        <f>estimate!A9</f>
+        <v>1</v>
+      </c>
+      <c r="B13" s="36" t="str">
+        <f>estimate!B9</f>
+        <v>sfnf] kmnfd] kfO{ksf] 6«; agfO{ h8fg ug]{ sfd</v>
+      </c>
+      <c r="C13" s="84" t="str">
+        <f>estimate!H17</f>
+        <v>Kg</v>
+      </c>
+      <c r="D13" s="84">
+        <f>estimate!G17</f>
+        <v>506.57726302956416</v>
+      </c>
+      <c r="E13" s="84">
+        <f>estimate!I17</f>
+        <v>182.51</v>
+      </c>
+      <c r="F13" s="84">
+        <f>D13*E13</f>
+        <v>92455.416275525757</v>
+      </c>
+      <c r="G13" s="84">
+        <f>V!G28</f>
+        <v>495.88546019506242</v>
+      </c>
+      <c r="H13" s="84">
+        <f>V!I28</f>
+        <v>182.51</v>
+      </c>
+      <c r="I13" s="84">
+        <f>G13*H13</f>
+        <v>90504.055340200837</v>
+      </c>
+      <c r="J13" s="85">
+        <f>I13-F13</f>
+        <v>-1951.3609353249194</v>
+      </c>
+      <c r="K13" s="86"/>
+      <c r="M13" s="35">
+        <f>1.25*F13</f>
+        <v>115569.2703444072</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="83"/>
+      <c r="B14" s="87" t="str">
+        <f>estimate!B18</f>
+        <v>-VAT 13% for materials</v>
+      </c>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84">
+        <f>estimate!J18</f>
+        <v>6506.9929675418325</v>
+      </c>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84">
+        <f>V!J29</f>
+        <v>6369.6565907799195</v>
+      </c>
+      <c r="J14" s="85">
+        <f>I14-F14</f>
+        <v>-137.33637676191302</v>
+      </c>
+      <c r="K14" s="86"/>
+      <c r="M14" s="35">
+        <f t="shared" ref="M14:M38" si="0">1.25*F14</f>
+        <v>8133.7412094272904</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="88"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="86"/>
+    </row>
+    <row r="16" spans="1:13" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A16" s="83">
+        <f>estimate!A20</f>
+        <v>2</v>
+      </c>
+      <c r="B16" s="36" t="str">
+        <f>estimate!B20</f>
+        <v>).#^ lblv ).$ dL.dL.afSnf] sf]?u]6]8 /+lug ss{6 kftfsf] 5fgf 5fpg] sfd</v>
+      </c>
+      <c r="C16" s="84" t="str">
+        <f>estimate!H23</f>
+        <v>sqm</v>
+      </c>
+      <c r="D16" s="84">
+        <f>estimate!G23</f>
+        <v>51.92773108978286</v>
+      </c>
+      <c r="E16" s="84">
+        <f>estimate!I23</f>
+        <v>1074.98</v>
+      </c>
+      <c r="F16" s="84">
+        <f>D16*E16</f>
+        <v>55821.27236689478</v>
+      </c>
+      <c r="G16" s="84">
+        <f>V!G36</f>
+        <v>53.456394314851664</v>
+      </c>
+      <c r="H16" s="84">
+        <f>V!I36</f>
+        <v>1074.98</v>
+      </c>
+      <c r="I16" s="84">
+        <f>G16*H16</f>
+        <v>57464.554760579245</v>
+      </c>
+      <c r="J16" s="85">
+        <f>I16-F16</f>
+        <v>1643.2823936844652</v>
+      </c>
+      <c r="K16" s="86"/>
+      <c r="M16" s="35">
+        <f t="shared" si="0"/>
+        <v>69776.590458618477</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="83"/>
+      <c r="B17" s="87" t="str">
+        <f>estimate!B24</f>
+        <v>-13% VAT for sheet</v>
+      </c>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84">
+        <f>estimate!J24</f>
+        <v>4505.7993447444915</v>
+      </c>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="84">
+        <f>V!J37</f>
+        <v>4638.4423394083815</v>
+      </c>
+      <c r="J17" s="85">
+        <f t="shared" ref="J17:J20" si="1">I17-F17</f>
+        <v>132.64299466389002</v>
+      </c>
+      <c r="K17" s="86"/>
+      <c r="M17" s="35">
+        <f t="shared" si="0"/>
+        <v>5632.2491809306139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="83"/>
+      <c r="B18" s="87" t="str">
+        <f>estimate!B25</f>
+        <v>-13% VAT for nut bolt</v>
+      </c>
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84">
+        <f>estimate!J25</f>
+        <v>691.09319114114771</v>
+      </c>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="84">
+        <f>V!J38</f>
+        <v>711.43778783778214</v>
+      </c>
+      <c r="J18" s="85">
+        <f t="shared" si="1"/>
+        <v>20.344596696634426</v>
+      </c>
+      <c r="K18" s="86"/>
+      <c r="M18" s="35">
+        <f t="shared" si="0"/>
+        <v>863.86648892643461</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="83"/>
+      <c r="B19" s="87" t="str">
+        <f>estimate!B26</f>
+        <v>-13% VAT for j-hook</v>
+      </c>
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84">
+        <f>estimate!J26</f>
+        <v>235.06281815605274</v>
+      </c>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84">
+        <f>V!J39</f>
+        <v>241.98266383686845</v>
+      </c>
+      <c r="J19" s="85">
+        <f t="shared" si="1"/>
+        <v>6.9198456808157118</v>
+      </c>
+      <c r="K19" s="86"/>
+      <c r="M19" s="35">
+        <f t="shared" si="0"/>
+        <v>293.82852269506594</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="83"/>
+      <c r="B20" s="87" t="str">
+        <f>estimate!B27</f>
+        <v>-13% VAT for bitumen washer</v>
+      </c>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84">
+        <f>estimate!J27</f>
+        <v>111.38498318758425</v>
+      </c>
+      <c r="G20" s="84"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="84">
+        <f>V!J40</f>
+        <v>114.66396580535684</v>
+      </c>
+      <c r="J20" s="85">
+        <f t="shared" si="1"/>
+        <v>3.2789826177725843</v>
+      </c>
+      <c r="K20" s="86"/>
+      <c r="M20" s="35">
+        <f t="shared" si="0"/>
+        <v>139.23122898448031</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="88"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="84"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="84"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="85"/>
+      <c r="K21" s="86"/>
+    </row>
+    <row r="22" spans="1:13" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A22" s="83">
+        <f>estimate!A29</f>
+        <v>3</v>
+      </c>
+      <c r="B22" s="36" t="str">
+        <f>estimate!B29</f>
+        <v>g/d k|sf/sf] Sn] / l;N6L df6f]df ;j} lsl;dsf] vGg] sfd</v>
+      </c>
+      <c r="C22" s="84" t="str">
+        <f>estimate!H32</f>
+        <v>cum</v>
+      </c>
+      <c r="D22" s="84">
+        <f>estimate!G32</f>
+        <v>5.6780152392563235</v>
+      </c>
+      <c r="E22" s="84">
+        <f>estimate!I32</f>
+        <v>674.12</v>
+      </c>
+      <c r="F22" s="84">
+        <f>D22*E22</f>
+        <v>3827.6636330874726</v>
+      </c>
+      <c r="G22" s="84">
+        <f>V!G49</f>
+        <v>5.9193849876000471</v>
+      </c>
+      <c r="H22" s="84">
+        <f>V!I49</f>
+        <v>674.12</v>
+      </c>
+      <c r="I22" s="84">
+        <f>G22*H22</f>
+        <v>3990.3758078409437</v>
+      </c>
+      <c r="J22" s="85">
+        <f>I22-F22</f>
+        <v>162.71217475347112</v>
+      </c>
+      <c r="K22" s="86"/>
+      <c r="M22" s="35">
+        <f t="shared" si="0"/>
+        <v>4784.5795413593405</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="88"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="84"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="86"/>
+    </row>
+    <row r="24" spans="1:13" s="35" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="83">
+        <f>estimate!A34</f>
+        <v>4</v>
+      </c>
+      <c r="B24" s="36" t="str">
+        <f>estimate!B34</f>
+        <v>husf] vf8ndf 9'+uf eg]{ / n]en ug]{ sfddf</v>
+      </c>
+      <c r="C24" s="84" t="str">
+        <f>estimate!H38</f>
+        <v>cum</v>
+      </c>
+      <c r="D24" s="84">
+        <f>estimate!G38</f>
+        <v>2.6789565844223686</v>
+      </c>
+      <c r="E24" s="84">
+        <f>estimate!I38</f>
+        <v>4495.6400000000003</v>
+      </c>
+      <c r="F24" s="84">
+        <f>D24*E24</f>
+        <v>12043.624379192579</v>
+      </c>
+      <c r="G24" s="84">
+        <f>V!G58</f>
+        <v>2.9002499999999998</v>
+      </c>
+      <c r="H24" s="84">
+        <f>V!I58</f>
+        <v>4495.6400000000003</v>
+      </c>
+      <c r="I24" s="84">
+        <f>G24*H24</f>
+        <v>13038.47991</v>
+      </c>
+      <c r="J24" s="85">
+        <f>I24-F24</f>
+        <v>994.85553080742102</v>
+      </c>
+      <c r="K24" s="86"/>
+      <c r="M24" s="35">
+        <f t="shared" si="0"/>
+        <v>15054.530473990724</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="83"/>
+      <c r="B25" s="87" t="str">
+        <f>estimate!B39</f>
+        <v>-13% VAT for block stone</v>
+      </c>
+      <c r="C25" s="84"/>
+      <c r="D25" s="84"/>
+      <c r="E25" s="84"/>
+      <c r="F25" s="84">
+        <f>estimate!J39</f>
+        <v>897.69665189160207</v>
+      </c>
+      <c r="G25" s="84"/>
+      <c r="H25" s="84"/>
+      <c r="I25" s="84">
+        <f>V!J59</f>
+        <v>971.85028297500003</v>
+      </c>
+      <c r="J25" s="85">
+        <f>I25-F25</f>
+        <v>74.153631083397954</v>
+      </c>
+      <c r="K25" s="86"/>
+      <c r="M25" s="35">
+        <f t="shared" si="0"/>
+        <v>1122.1208148645026</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="83"/>
+      <c r="B26" s="87" t="str">
+        <f>estimate!B40</f>
+        <v>-13% VAT for bond stone</v>
+      </c>
+      <c r="C26" s="84"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="84">
+        <f>estimate!J40</f>
+        <v>179.53724079218455</v>
+      </c>
+      <c r="G26" s="84"/>
+      <c r="H26" s="84"/>
+      <c r="I26" s="84">
+        <f>V!J60</f>
+        <v>194.36779439999998</v>
+      </c>
+      <c r="J26" s="85">
+        <f t="shared" ref="J26" si="2">I26-F26</f>
+        <v>14.830553607815432</v>
+      </c>
+      <c r="K26" s="86"/>
+      <c r="M26" s="35">
+        <f t="shared" si="0"/>
+        <v>224.42155099023068</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="88"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="86"/>
+    </row>
+    <row r="28" spans="1:13" s="35" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A28" s="83">
+        <f>estimate!A42</f>
+        <v>5</v>
+      </c>
+      <c r="B28" s="36" t="str">
+        <f>estimate!B42</f>
+        <v>hu leQf kvf{ndf l;d]G6 s+lqm6 ug]{ sfd -lk=;L=;L= !M@M$_</v>
+      </c>
+      <c r="C28" s="84" t="str">
+        <f>estimate!H47</f>
+        <v>cum</v>
+      </c>
+      <c r="D28" s="84">
+        <f>estimate!G47</f>
+        <v>2.0772289044985861</v>
+      </c>
+      <c r="E28" s="84">
+        <f>estimate!I47</f>
+        <v>13351.1</v>
+      </c>
+      <c r="F28" s="84">
+        <f>D28*E28</f>
+        <v>27733.290826851073</v>
+      </c>
+      <c r="G28" s="84">
+        <f>V!G69</f>
+        <v>2.3494999999999999</v>
+      </c>
+      <c r="H28" s="84">
+        <f>V!I69</f>
+        <v>13351.1</v>
+      </c>
+      <c r="I28" s="84">
+        <f>G28*H28</f>
+        <v>31368.409449999999</v>
+      </c>
+      <c r="J28" s="85">
+        <f>I28-F28</f>
+        <v>3635.1186231489264</v>
+      </c>
+      <c r="K28" s="86"/>
+      <c r="M28" s="35">
+        <f t="shared" si="0"/>
+        <v>34666.613533563839</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="83"/>
+      <c r="B29" s="87" t="str">
+        <f>estimate!B48</f>
+        <v>-13% VAT for cement</v>
+      </c>
+      <c r="C29" s="84"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="84"/>
+      <c r="F29" s="84">
+        <f>estimate!J48</f>
+        <v>1126.0441859480768</v>
+      </c>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84">
+        <f>V!J70</f>
+        <v>1273.6395152</v>
+      </c>
+      <c r="J29" s="85">
+        <f>I29-F29</f>
+        <v>147.5953292519232</v>
+      </c>
+      <c r="K29" s="86"/>
+      <c r="M29" s="35">
+        <f t="shared" si="0"/>
+        <v>1407.5552324350961</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="83"/>
+      <c r="B30" s="87" t="str">
+        <f>estimate!B49</f>
+        <v>-13% VAT for sand</v>
+      </c>
+      <c r="C30" s="84"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84">
+        <f>estimate!J49</f>
+        <v>381.87942358614367</v>
+      </c>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84">
+        <f>V!J71</f>
+        <v>431.93395960000004</v>
+      </c>
+      <c r="J30" s="85">
+        <f t="shared" ref="J30:J32" si="3">I30-F30</f>
+        <v>50.054536013856364</v>
+      </c>
+      <c r="K30" s="86"/>
+      <c r="M30" s="35">
+        <f t="shared" si="0"/>
+        <v>477.34927948267961</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="83"/>
+      <c r="B31" s="87" t="str">
+        <f>estimate!B50</f>
+        <v>-13% VAT for aggregate</v>
+      </c>
+      <c r="C31" s="84"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
+      <c r="F31" s="84">
+        <f>estimate!J50</f>
+        <v>739.91703697512401</v>
+      </c>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84">
+        <f>V!J72</f>
+        <v>836.90106305000006</v>
+      </c>
+      <c r="J31" s="85">
+        <f t="shared" si="3"/>
+        <v>96.984026074876056</v>
+      </c>
+      <c r="K31" s="86"/>
+      <c r="M31" s="35">
+        <f t="shared" si="0"/>
+        <v>924.89629621890504</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="83"/>
+      <c r="B32" s="87" t="str">
+        <f>estimate!B51</f>
+        <v>-13% VAT for water</v>
+      </c>
+      <c r="C32" s="84"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84">
+        <f>estimate!J51</f>
+        <v>11.341669818562281</v>
+      </c>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84">
+        <f>V!J73</f>
+        <v>12.82827</v>
+      </c>
+      <c r="J32" s="85">
+        <f t="shared" si="3"/>
+        <v>1.4866001814377192</v>
+      </c>
+      <c r="K32" s="86"/>
+      <c r="M32" s="35">
+        <f t="shared" si="0"/>
+        <v>14.177087273202851</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="88"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="84"/>
+      <c r="D33" s="84"/>
+      <c r="E33" s="84"/>
+      <c r="F33" s="84"/>
+      <c r="G33" s="84"/>
+      <c r="H33" s="84"/>
+      <c r="I33" s="84"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="86"/>
+    </row>
+    <row r="34" spans="1:13" s="35" customFormat="1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A34" s="83">
+        <f>estimate!A53</f>
+        <v>6</v>
+      </c>
+      <c r="B34" s="36" t="str">
+        <f>estimate!B53</f>
+        <v>9'Ëfsf] uf/f] df6f] nufpg] sfd</v>
+      </c>
+      <c r="C34" s="84" t="str">
+        <f>estimate!H55</f>
+        <v>cum</v>
+      </c>
+      <c r="D34" s="84">
+        <f>estimate!G55</f>
+        <v>3.9500152392563237</v>
+      </c>
+      <c r="E34" s="84">
+        <f>estimate!I55</f>
+        <v>6337.3</v>
+      </c>
+      <c r="F34" s="84">
+        <f>D34*E34</f>
+        <v>25032.431575739101</v>
+      </c>
+      <c r="G34" s="84">
+        <f>V!G79</f>
+        <v>4.135007619628162</v>
+      </c>
+      <c r="H34" s="84">
+        <f>V!I79</f>
+        <v>6337.3</v>
+      </c>
+      <c r="I34" s="84">
+        <f>G34*H34</f>
+        <v>26204.78378786955</v>
+      </c>
+      <c r="J34" s="85">
+        <f>I34-F34</f>
+        <v>1172.3522121304486</v>
+      </c>
+      <c r="K34" s="86"/>
+      <c r="M34" s="35">
+        <f t="shared" si="0"/>
+        <v>31290.539469673877</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="83"/>
+      <c r="B35" s="87" t="str">
+        <f>estimate!B56</f>
+        <v>-13% VAT for block stone</v>
+      </c>
+      <c r="C35" s="84"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="84"/>
+      <c r="F35" s="84">
+        <f>estimate!J56</f>
+        <v>1323.6181115513564</v>
+      </c>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="84">
+        <f>V!J80</f>
+        <v>1385.6075597756783</v>
+      </c>
+      <c r="J35" s="85">
+        <f>I35-F35</f>
+        <v>61.989448224321904</v>
+      </c>
+      <c r="K35" s="86"/>
+      <c r="M35" s="35">
+        <f t="shared" si="0"/>
+        <v>1654.5226394391955</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="83"/>
+      <c r="B36" s="87" t="str">
+        <f>estimate!B57</f>
+        <v>-13% VAT for bond stone</v>
+      </c>
+      <c r="C36" s="84"/>
+      <c r="D36" s="84"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="84">
+        <f>estimate!J57</f>
+        <v>132.3602706491923</v>
+      </c>
+      <c r="G36" s="84"/>
+      <c r="H36" s="84"/>
+      <c r="I36" s="84">
+        <f>V!J81</f>
+        <v>138.55914332459616</v>
+      </c>
+      <c r="J36" s="85">
+        <f t="shared" ref="J36:J38" si="4">I36-F36</f>
+        <v>6.1988726754038623</v>
+      </c>
+      <c r="K36" s="86"/>
+      <c r="M36" s="35">
+        <f t="shared" si="0"/>
+        <v>165.45033831149038</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="88"/>
+      <c r="B37" s="87" t="str">
+        <f>estimate!B58</f>
+        <v>-13% VAT for stone</v>
+      </c>
+      <c r="C37" s="84"/>
+      <c r="D37" s="84"/>
+      <c r="E37" s="84"/>
+      <c r="F37" s="84">
+        <f>estimate!J58</f>
+        <v>68.583324596159699</v>
+      </c>
+      <c r="G37" s="84"/>
+      <c r="H37" s="84"/>
+      <c r="I37" s="84">
+        <f>V!J82</f>
+        <v>71.795310298079855</v>
+      </c>
+      <c r="J37" s="85">
+        <f t="shared" si="4"/>
+        <v>3.2119857019201561</v>
+      </c>
+      <c r="K37" s="86"/>
+      <c r="M37" s="35">
+        <f t="shared" si="0"/>
+        <v>85.72915574519962</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="83"/>
+      <c r="B38" s="87" t="str">
+        <f>estimate!B59</f>
+        <v>-13% VAT for water</v>
+      </c>
+      <c r="C38" s="84"/>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+      <c r="F38" s="84">
+        <f>estimate!J59</f>
+        <v>10.064638829625114</v>
+      </c>
+      <c r="G38" s="84"/>
+      <c r="H38" s="84"/>
+      <c r="I38" s="84">
+        <f>V!J83</f>
+        <v>10.535999414812558</v>
+      </c>
+      <c r="J38" s="85">
+        <f t="shared" si="4"/>
+        <v>0.47136058518744406</v>
+      </c>
+      <c r="K38" s="86"/>
+      <c r="M38" s="35">
+        <f t="shared" si="0"/>
+        <v>12.580798537031392</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="88"/>
+      <c r="B39" s="89"/>
+      <c r="C39" s="84"/>
+      <c r="D39" s="84"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
+      <c r="J39" s="85"/>
+      <c r="K39" s="86"/>
+      <c r="M39" s="90"/>
+    </row>
+    <row r="40" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="83">
+        <f>estimate!A61</f>
+        <v>7</v>
+      </c>
+      <c r="B40" s="91" t="str">
+        <f>estimate!B61</f>
+        <v>Information board (सुचना पाटि)</v>
+      </c>
+      <c r="C40" s="84" t="str">
+        <f>estimate!H61</f>
+        <v>no.</v>
+      </c>
+      <c r="D40" s="84">
+        <f>estimate!G61</f>
+        <v>1</v>
+      </c>
+      <c r="E40" s="84">
+        <f>estimate!I61</f>
+        <v>1000</v>
+      </c>
+      <c r="F40" s="84">
+        <f>D40*E40</f>
+        <v>1000</v>
+      </c>
+      <c r="G40" s="84">
+        <f>V!G85</f>
+        <v>1</v>
+      </c>
+      <c r="H40" s="84">
+        <f>V!I85</f>
+        <v>1000</v>
+      </c>
+      <c r="I40" s="84">
+        <f>G40*H40</f>
+        <v>1000</v>
+      </c>
+      <c r="J40" s="85">
+        <f>I40-F40</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="86"/>
+    </row>
+    <row r="41" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="89"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="84"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="84"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="84"/>
+      <c r="J41" s="85"/>
+      <c r="K41" s="86"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="92"/>
+      <c r="B42" s="93" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="93"/>
+      <c r="D42" s="94"/>
+      <c r="E42" s="94"/>
+      <c r="F42" s="94">
+        <f>SUM(F13:F40)</f>
+        <v>234835.07491669987</v>
+      </c>
+      <c r="G42" s="94"/>
+      <c r="H42" s="94"/>
+      <c r="I42" s="94">
+        <f>SUM(I13:I40)</f>
+        <v>240974.86130219698</v>
+      </c>
+      <c r="J42" s="95">
+        <f>I42-F42</f>
+        <v>6139.7863854971074</v>
+      </c>
+      <c r="K42" s="92"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J6:K6"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="80" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter xml:space="preserve">&amp;LPrepared By:
+&amp;CChecked By:
+&amp;RApproved By:
+</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/बजेट माग estimate/वडा बजेट estimate/ukhu kheti/valuation ukhu kheti.xlsx
+++ b/बजेट माग estimate/वडा बजेट estimate/ukhu kheti/valuation ukhu kheti.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BEA951-EC57-45DA-AC2A-308901476F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
     <sheet name="V" sheetId="13" r:id="rId2"/>
     <sheet name="WCR" sheetId="14" r:id="rId3"/>
+    <sheet name="M" sheetId="15" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
     <definedName name="description_103">[1]Abstract!$B$16</definedName>
     <definedName name="description_124" localSheetId="0">#REF!</definedName>
+    <definedName name="description_124" localSheetId="3">#REF!</definedName>
     <definedName name="description_124" localSheetId="1">#REF!</definedName>
     <definedName name="description_124" localSheetId="2">#REF!</definedName>
     <definedName name="description_124">#REF!</definedName>
@@ -33,33 +36,39 @@
     <definedName name="description_276">[3]Abstract!$B$40</definedName>
     <definedName name="description_3">[1]Abstract!$B$169</definedName>
     <definedName name="description_310" localSheetId="0">#REF!</definedName>
+    <definedName name="description_310" localSheetId="3">#REF!</definedName>
     <definedName name="description_310" localSheetId="1">#REF!</definedName>
-    <definedName name="description_310" localSheetId="2">[5]Abstract!$B$60</definedName>
+    <definedName name="description_310" localSheetId="2">[4]Abstract!$B$60</definedName>
     <definedName name="description_310">#REF!</definedName>
     <definedName name="description_312" localSheetId="0">#REF!</definedName>
+    <definedName name="description_312" localSheetId="3">#REF!</definedName>
     <definedName name="description_312" localSheetId="1">#REF!</definedName>
-    <definedName name="description_312" localSheetId="2">[6]Abstract!$B$61</definedName>
+    <definedName name="description_312" localSheetId="2">[5]Abstract!$B$61</definedName>
     <definedName name="description_312">#REF!</definedName>
     <definedName name="description_5">[1]Abstract!$B$171</definedName>
     <definedName name="description_6" localSheetId="0">#REF!</definedName>
+    <definedName name="description_6" localSheetId="3">#REF!</definedName>
     <definedName name="description_6" localSheetId="1">#REF!</definedName>
-    <definedName name="description_6" localSheetId="2">[5]Abstract!$B$172</definedName>
+    <definedName name="description_6" localSheetId="2">[4]Abstract!$B$172</definedName>
     <definedName name="description_6">#REF!</definedName>
     <definedName name="description_759">[1]Abstract!$B$278</definedName>
     <definedName name="description_781" localSheetId="0">#REF!</definedName>
+    <definedName name="description_781" localSheetId="3">#REF!</definedName>
     <definedName name="description_781" localSheetId="1">#REF!</definedName>
-    <definedName name="description_781" localSheetId="2">[7]Abstract!$B$299</definedName>
+    <definedName name="description_781" localSheetId="2">[6]Abstract!$B$299</definedName>
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$70</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">V!$A$1:$K$94</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">M!$A$1:$K$89</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">V!$A$1:$K$89</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">WCR!$A$1:$K$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">M!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">V!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">WCR!$1:$12</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -77,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="93">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -328,9 +337,6 @@
     <t xml:space="preserve">F.Y:2082/2083            </t>
   </si>
   <si>
-    <t xml:space="preserve">Date:2082/10/19       </t>
-  </si>
-  <si>
     <t>S.No.</t>
   </si>
   <si>
@@ -359,15 +365,24 @@
   </si>
   <si>
     <t>for tunnel</t>
+  </si>
+  <si>
+    <t>Date:2082/11/10</t>
+  </si>
+  <si>
+    <t>Detail Quantity Measurement Sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:2082/11/10       </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -507,7 +522,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -517,12 +532,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,13 +603,13 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -608,7 +617,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -632,14 +641,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -658,7 +667,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -673,7 +682,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -704,7 +713,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -713,118 +722,28 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -839,7 +758,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -850,15 +769,92 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3"/>
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="5"/>
-    <cellStyle name="Percent 2" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -874,7 +870,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -968,7 +964,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1027,7 +1023,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1091,43 +1087,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="estimate"/>
-      <sheetName val="valuation"/>
-      <sheetName val="WCR"/>
-      <sheetName val="m"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Project:-तिनघरे बाटो स्तरोन्नति</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Location:- Shankharapur Municipality 1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="12">
-          <cell r="G12">
-            <v>63.93</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1190,8 +1150,8 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1249,8 +1209,8 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1308,10 +1268,46 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="estimate"/>
+      <sheetName val="valuation"/>
+      <sheetName val="WCR"/>
+      <sheetName val="m"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>Project:-तिनघरे बाटो स्तरोन्नति</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>Location:- Shankharapur Municipality 1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="12">
+          <cell r="G12">
+            <v>63.93</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1349,9 +1345,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1386,7 +1382,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1421,7 +1417,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1594,135 +1590,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S70"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="19" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="19"/>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="19" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.109375" style="19"/>
+    <col min="9" max="9" width="9.5703125" style="19" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="19"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-    </row>
-    <row r="2" spans="1:18" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+    </row>
+    <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="57" t="s">
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="57" t="s">
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-    </row>
-    <row r="5" spans="1:18" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="58" t="s">
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-    </row>
-    <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="53" t="s">
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+    </row>
+    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-    </row>
-    <row r="7" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="61" t="s">
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+    </row>
+    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="62" t="s">
+      <c r="H7" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
-    </row>
-    <row r="8" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
@@ -1757,7 +1753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -1782,7 +1778,7 @@
       <c r="J9" s="39"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:18" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="40" t="s">
         <v>57</v>
@@ -1811,7 +1807,7 @@
       <c r="J10" s="39"/>
       <c r="K10" s="27"/>
     </row>
-    <row r="11" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="40"/>
       <c r="C11" s="41">
@@ -1838,7 +1834,7 @@
       <c r="J11" s="39"/>
       <c r="K11" s="27"/>
     </row>
-    <row r="12" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="40"/>
       <c r="C12" s="41">
@@ -1865,7 +1861,7 @@
       <c r="J12" s="39"/>
       <c r="K12" s="27"/>
     </row>
-    <row r="13" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="40"/>
       <c r="C13" s="41">
@@ -1892,7 +1888,7 @@
       <c r="J13" s="39"/>
       <c r="K13" s="27"/>
     </row>
-    <row r="14" spans="1:18" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="40" t="s">
         <v>58</v>
@@ -1929,7 +1925,7 @@
         <v>89.995608214319134</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="40"/>
       <c r="C15" s="41">
@@ -1956,7 +1952,7 @@
       <c r="J15" s="39"/>
       <c r="K15" s="27"/>
     </row>
-    <row r="16" spans="1:18" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="40" t="s">
         <v>59</v>
@@ -1985,7 +1981,7 @@
       <c r="J16" s="39"/>
       <c r="K16" s="27"/>
     </row>
-    <row r="17" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="40" t="s">
         <v>36</v>
@@ -2010,7 +2006,7 @@
       </c>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="40" t="s">
         <v>38</v>
@@ -2028,7 +2024,7 @@
       </c>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="40"/>
       <c r="C19" s="3"/>
@@ -2041,7 +2037,7 @@
       <c r="J19" s="39"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>2</v>
       </c>
@@ -2058,7 +2054,7 @@
       <c r="J20" s="39"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="40" t="s">
         <v>39</v>
@@ -2085,7 +2081,7 @@
       <c r="J21" s="39"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="40"/>
       <c r="C22" s="3">
@@ -2109,7 +2105,7 @@
       <c r="J22" s="39"/>
       <c r="K22" s="5"/>
     </row>
-    <row r="23" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="40" t="s">
         <v>36</v>
@@ -2134,7 +2130,7 @@
       </c>
       <c r="K23" s="5"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="32" t="s">
         <v>41</v>
@@ -2152,7 +2148,7 @@
       </c>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="32" t="s">
         <v>42</v>
@@ -2170,7 +2166,7 @@
       </c>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="32" t="s">
         <v>43</v>
@@ -2188,7 +2184,7 @@
       </c>
       <c r="K26" s="17"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="32" t="s">
         <v>44</v>
@@ -2206,7 +2202,7 @@
       </c>
       <c r="K27" s="17"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="32"/>
       <c r="C28" s="17"/>
@@ -2219,7 +2215,7 @@
       <c r="J28" s="18"/>
       <c r="K28" s="17"/>
     </row>
-    <row r="29" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>3</v>
       </c>
@@ -2236,7 +2232,7 @@
       <c r="J29" s="18"/>
       <c r="K29" s="17"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="32" t="s">
         <v>45</v>
@@ -2264,7 +2260,7 @@
       <c r="J30" s="18"/>
       <c r="K30" s="17"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
       <c r="B31" s="32" t="s">
         <v>47</v>
@@ -2291,7 +2287,7 @@
       <c r="J31" s="18"/>
       <c r="K31" s="17"/>
     </row>
-    <row r="32" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="40" t="s">
         <v>36</v>
@@ -2316,7 +2312,7 @@
       </c>
       <c r="K32" s="5"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="16"/>
       <c r="B33" s="32"/>
       <c r="C33" s="17"/>
@@ -2329,7 +2325,7 @@
       <c r="J33" s="18"/>
       <c r="K33" s="17"/>
     </row>
-    <row r="34" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>4</v>
       </c>
@@ -2346,7 +2342,7 @@
       <c r="J34" s="18"/>
       <c r="K34" s="17"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
       <c r="B35" s="32" t="str">
         <f>B31</f>
@@ -2376,7 +2372,7 @@
       <c r="J35" s="18"/>
       <c r="K35" s="17"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="16"/>
       <c r="B36" s="32" t="s">
         <v>55</v>
@@ -2405,7 +2401,7 @@
       <c r="J36" s="18"/>
       <c r="K36" s="17"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="32" t="s">
         <v>56</v>
@@ -2434,7 +2430,7 @@
       <c r="J37" s="18"/>
       <c r="K37" s="17"/>
     </row>
-    <row r="38" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="40" t="s">
         <v>36</v>
@@ -2459,7 +2455,7 @@
       </c>
       <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" s="32" t="s">
         <v>51</v>
@@ -2477,7 +2473,7 @@
       </c>
       <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
       <c r="B40" s="32" t="s">
         <v>52</v>
@@ -2495,7 +2491,7 @@
       </c>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
       <c r="B41" s="42"/>
       <c r="C41" s="17"/>
@@ -2508,7 +2504,7 @@
       <c r="J41" s="18"/>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>5</v>
       </c>
@@ -2525,7 +2521,7 @@
       <c r="J42" s="17"/>
       <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="32" t="str">
         <f>B35</f>
@@ -2553,7 +2549,7 @@
       <c r="J43" s="18"/>
       <c r="K43" s="17"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
       <c r="B44" s="32"/>
       <c r="C44" s="17">
@@ -2578,7 +2574,7 @@
       <c r="J44" s="18"/>
       <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="32" t="str">
         <f>B36</f>
@@ -2608,7 +2604,7 @@
       <c r="J45" s="18"/>
       <c r="K45" s="17"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" s="32" t="s">
         <v>56</v>
@@ -2637,7 +2633,7 @@
       <c r="J46" s="18"/>
       <c r="K46" s="17"/>
     </row>
-    <row r="47" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="40" t="s">
         <v>36</v>
@@ -2662,7 +2658,7 @@
       </c>
       <c r="K47" s="5"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
       <c r="B48" s="32" t="s">
         <v>26</v>
@@ -2680,7 +2676,7 @@
       </c>
       <c r="K48" s="17"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="16"/>
       <c r="B49" s="32" t="s">
         <v>27</v>
@@ -2698,7 +2694,7 @@
       </c>
       <c r="K49" s="17"/>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
       <c r="B50" s="32" t="s">
         <v>28</v>
@@ -2716,7 +2712,7 @@
       </c>
       <c r="K50" s="17"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="16"/>
       <c r="B51" s="32" t="s">
         <v>30</v>
@@ -2734,7 +2730,7 @@
       </c>
       <c r="K51" s="17"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
       <c r="B52" s="32"/>
       <c r="C52" s="17"/>
@@ -2747,7 +2743,7 @@
       <c r="J52" s="18"/>
       <c r="K52" s="17"/>
     </row>
-    <row r="53" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <v>6</v>
       </c>
@@ -2764,7 +2760,7 @@
       <c r="J53" s="17"/>
       <c r="K53" s="17"/>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
       <c r="B54" s="32" t="s">
         <v>45</v>
@@ -2805,7 +2801,7 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="34" t="s">
         <v>16</v>
@@ -2830,7 +2826,7 @@
       </c>
       <c r="K55" s="5"/>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
       <c r="B56" s="32" t="s">
         <v>51</v>
@@ -2848,7 +2844,7 @@
       </c>
       <c r="K56" s="17"/>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="16"/>
       <c r="B57" s="32" t="s">
         <v>52</v>
@@ -2866,7 +2862,7 @@
       </c>
       <c r="K57" s="17"/>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="16"/>
       <c r="B58" s="32" t="s">
         <v>29</v>
@@ -2884,7 +2880,7 @@
       </c>
       <c r="K58" s="17"/>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="16"/>
       <c r="B59" s="32" t="s">
         <v>30</v>
@@ -2902,7 +2898,7 @@
       </c>
       <c r="K59" s="17"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="16"/>
       <c r="B60" s="32"/>
       <c r="C60" s="17"/>
@@ -2915,7 +2911,7 @@
       <c r="J60" s="18"/>
       <c r="K60" s="17"/>
     </row>
-    <row r="61" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>7</v>
       </c>
@@ -2944,7 +2940,7 @@
       </c>
       <c r="K61" s="5"/>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="8"/>
       <c r="C62" s="3"/>
@@ -2957,7 +2953,7 @@
       <c r="J62" s="18"/>
       <c r="K62" s="5"/>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="22" t="s">
         <v>20</v>
@@ -2975,7 +2971,7 @@
       </c>
       <c r="K63" s="25"/>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="M64" s="20"/>
       <c r="N64" s="20"/>
       <c r="O64" s="20"/>
@@ -2984,16 +2980,16 @@
       <c r="R64" s="20"/>
       <c r="S64" s="20"/>
     </row>
-    <row r="65" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="26"/>
       <c r="B65" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C65" s="59">
+      <c r="C65" s="65">
         <f>J63</f>
         <v>234835.07491669987</v>
       </c>
-      <c r="D65" s="60"/>
+      <c r="D65" s="66"/>
       <c r="E65" s="9">
         <v>100</v>
       </c>
@@ -3011,66 +3007,66 @@
       <c r="R65" s="19"/>
       <c r="S65" s="19"/>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B66" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="63">
+      <c r="C66" s="68">
         <v>200000</v>
       </c>
-      <c r="D66" s="64"/>
+      <c r="D66" s="69"/>
       <c r="E66" s="9"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B67" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="63">
+      <c r="C67" s="68">
         <f>C66-C69-C70</f>
         <v>190000</v>
       </c>
-      <c r="D67" s="64"/>
+      <c r="D67" s="69"/>
       <c r="E67" s="9">
         <f>C67/C65*100</f>
         <v>80.907845673137345</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B68" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C68" s="65">
+      <c r="C68" s="70">
         <f>C65-C67</f>
         <v>44835.074916699872</v>
       </c>
-      <c r="D68" s="65"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="9">
         <f>100-E67</f>
         <v>19.092154326862655</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B69" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C69" s="59">
+      <c r="C69" s="65">
         <f>C66*0.03</f>
         <v>6000</v>
       </c>
-      <c r="D69" s="60"/>
+      <c r="D69" s="66"/>
       <c r="E69" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B70" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C70" s="59">
+      <c r="C70" s="65">
         <f>C66*0.02</f>
         <v>4000</v>
       </c>
-      <c r="D70" s="60"/>
+      <c r="D70" s="66"/>
       <c r="E70" s="9">
         <v>2</v>
       </c>
@@ -3105,135 +3101,135 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S94"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:S89"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="19" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="19"/>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="19" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.109375" style="19"/>
+    <col min="9" max="9" width="9.5703125" style="19" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="19"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="57" t="s">
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="57" t="s">
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="57"/>
-    </row>
-    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="58" t="s">
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="53" t="s">
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="61" t="s">
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="62" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H7" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
@@ -3268,7 +3264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -3293,26 +3289,26 @@
       <c r="J9" s="39"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="41">
         <v>2</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="9">
         <f>(15.5+1)/3.281</f>
         <v>5.0289545870161536</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="9">
         <v>3.54</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="9">
         <f t="shared" ref="F10" si="0">PRODUCT(C10:E10)</f>
         <v>35.604998476074371</v>
       </c>
-      <c r="G10" s="51">
+      <c r="G10" s="9">
         <f t="shared" ref="G10" si="1">F10</f>
         <v>35.604998476074371</v>
       </c>
@@ -3321,24 +3317,24 @@
       <c r="J10" s="39"/>
       <c r="K10" s="27"/>
     </row>
-    <row r="11" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="40"/>
-      <c r="C11" s="50">
+      <c r="C11" s="41">
         <v>2</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="9">
         <f>(15.5-1.5+2)/3.281</f>
         <v>4.8765620237732392</v>
       </c>
-      <c r="E11" s="51">
+      <c r="E11" s="9">
         <v>3.54</v>
       </c>
-      <c r="F11" s="51">
+      <c r="F11" s="9">
         <f t="shared" ref="F11" si="2">PRODUCT(C11:E11)</f>
         <v>34.526059128314536</v>
       </c>
-      <c r="G11" s="51">
+      <c r="G11" s="9">
         <f t="shared" ref="G11" si="3">F11</f>
         <v>34.526059128314536</v>
       </c>
@@ -3347,25 +3343,25 @@
       <c r="J11" s="39"/>
       <c r="K11" s="27"/>
     </row>
-    <row r="12" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="50">
+      <c r="C12" s="41">
         <v>2</v>
       </c>
-      <c r="D12" s="51">
+      <c r="D12" s="9">
         <v>3.9</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="9">
         <v>2.14</v>
       </c>
-      <c r="F12" s="51">
+      <c r="F12" s="9">
         <f>PRODUCT(C12:E12)</f>
         <v>16.692</v>
       </c>
-      <c r="G12" s="51">
+      <c r="G12" s="9">
         <f>F12</f>
         <v>16.692</v>
       </c>
@@ -3374,25 +3370,25 @@
       <c r="J12" s="39"/>
       <c r="K12" s="27"/>
     </row>
-    <row r="13" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="50">
+      <c r="C13" s="41">
         <v>9</v>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="9">
         <v>3.09</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="9">
         <v>2.14</v>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="9">
         <f t="shared" ref="F13" si="4">PRODUCT(C13:E13)</f>
         <v>59.513399999999997</v>
       </c>
-      <c r="G13" s="51">
+      <c r="G13" s="9">
         <f t="shared" ref="G13" si="5">F13</f>
         <v>59.513399999999997</v>
       </c>
@@ -3401,25 +3397,25 @@
       <c r="J13" s="39"/>
       <c r="K13" s="27"/>
     </row>
-    <row r="14" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="50">
+      <c r="C14" s="41">
         <v>1</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="9">
         <v>3.9</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="9">
         <v>2.35</v>
       </c>
-      <c r="F14" s="51">
+      <c r="F14" s="9">
         <f t="shared" ref="F14" si="6">PRODUCT(C14:E14)</f>
         <v>9.1650000000000009</v>
       </c>
-      <c r="G14" s="51">
+      <c r="G14" s="9">
         <f t="shared" ref="G14" si="7">F14</f>
         <v>9.1650000000000009</v>
       </c>
@@ -3428,26 +3424,26 @@
       <c r="J14" s="39"/>
       <c r="K14" s="27"/>
     </row>
-    <row r="15" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="50">
+      <c r="C15" s="41">
         <v>3</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="9">
         <f>(7+1)/3.281</f>
         <v>2.4382810118866196</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="9">
         <v>3.54</v>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="9">
         <f t="shared" ref="F15" si="8">PRODUCT(C15:E15)</f>
         <v>25.8945443462359</v>
       </c>
-      <c r="G15" s="51">
+      <c r="G15" s="9">
         <f t="shared" ref="G15" si="9">F15</f>
         <v>25.8945443462359</v>
       </c>
@@ -3456,23 +3452,23 @@
       <c r="J15" s="39"/>
       <c r="K15" s="27"/>
     </row>
-    <row r="16" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="40"/>
-      <c r="C16" s="50">
+      <c r="C16" s="41">
         <v>3</v>
       </c>
-      <c r="D16" s="51">
+      <c r="D16" s="9">
         <v>2.6</v>
       </c>
-      <c r="E16" s="51">
+      <c r="E16" s="9">
         <v>3.54</v>
       </c>
-      <c r="F16" s="51">
+      <c r="F16" s="9">
         <f t="shared" ref="F16:F17" si="10">PRODUCT(C16:E16)</f>
         <v>27.612000000000002</v>
       </c>
-      <c r="G16" s="51">
+      <c r="G16" s="9">
         <f t="shared" ref="G16:G17" si="11">F16</f>
         <v>27.612000000000002</v>
       </c>
@@ -3481,25 +3477,25 @@
       <c r="J16" s="39"/>
       <c r="K16" s="27"/>
     </row>
-    <row r="17" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="50">
+      <c r="C17" s="41">
         <v>5</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="9">
         <v>3.09</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="9">
         <v>1.39</v>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="9">
         <f t="shared" si="10"/>
         <v>21.475499999999997</v>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="9">
         <f t="shared" si="11"/>
         <v>21.475499999999997</v>
       </c>
@@ -3508,26 +3504,26 @@
       <c r="J17" s="39"/>
       <c r="K17" s="27"/>
     </row>
-    <row r="18" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="50">
+      <c r="C18" s="41">
         <v>5</v>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="9">
         <f>1.8+1.9</f>
         <v>3.7</v>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="9">
         <v>1.39</v>
       </c>
-      <c r="F18" s="51">
+      <c r="F18" s="9">
         <f t="shared" ref="F18" si="12">PRODUCT(C18:E18)</f>
         <v>25.715</v>
       </c>
-      <c r="G18" s="51">
+      <c r="G18" s="9">
         <f t="shared" ref="G18" si="13">F18</f>
         <v>25.715</v>
       </c>
@@ -3536,26 +3532,26 @@
       <c r="J18" s="39"/>
       <c r="K18" s="27"/>
     </row>
-    <row r="19" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="50">
+      <c r="C19" s="41">
         <v>3</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="9">
         <f>13/3.281</f>
         <v>3.9622066443157573</v>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="9">
         <v>1.39</v>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="9">
         <f t="shared" ref="F19:F20" si="14">PRODUCT(C19:E19)</f>
         <v>16.522401706796707</v>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="9">
         <f t="shared" ref="G19:G20" si="15">F19</f>
         <v>16.522401706796707</v>
       </c>
@@ -3564,26 +3560,26 @@
       <c r="J19" s="39"/>
       <c r="K19" s="27"/>
     </row>
-    <row r="20" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="50">
+      <c r="C20" s="41">
         <v>3</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="9">
         <f>(13)/3.281</f>
         <v>3.9622066443157573</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="9">
         <v>3.54</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="9">
         <f t="shared" si="14"/>
         <v>42.078634562633347</v>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="9">
         <f t="shared" si="15"/>
         <v>42.078634562633347</v>
       </c>
@@ -3592,24 +3588,24 @@
       <c r="J20" s="39"/>
       <c r="K20" s="27"/>
     </row>
-    <row r="21" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="40"/>
-      <c r="C21" s="50">
+      <c r="C21" s="41">
         <v>3</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="9">
         <f>(9)/3.281</f>
         <v>2.7430661383724475</v>
       </c>
-      <c r="E21" s="51">
+      <c r="E21" s="9">
         <v>3.54</v>
       </c>
-      <c r="F21" s="51">
+      <c r="F21" s="9">
         <f t="shared" ref="F21:F24" si="16">PRODUCT(C21:E21)</f>
         <v>29.131362389515388</v>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="9">
         <f t="shared" ref="G21:G24" si="17">F21</f>
         <v>29.131362389515388</v>
       </c>
@@ -3618,26 +3614,26 @@
       <c r="J21" s="39"/>
       <c r="K21" s="27"/>
     </row>
-    <row r="22" spans="1:11" s="35" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="50">
+      <c r="C22" s="41">
         <v>5</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="9">
         <f>3.8+7-11.33/3.281+0.6</f>
         <v>7.9467845169155744</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="9">
         <v>1.39</v>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="9">
         <f t="shared" si="16"/>
         <v>55.230152392563234</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="9">
         <f t="shared" si="17"/>
         <v>55.230152392563234</v>
       </c>
@@ -3646,26 +3642,26 @@
       <c r="J22" s="39"/>
       <c r="K22" s="27"/>
     </row>
-    <row r="23" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="50">
+        <v>87</v>
+      </c>
+      <c r="C23" s="41">
         <v>3</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="9">
         <f>11.25/3.281</f>
         <v>3.4288326729655592</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="9">
         <v>2.35</v>
       </c>
-      <c r="F23" s="51">
+      <c r="F23" s="9">
         <f t="shared" si="16"/>
         <v>24.173270344407193</v>
       </c>
-      <c r="G23" s="51">
+      <c r="G23" s="9">
         <f t="shared" si="17"/>
         <v>24.173270344407193</v>
       </c>
@@ -3674,26 +3670,26 @@
       <c r="J23" s="39"/>
       <c r="K23" s="27"/>
     </row>
-    <row r="24" spans="1:11" s="35" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="50">
+        <v>88</v>
+      </c>
+      <c r="C24" s="41">
         <v>3</v>
       </c>
-      <c r="D24" s="51">
+      <c r="D24" s="9">
         <f>(11.667*2)/3.281</f>
         <v>7.1118561414202981</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="9">
         <v>1.39</v>
       </c>
-      <c r="F24" s="51">
+      <c r="F24" s="9">
         <f t="shared" si="16"/>
         <v>29.656440109722642</v>
       </c>
-      <c r="G24" s="51">
+      <c r="G24" s="9">
         <f t="shared" si="17"/>
         <v>29.656440109722642</v>
       </c>
@@ -3702,24 +3698,24 @@
       <c r="J24" s="39"/>
       <c r="K24" s="27"/>
     </row>
-    <row r="25" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
       <c r="B25" s="40"/>
-      <c r="C25" s="50">
+      <c r="C25" s="41">
         <v>3</v>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="9">
         <f>11.25/3.281</f>
         <v>3.4288326729655592</v>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="9">
         <v>1.39</v>
       </c>
-      <c r="F25" s="51">
+      <c r="F25" s="9">
         <f t="shared" ref="F25" si="18">PRODUCT(C25:E25)</f>
         <v>14.298232246266382</v>
       </c>
-      <c r="G25" s="51">
+      <c r="G25" s="9">
         <f t="shared" ref="G25" si="19">F25</f>
         <v>14.298232246266382</v>
       </c>
@@ -3728,24 +3724,24 @@
       <c r="J25" s="39"/>
       <c r="K25" s="27"/>
     </row>
-    <row r="26" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="40"/>
-      <c r="C26" s="50">
+      <c r="C26" s="41">
         <v>6</v>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="9">
         <f>11.25/3.281</f>
         <v>3.4288326729655592</v>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="9">
         <v>1.39</v>
       </c>
-      <c r="F26" s="51">
+      <c r="F26" s="9">
         <f t="shared" ref="F26" si="20">PRODUCT(C26:E26)</f>
         <v>28.596464492532764</v>
       </c>
-      <c r="G26" s="51">
+      <c r="G26" s="9">
         <f t="shared" ref="G26" si="21">F26</f>
         <v>28.596464492532764</v>
       </c>
@@ -3754,49 +3750,52 @@
       <c r="J26" s="39"/>
       <c r="K26" s="27"/>
     </row>
-    <row r="27" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="16"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="27"/>
-    </row>
-    <row r="28" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="39">
+        <f>SUM(G10:G26)</f>
+        <v>495.88546019506242</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" s="6">
+        <v>182.51</v>
+      </c>
+      <c r="J27" s="39">
+        <f>G27*I27</f>
+        <v>90504.055340200837</v>
+      </c>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="40" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
-      <c r="G28" s="39">
-        <f>SUM(G10:G27)</f>
-        <v>495.88546019506242</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I28" s="6">
-        <v>182.51</v>
-      </c>
+      <c r="G28" s="39"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="6"/>
       <c r="J28" s="39">
-        <f>G28*I28</f>
-        <v>90504.055340200837</v>
+        <f>0.13*G27*(1871.42/18.94)</f>
+        <v>6369.6565907799195</v>
       </c>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="40" t="s">
-        <v>38</v>
-      </c>
+      <c r="B29" s="40"/>
       <c r="C29" s="3"/>
       <c r="D29" s="4"/>
       <c r="E29" s="5"/>
@@ -3804,15 +3803,16 @@
       <c r="G29" s="39"/>
       <c r="H29" s="7"/>
       <c r="I29" s="6"/>
-      <c r="J29" s="39">
-        <f>0.13*G28*(1871.42/18.94)</f>
-        <v>6369.6565907799195</v>
-      </c>
+      <c r="J29" s="39"/>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="40"/>
+    <row r="30" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>2</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>62</v>
+      </c>
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
       <c r="E30" s="5"/>
@@ -3823,152 +3823,147 @@
       <c r="J30" s="39"/>
       <c r="K30" s="5"/>
     </row>
-    <row r="31" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>2</v>
-      </c>
-      <c r="B31" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="5"/>
+    <row r="31" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4">
+        <f>(10+3)/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E31" s="5">
+        <f>(7)/3.281</f>
+        <v>2.1334958854007922</v>
+      </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="39"/>
+      <c r="G31" s="33">
+        <f t="shared" ref="G31:G32" si="22">PRODUCT(C31:F31)</f>
+        <v>8.4533515727553485</v>
+      </c>
       <c r="H31" s="7"/>
       <c r="I31" s="6"/>
       <c r="J31" s="39"/>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="47">
+        <v>73</v>
+      </c>
+      <c r="C32" s="3">
         <v>1</v>
       </c>
-      <c r="D32" s="48">
-        <f>(10+3)/3.281</f>
+      <c r="D32" s="4">
+        <f>(13)/3.281</f>
         <v>3.9622066443157573</v>
       </c>
-      <c r="E32" s="49">
-        <f>(7)/3.281</f>
-        <v>2.1334958854007922</v>
-      </c>
-      <c r="F32" s="49"/>
-      <c r="G32" s="45">
-        <f t="shared" ref="G32:G33" si="22">PRODUCT(C32:F32)</f>
-        <v>8.4533515727553485</v>
+      <c r="E32" s="5">
+        <f>1.75+1.75</f>
+        <v>3.5</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="33">
+        <f t="shared" si="22"/>
+        <v>13.867723255105151</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="6"/>
       <c r="J32" s="39"/>
       <c r="K32" s="5"/>
     </row>
-    <row r="33" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="47">
+      <c r="B33" s="40"/>
+      <c r="C33" s="3">
         <v>1</v>
       </c>
-      <c r="D33" s="48">
-        <f>(13)/3.281</f>
-        <v>3.9622066443157573</v>
-      </c>
-      <c r="E33" s="49">
-        <f>1.75+1.75</f>
-        <v>3.5</v>
-      </c>
-      <c r="F33" s="49"/>
-      <c r="G33" s="45">
-        <f t="shared" si="22"/>
-        <v>13.867723255105151</v>
+      <c r="D33" s="4">
+        <f>3.75+7-11.33/3.281</f>
+        <v>7.2967845169155741</v>
+      </c>
+      <c r="E33" s="5">
+        <f>14/3.281</f>
+        <v>4.2669917708015843</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="33">
+        <f t="shared" ref="G33" si="23">PRODUCT(C33:F33)</f>
+        <v>31.135319486991168</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="6"/>
       <c r="J33" s="39"/>
       <c r="K33" s="5"/>
     </row>
-    <row r="34" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
-      <c r="B34" s="40"/>
-      <c r="C34" s="47">
-        <v>0</v>
-      </c>
-      <c r="D34" s="48">
-        <f>(7)/3.281</f>
-        <v>2.1334958854007922</v>
-      </c>
-      <c r="E34" s="49">
-        <f>1.75+1.9</f>
-        <v>3.65</v>
-      </c>
-      <c r="F34" s="49"/>
-      <c r="G34" s="45">
-        <f t="shared" ref="G34:G35" si="23">PRODUCT(C34:F34)</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="39"/>
+      <c r="B34" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="39">
+        <f>SUM(G31:G33)</f>
+        <v>53.456394314851664</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I34" s="6">
+        <v>1074.98</v>
+      </c>
+      <c r="J34" s="39">
+        <f>G34*I34</f>
+        <v>57464.554760579245</v>
+      </c>
       <c r="K34" s="5"/>
     </row>
-    <row r="35" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="40"/>
-      <c r="C35" s="47">
-        <v>1</v>
-      </c>
-      <c r="D35" s="48">
-        <f>3.75+7-11.33/3.281</f>
-        <v>7.2967845169155741</v>
-      </c>
-      <c r="E35" s="49">
-        <f>14/3.281</f>
-        <v>4.2669917708015843</v>
-      </c>
-      <c r="F35" s="49"/>
-      <c r="G35" s="45">
-        <f t="shared" si="23"/>
-        <v>31.135319486991168</v>
-      </c>
-      <c r="H35" s="7"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="5"/>
-    </row>
-    <row r="36" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="39">
-        <f>SUM(G32:G35)</f>
-        <v>53.456394314851664</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I36" s="6">
-        <v>1074.98</v>
-      </c>
-      <c r="J36" s="39">
-        <f>G36*I36</f>
-        <v>57464.554760579245</v>
-      </c>
-      <c r="K36" s="5"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="16"/>
+      <c r="B35" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="18">
+        <f>0.13*G34*6674.66/10</f>
+        <v>4638.4423394083815</v>
+      </c>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="16"/>
+      <c r="B36" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="18">
+        <f>0.13*G34*1023.75/10</f>
+        <v>711.43778783778214</v>
+      </c>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -3978,15 +3973,15 @@
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
       <c r="J37" s="18">
-        <f>0.13*G36*6674.66/10</f>
-        <v>4638.4423394083815</v>
+        <f>0.13*G34*348.21/10</f>
+        <v>241.98266383686845</v>
       </c>
       <c r="K37" s="17"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
       <c r="B38" s="32" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -3996,16 +3991,14 @@
       <c r="H38" s="17"/>
       <c r="I38" s="17"/>
       <c r="J38" s="18">
-        <f>0.13*G36*1023.75/10</f>
-        <v>711.43778783778214</v>
+        <f>0.13*G34*165/10</f>
+        <v>114.66396580535684</v>
       </c>
       <c r="K38" s="17"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
-      <c r="B39" s="32" t="s">
-        <v>43</v>
-      </c>
+      <c r="B39" s="32"/>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
@@ -4013,16 +4006,15 @@
       <c r="G39" s="17"/>
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
-      <c r="J39" s="18">
-        <f>0.13*G36*348.21/10</f>
-        <v>241.98266383686845</v>
-      </c>
+      <c r="J39" s="18"/>
       <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="16"/>
-      <c r="B40" s="32" t="s">
-        <v>44</v>
+    <row r="40" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>3</v>
+      </c>
+      <c r="B40" s="43" t="s">
+        <v>49</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -4031,452 +4023,445 @@
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
-      <c r="J40" s="18">
-        <f>0.13*G36*165/10</f>
-        <v>114.66396580535684</v>
-      </c>
+      <c r="J40" s="18"/>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
+      <c r="B41" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="17">
+        <v>2</v>
+      </c>
+      <c r="D41" s="33">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E41" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F41" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="G41" s="33">
+        <f t="shared" ref="G41:G45" si="24">PRODUCT(C41:F41)</f>
+        <v>1.9750076196281618</v>
+      </c>
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
       <c r="J41" s="18"/>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="16">
-        <v>3</v>
-      </c>
-      <c r="B42" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="16"/>
+      <c r="B42" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="17">
+        <f>2*6</f>
+        <v>12</v>
+      </c>
+      <c r="D42" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E42" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F42" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="G42" s="33">
+        <f t="shared" si="24"/>
+        <v>1.0935000000000001</v>
+      </c>
       <c r="H42" s="17"/>
       <c r="I42" s="17"/>
       <c r="J42" s="18"/>
       <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="44">
-        <v>2</v>
-      </c>
-      <c r="D43" s="45">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E43" s="44">
-        <v>0.45</v>
-      </c>
-      <c r="F43" s="44">
-        <v>0.9</v>
-      </c>
-      <c r="G43" s="45">
-        <f t="shared" ref="G43:G48" si="24">PRODUCT(C43:F43)</f>
-        <v>1.9750076196281618</v>
+        <v>55</v>
+      </c>
+      <c r="C43" s="17">
+        <v>1</v>
+      </c>
+      <c r="D43" s="33">
+        <f>13/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E43" s="33">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="F43" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="G43" s="33">
+        <f t="shared" si="24"/>
+        <v>1.2076216532507642</v>
       </c>
       <c r="H43" s="17"/>
       <c r="I43" s="17"/>
       <c r="J43" s="18"/>
       <c r="K43" s="17"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="16"/>
-      <c r="B44" s="32"/>
+      <c r="B44" s="32" t="s">
+        <v>47</v>
+      </c>
       <c r="C44" s="17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D44" s="33">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E44" s="17">
-        <v>0.45</v>
+        <f>0.3</f>
+        <v>0.3</v>
+      </c>
+      <c r="E44" s="33">
+        <v>0.3</v>
       </c>
       <c r="F44" s="17">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="G44" s="33">
-        <f t="shared" ref="G44" si="25">PRODUCT(C44:F44)</f>
-        <v>0</v>
+        <f t="shared" si="24"/>
+        <v>0.16199999999999998</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="17"/>
       <c r="J44" s="18"/>
       <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="44">
-        <f>2*6</f>
-        <v>12</v>
-      </c>
-      <c r="D45" s="45">
-        <v>0.45</v>
-      </c>
-      <c r="E45" s="44">
-        <v>0.45</v>
-      </c>
-      <c r="F45" s="44">
-        <v>0.45</v>
-      </c>
-      <c r="G45" s="45">
+        <v>89</v>
+      </c>
+      <c r="C45" s="17">
+        <v>1</v>
+      </c>
+      <c r="D45" s="33">
+        <f>9/3.281</f>
+        <v>2.7430661383724475</v>
+      </c>
+      <c r="E45" s="33">
+        <v>0.6</v>
+      </c>
+      <c r="F45" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="G45" s="33">
         <f t="shared" si="24"/>
-        <v>1.0935000000000001</v>
+        <v>1.4812557147211216</v>
       </c>
       <c r="H45" s="17"/>
       <c r="I45" s="17"/>
       <c r="J45" s="18"/>
       <c r="K45" s="17"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="16"/>
-      <c r="B46" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="44">
-        <v>1</v>
-      </c>
-      <c r="D46" s="45">
-        <f>13/3.281</f>
-        <v>3.9622066443157573</v>
-      </c>
-      <c r="E46" s="45">
-        <f>10/3.281</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="F46" s="44">
-        <v>0.1</v>
-      </c>
-      <c r="G46" s="45">
-        <f t="shared" si="24"/>
-        <v>1.2076216532507642</v>
-      </c>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="18"/>
-      <c r="K46" s="17"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="39">
+        <f>SUM(G41:G45)</f>
+        <v>5.9193849876000471</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="6">
+        <v>674.12</v>
+      </c>
+      <c r="J46" s="39">
+        <f>G46*I46</f>
+        <v>3990.3758078409437</v>
+      </c>
+      <c r="K46" s="5"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
-      <c r="B47" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" s="44">
-        <v>6</v>
-      </c>
-      <c r="D47" s="45">
-        <f>0.3</f>
-        <v>0.3</v>
-      </c>
-      <c r="E47" s="45">
-        <v>0.3</v>
-      </c>
-      <c r="F47" s="44">
-        <v>0.3</v>
-      </c>
-      <c r="G47" s="45">
-        <f t="shared" si="24"/>
-        <v>0.16199999999999998</v>
-      </c>
+      <c r="B47" s="32"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
       <c r="H47" s="17"/>
       <c r="I47" s="17"/>
       <c r="J47" s="18"/>
       <c r="K47" s="17"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="16"/>
-      <c r="B48" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" s="44">
-        <v>1</v>
-      </c>
-      <c r="D48" s="45">
-        <f>9/3.281</f>
-        <v>2.7430661383724475</v>
-      </c>
-      <c r="E48" s="45">
-        <v>0.6</v>
-      </c>
-      <c r="F48" s="44">
-        <v>0.9</v>
-      </c>
-      <c r="G48" s="45">
-        <f t="shared" si="24"/>
-        <v>1.4812557147211216</v>
-      </c>
+    <row r="48" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="16">
+        <v>4</v>
+      </c>
+      <c r="B48" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
       <c r="H48" s="17"/>
       <c r="I48" s="17"/>
       <c r="J48" s="18"/>
       <c r="K48" s="17"/>
     </row>
-    <row r="49" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2"/>
-      <c r="B49" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="39">
-        <f>SUM(G43:G48)</f>
-        <v>5.9193849876000471</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I49" s="6">
-        <v>674.12</v>
-      </c>
-      <c r="J49" s="39">
-        <f>G49*I49</f>
-        <v>3990.3758078409437</v>
-      </c>
-      <c r="K49" s="5"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="16"/>
+      <c r="B49" s="32" t="str">
+        <f>B42</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C49" s="17">
+        <f>C42</f>
+        <v>12</v>
+      </c>
+      <c r="D49" s="33">
+        <f>D42</f>
+        <v>0.45</v>
+      </c>
+      <c r="E49" s="33">
+        <f>E42</f>
+        <v>0.45</v>
+      </c>
+      <c r="F49" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G49" s="33">
+        <f t="shared" ref="G49:G52" si="25">PRODUCT(C49:F49)</f>
+        <v>0.18225</v>
+      </c>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="16"/>
-      <c r="B50" s="32"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
+      <c r="B50" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="17">
+        <f t="shared" ref="C50:E52" si="26">C61</f>
+        <v>1</v>
+      </c>
+      <c r="D50" s="33">
+        <f t="shared" si="26"/>
+        <v>3.5</v>
+      </c>
+      <c r="E50" s="33">
+        <f t="shared" si="26"/>
+        <v>3.5</v>
+      </c>
+      <c r="F50" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G50" s="33">
+        <f t="shared" si="25"/>
+        <v>0.91874999999999996</v>
+      </c>
       <c r="H50" s="17"/>
       <c r="I50" s="17"/>
       <c r="J50" s="18"/>
       <c r="K50" s="17"/>
     </row>
-    <row r="51" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="16">
-        <v>4</v>
-      </c>
-      <c r="B51" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="16"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="17">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="D51" s="33">
+        <f t="shared" si="26"/>
+        <v>4.2</v>
+      </c>
+      <c r="E51" s="33">
+        <f t="shared" si="26"/>
+        <v>3.2</v>
+      </c>
+      <c r="F51" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G51" s="33">
+        <f t="shared" ref="G51" si="27">PRODUCT(C51:F51)</f>
+        <v>1.008</v>
+      </c>
       <c r="H51" s="17"/>
       <c r="I51" s="17"/>
       <c r="J51" s="18"/>
       <c r="K51" s="17"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
-      <c r="B52" s="32" t="str">
-        <f>B45</f>
-        <v>-for footing of vertical post</v>
-      </c>
-      <c r="C52" s="44">
-        <f>C45</f>
-        <v>12</v>
-      </c>
-      <c r="D52" s="45">
-        <f>D45</f>
-        <v>0.45</v>
-      </c>
-      <c r="E52" s="45">
-        <f>E45</f>
-        <v>0.45</v>
-      </c>
-      <c r="F52" s="45">
+      <c r="B52" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="17">
+        <f t="shared" si="26"/>
+        <v>-1</v>
+      </c>
+      <c r="D52" s="33">
+        <f t="shared" si="26"/>
+        <v>3</v>
+      </c>
+      <c r="E52" s="33">
+        <f t="shared" si="26"/>
+        <v>1.5</v>
+      </c>
+      <c r="F52" s="33">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G52" s="45">
-        <f t="shared" ref="G52:G55" si="26">PRODUCT(C52:F52)</f>
-        <v>0.18225</v>
+      <c r="G52" s="33">
+        <f t="shared" si="25"/>
+        <v>-0.33749999999999997</v>
       </c>
       <c r="H52" s="17"/>
       <c r="I52" s="17"/>
       <c r="J52" s="18"/>
       <c r="K52" s="17"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="16"/>
-      <c r="B53" s="52" t="s">
+      <c r="B53" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C53" s="44">
-        <f t="shared" ref="C53:E55" si="27">C65</f>
+      <c r="C53" s="17">
         <v>1</v>
       </c>
-      <c r="D53" s="45">
-        <f t="shared" si="27"/>
+      <c r="D53" s="33">
         <v>3.5</v>
       </c>
-      <c r="E53" s="45">
-        <f t="shared" si="27"/>
-        <v>3.5</v>
-      </c>
-      <c r="F53" s="45">
+      <c r="E53" s="33">
+        <v>3.65</v>
+      </c>
+      <c r="F53" s="33">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G53" s="45">
-        <f t="shared" si="26"/>
-        <v>0.91874999999999996</v>
+      <c r="G53" s="33">
+        <f t="shared" ref="G53:G54" si="28">PRODUCT(C53:F53)</f>
+        <v>0.958125</v>
       </c>
       <c r="H53" s="17"/>
       <c r="I53" s="17"/>
       <c r="J53" s="18"/>
       <c r="K53" s="17"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="16"/>
-      <c r="B54" s="52"/>
-      <c r="C54" s="44">
-        <f t="shared" si="27"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="17">
         <v>1</v>
       </c>
-      <c r="D54" s="45">
-        <f t="shared" si="27"/>
-        <v>4.2</v>
-      </c>
-      <c r="E54" s="45">
-        <f t="shared" si="27"/>
-        <v>3.2</v>
-      </c>
-      <c r="F54" s="45">
+      <c r="D54" s="33">
+        <v>3.5</v>
+      </c>
+      <c r="E54" s="33">
+        <v>0.65</v>
+      </c>
+      <c r="F54" s="33">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G54" s="45">
-        <f t="shared" ref="G54" si="28">PRODUCT(C54:F54)</f>
-        <v>1.008</v>
+      <c r="G54" s="33">
+        <f t="shared" si="28"/>
+        <v>0.170625</v>
       </c>
       <c r="H54" s="17"/>
       <c r="I54" s="17"/>
       <c r="J54" s="18"/>
       <c r="K54" s="17"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="16"/>
-      <c r="B55" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" s="44">
-        <f t="shared" si="27"/>
-        <v>-1</v>
-      </c>
-      <c r="D55" s="45">
-        <f t="shared" si="27"/>
-        <v>3</v>
-      </c>
-      <c r="E55" s="45">
-        <f t="shared" si="27"/>
-        <v>1.5</v>
-      </c>
-      <c r="F55" s="45">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G55" s="45">
-        <f t="shared" si="26"/>
-        <v>-0.33749999999999997</v>
-      </c>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="17"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="39">
+        <f>SUM(G49:G54)</f>
+        <v>2.9002499999999998</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I55" s="6">
+        <v>4495.6400000000003</v>
+      </c>
+      <c r="J55" s="39">
+        <f>G55*I55</f>
+        <v>13038.47991</v>
+      </c>
+      <c r="K55" s="5"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="16"/>
-      <c r="B56" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="C56" s="44">
-        <v>1</v>
-      </c>
-      <c r="D56" s="45">
-        <v>3.5</v>
-      </c>
-      <c r="E56" s="45">
-        <v>3.65</v>
-      </c>
-      <c r="F56" s="45">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G56" s="45">
-        <f t="shared" ref="G56:G57" si="29">PRODUCT(C56:F56)</f>
-        <v>0.958125</v>
-      </c>
+      <c r="B56" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
       <c r="H56" s="17"/>
       <c r="I56" s="17"/>
-      <c r="J56" s="18"/>
+      <c r="J56" s="18">
+        <f>0.13*G55*2577.63</f>
+        <v>971.85028297500003</v>
+      </c>
       <c r="K56" s="17"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="16"/>
-      <c r="B57" s="52"/>
-      <c r="C57" s="44">
-        <v>1</v>
-      </c>
-      <c r="D57" s="45">
-        <v>3.5</v>
-      </c>
-      <c r="E57" s="45">
-        <v>0.65</v>
-      </c>
-      <c r="F57" s="45">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G57" s="45">
-        <f t="shared" si="29"/>
-        <v>0.170625</v>
-      </c>
+      <c r="B57" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
       <c r="H57" s="17"/>
       <c r="I57" s="17"/>
-      <c r="J57" s="18"/>
+      <c r="J57" s="18">
+        <f>0.13*G55*515.52</f>
+        <v>194.36779439999998</v>
+      </c>
       <c r="K57" s="17"/>
     </row>
-    <row r="58" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="2"/>
-      <c r="B58" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C58" s="3"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="39">
-        <f>SUM(G52:G57)</f>
-        <v>2.9002499999999998</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I58" s="6">
-        <v>4495.6400000000003</v>
-      </c>
-      <c r="J58" s="39">
-        <f>G58*I58</f>
-        <v>13038.47991</v>
-      </c>
-      <c r="K58" s="5"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="16"/>
-      <c r="B59" s="32" t="s">
-        <v>51</v>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="16"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="17"/>
+    </row>
+    <row r="59" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="16">
+        <v>5</v>
+      </c>
+      <c r="B59" s="43" t="s">
+        <v>53</v>
       </c>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
@@ -4485,246 +4470,241 @@
       <c r="G59" s="17"/>
       <c r="H59" s="17"/>
       <c r="I59" s="17"/>
-      <c r="J59" s="18">
-        <f>0.13*G58*2577.63</f>
-        <v>971.85028297500003</v>
-      </c>
+      <c r="J59" s="17"/>
       <c r="K59" s="17"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="16"/>
-      <c r="B60" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
+      <c r="B60" s="32" t="str">
+        <f>B49</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C60" s="17">
+        <f>C42</f>
+        <v>12</v>
+      </c>
+      <c r="D60" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E60" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F60" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G60" s="33">
+        <f t="shared" ref="G60:G64" si="29">PRODUCT(C60:F60)</f>
+        <v>0.12150000000000001</v>
+      </c>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
-      <c r="J60" s="18">
-        <f>0.13*G58*515.52</f>
-        <v>194.36779439999998</v>
-      </c>
+      <c r="J60" s="18"/>
       <c r="K60" s="17"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="16"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
+      <c r="B61" s="32" t="str">
+        <f>B50</f>
+        <v>-for flooring</v>
+      </c>
+      <c r="C61" s="17">
+        <v>1</v>
+      </c>
+      <c r="D61" s="33">
+        <v>3.5</v>
+      </c>
+      <c r="E61" s="33">
+        <v>3.5</v>
+      </c>
+      <c r="F61" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G61" s="33">
+        <f t="shared" si="29"/>
+        <v>0.91874999999999996</v>
+      </c>
       <c r="H61" s="17"/>
       <c r="I61" s="17"/>
       <c r="J61" s="18"/>
       <c r="K61" s="17"/>
     </row>
-    <row r="62" spans="1:11" ht="30.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="16">
-        <v>5</v>
-      </c>
-      <c r="B62" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="16"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="17">
+        <v>1</v>
+      </c>
+      <c r="D62" s="33">
+        <v>4.2</v>
+      </c>
+      <c r="E62" s="33">
+        <v>3.2</v>
+      </c>
+      <c r="F62" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G62" s="33">
+        <f t="shared" si="29"/>
+        <v>1.008</v>
+      </c>
       <c r="H62" s="17"/>
       <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
+      <c r="J62" s="18"/>
       <c r="K62" s="17"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="16"/>
-      <c r="B63" s="32" t="str">
-        <f>B52</f>
-        <v>-for footing of vertical post</v>
-      </c>
-      <c r="C63" s="44">
-        <f>C45</f>
-        <v>12</v>
-      </c>
-      <c r="D63" s="45">
-        <v>0.45</v>
-      </c>
-      <c r="E63" s="44">
-        <v>0.45</v>
-      </c>
-      <c r="F63" s="45">
-        <v>0.05</v>
-      </c>
-      <c r="G63" s="45">
-        <f t="shared" ref="G63:G68" si="30">PRODUCT(C63:F63)</f>
-        <v>0.12150000000000001</v>
+      <c r="B63" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D63" s="33">
+        <v>3</v>
+      </c>
+      <c r="E63" s="33">
+        <f>0.6+0.45+0.45</f>
+        <v>1.5</v>
+      </c>
+      <c r="F63" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G63" s="33">
+        <f t="shared" si="29"/>
+        <v>-0.33749999999999997</v>
       </c>
       <c r="H63" s="17"/>
       <c r="I63" s="17"/>
       <c r="J63" s="18"/>
       <c r="K63" s="17"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="16"/>
-      <c r="B64" s="32"/>
+      <c r="B64" s="32" t="s">
+        <v>55</v>
+      </c>
       <c r="C64" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="E64" s="17">
-        <v>0.45</v>
+        <v>3.5</v>
+      </c>
+      <c r="E64" s="33">
+        <v>3.65</v>
       </c>
       <c r="F64" s="33">
-        <v>0.45</v>
+        <v>0.05</v>
       </c>
       <c r="G64" s="33">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>0.63875000000000004</v>
       </c>
       <c r="H64" s="17"/>
       <c r="I64" s="17"/>
       <c r="J64" s="18"/>
       <c r="K64" s="17"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" s="16"/>
-      <c r="B65" s="32" t="str">
-        <f>B53</f>
-        <v>-for flooring</v>
-      </c>
-      <c r="C65" s="44">
-        <v>1</v>
-      </c>
-      <c r="D65" s="45">
-        <v>3.5</v>
-      </c>
-      <c r="E65" s="45">
-        <v>3.5</v>
-      </c>
-      <c r="F65" s="45">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G65" s="45">
-        <f t="shared" si="30"/>
-        <v>0.91874999999999996</v>
-      </c>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="17"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="B65" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="39">
+        <f>SUM(G60:G64)</f>
+        <v>2.3494999999999999</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I65" s="6">
+        <v>13351.1</v>
+      </c>
+      <c r="J65" s="39">
+        <f>G65*I65</f>
+        <v>31368.409449999999</v>
+      </c>
+      <c r="K65" s="5"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="16"/>
-      <c r="B66" s="32"/>
-      <c r="C66" s="44">
-        <v>1</v>
-      </c>
-      <c r="D66" s="45">
-        <v>4.2</v>
-      </c>
-      <c r="E66" s="45">
-        <v>3.2</v>
-      </c>
-      <c r="F66" s="45">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G66" s="45">
-        <f t="shared" si="30"/>
-        <v>1.008</v>
-      </c>
+      <c r="B66" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
       <c r="H66" s="17"/>
       <c r="I66" s="17"/>
-      <c r="J66" s="18"/>
+      <c r="J66" s="18">
+        <f>0.13*G65*4169.92</f>
+        <v>1273.6395152</v>
+      </c>
       <c r="K66" s="17"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="16"/>
       <c r="B67" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C67" s="44">
-        <v>-1</v>
-      </c>
-      <c r="D67" s="45">
-        <v>3</v>
-      </c>
-      <c r="E67" s="45">
-        <f>0.6+0.45+0.45</f>
-        <v>1.5</v>
-      </c>
-      <c r="F67" s="45">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G67" s="45">
-        <f t="shared" si="30"/>
-        <v>-0.33749999999999997</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
       <c r="H67" s="17"/>
       <c r="I67" s="17"/>
-      <c r="J67" s="18"/>
+      <c r="J67" s="18">
+        <f>0.13*G65*1414.16</f>
+        <v>431.93395960000004</v>
+      </c>
       <c r="K67" s="17"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="16"/>
-      <c r="B68" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="C68" s="44">
-        <v>1</v>
-      </c>
-      <c r="D68" s="45">
-        <v>3.5</v>
-      </c>
-      <c r="E68" s="45">
-        <v>3.65</v>
-      </c>
-      <c r="F68" s="45">
-        <v>0.05</v>
-      </c>
-      <c r="G68" s="45">
-        <f t="shared" si="30"/>
-        <v>0.63875000000000004</v>
-      </c>
+      <c r="B68" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
       <c r="H68" s="17"/>
       <c r="I68" s="17"/>
-      <c r="J68" s="18"/>
+      <c r="J68" s="18">
+        <f>0.13*G65*(1652.5+737.97+349.56)</f>
+        <v>836.90106305000006</v>
+      </c>
       <c r="K68" s="17"/>
     </row>
-    <row r="69" spans="1:16" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2"/>
-      <c r="B69" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="C69" s="3"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="39">
-        <f>SUM(G63:G68)</f>
-        <v>2.3494999999999999</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I69" s="6">
-        <v>13351.1</v>
-      </c>
-      <c r="J69" s="39">
-        <f>G69*I69</f>
-        <v>31368.409449999999</v>
-      </c>
-      <c r="K69" s="5"/>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="16"/>
+      <c r="B69" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="18">
+        <f>0.13*G65*42</f>
+        <v>12.82827</v>
+      </c>
+      <c r="K69" s="17"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="16"/>
-      <c r="B70" s="32" t="s">
-        <v>26</v>
-      </c>
+      <c r="B70" s="32"/>
       <c r="C70" s="17"/>
       <c r="D70" s="17"/>
       <c r="E70" s="17"/>
@@ -4732,16 +4712,15 @@
       <c r="G70" s="17"/>
       <c r="H70" s="17"/>
       <c r="I70" s="17"/>
-      <c r="J70" s="18">
-        <f>0.13*G69*4169.92</f>
-        <v>1273.6395152</v>
-      </c>
+      <c r="J70" s="18"/>
       <c r="K70" s="17"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A71" s="16"/>
-      <c r="B71" s="32" t="s">
-        <v>27</v>
+    <row r="71" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="16">
+        <v>6</v>
+      </c>
+      <c r="B71" s="43" t="s">
+        <v>54</v>
       </c>
       <c r="C71" s="17"/>
       <c r="D71" s="17"/>
@@ -4750,67 +4729,106 @@
       <c r="G71" s="17"/>
       <c r="H71" s="17"/>
       <c r="I71" s="17"/>
-      <c r="J71" s="18">
-        <f>0.13*G69*1414.16</f>
-        <v>431.93395960000004</v>
-      </c>
+      <c r="J71" s="17"/>
       <c r="K71" s="17"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="16"/>
       <c r="B72" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17"/>
-      <c r="G72" s="17"/>
+        <v>45</v>
+      </c>
+      <c r="C72" s="17">
+        <v>2</v>
+      </c>
+      <c r="D72" s="33">
+        <v>3</v>
+      </c>
+      <c r="E72" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F72" s="33">
+        <v>0.8</v>
+      </c>
+      <c r="G72" s="33">
+        <f>PRODUCT(C72:F72)</f>
+        <v>2.16</v>
+      </c>
       <c r="H72" s="17"/>
       <c r="I72" s="17"/>
-      <c r="J72" s="18">
-        <f>0.13*G69*(1652.5+737.97+349.56)</f>
-        <v>836.90106305000006</v>
-      </c>
+      <c r="J72" s="17"/>
       <c r="K72" s="17"/>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M72" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N72" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O72" s="33"/>
+      <c r="P72" s="33">
+        <f>PI()*M72*SQRT(M72^2+N72^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="16"/>
-      <c r="B73" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C73" s="17"/>
-      <c r="D73" s="17"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="17"/>
-      <c r="G73" s="17"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="17">
+        <v>2</v>
+      </c>
+      <c r="D73" s="33">
+        <f>9/3.281</f>
+        <v>2.7430661383724475</v>
+      </c>
+      <c r="E73" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F73" s="33">
+        <v>0.8</v>
+      </c>
+      <c r="G73" s="33">
+        <f t="shared" ref="G73" si="30">PRODUCT(C73:F73)</f>
+        <v>1.9750076196281623</v>
+      </c>
       <c r="H73" s="17"/>
       <c r="I73" s="17"/>
-      <c r="J73" s="18">
-        <f>0.13*G69*42</f>
-        <v>12.82827</v>
-      </c>
+      <c r="J73" s="17"/>
       <c r="K73" s="17"/>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A74" s="16"/>
-      <c r="B74" s="32"/>
-      <c r="C74" s="17"/>
-      <c r="D74" s="17"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="17"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="17"/>
-      <c r="I74" s="17"/>
-      <c r="J74" s="18"/>
-      <c r="K74" s="17"/>
-    </row>
-    <row r="75" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="16">
-        <v>6</v>
-      </c>
-      <c r="B75" s="43" t="s">
-        <v>54</v>
+      <c r="M73" s="44"/>
+      <c r="N73" s="44"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
+    </row>
+    <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="6">
+        <f>SUM(G72:G73)</f>
+        <v>4.135007619628162</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I74" s="6">
+        <v>6337.3</v>
+      </c>
+      <c r="J74" s="18">
+        <f>G74*I74</f>
+        <v>26204.78378786955</v>
+      </c>
+      <c r="K74" s="5"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="16"/>
+      <c r="B75" s="32" t="s">
+        <v>51</v>
       </c>
       <c r="C75" s="17"/>
       <c r="D75" s="17"/>
@@ -4819,385 +4837,249 @@
       <c r="G75" s="17"/>
       <c r="H75" s="17"/>
       <c r="I75" s="17"/>
-      <c r="J75" s="17"/>
+      <c r="J75" s="18">
+        <f>0.13*G74*2577.63</f>
+        <v>1385.6075597756783</v>
+      </c>
       <c r="K75" s="17"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="16"/>
       <c r="B76" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C76" s="44">
-        <v>2</v>
-      </c>
-      <c r="D76" s="45">
-        <v>3</v>
-      </c>
-      <c r="E76" s="45">
-        <v>0.45</v>
-      </c>
-      <c r="F76" s="45">
-        <v>0.8</v>
-      </c>
-      <c r="G76" s="45">
-        <f>PRODUCT(C76:F76)</f>
-        <v>2.16</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="17"/>
+      <c r="G76" s="17"/>
       <c r="H76" s="17"/>
       <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
+      <c r="J76" s="18">
+        <f>0.13*G74*257.76</f>
+        <v>138.55914332459616</v>
+      </c>
       <c r="K76" s="17"/>
-      <c r="M76" s="33">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N76" s="33">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="O76" s="33"/>
-      <c r="P76" s="33">
-        <f>PI()*M76*SQRT(M76^2+N76^2)</f>
-        <v>160.09797821843054</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="16"/>
-      <c r="B77" s="32"/>
-      <c r="C77" s="17">
-        <v>0</v>
-      </c>
-      <c r="D77" s="33">
-        <v>3</v>
-      </c>
-      <c r="E77" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="F77" s="33">
-        <v>0.8</v>
-      </c>
-      <c r="G77" s="45">
-        <f t="shared" ref="G77:G78" si="31">PRODUCT(C77:F77)</f>
-        <v>0</v>
-      </c>
+      <c r="B77" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17"/>
       <c r="H77" s="17"/>
       <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
+      <c r="J77" s="18">
+        <f>0.13*G74*133.56</f>
+        <v>71.795310298079855</v>
+      </c>
       <c r="K77" s="17"/>
-      <c r="M77" s="46"/>
-      <c r="N77" s="46"/>
-      <c r="O77" s="46"/>
-      <c r="P77" s="46"/>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="16"/>
-      <c r="B78" s="32"/>
-      <c r="C78" s="17">
-        <v>2</v>
-      </c>
-      <c r="D78" s="33">
-        <f>9/3.281</f>
-        <v>2.7430661383724475</v>
-      </c>
-      <c r="E78" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="F78" s="33">
-        <v>0.8</v>
-      </c>
-      <c r="G78" s="45">
-        <f t="shared" si="31"/>
-        <v>1.9750076196281623</v>
-      </c>
+      <c r="B78" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="17"/>
       <c r="H78" s="17"/>
       <c r="I78" s="17"/>
-      <c r="J78" s="17"/>
+      <c r="J78" s="18">
+        <f>0.13*G74*19.6</f>
+        <v>10.535999414812558</v>
+      </c>
       <c r="K78" s="17"/>
-      <c r="M78" s="46"/>
-      <c r="N78" s="46"/>
-      <c r="O78" s="46"/>
-      <c r="P78" s="46"/>
-    </row>
-    <row r="79" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2"/>
-      <c r="B79" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="6">
-        <f>SUM(G76:G78)</f>
-        <v>4.135007619628162</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I79" s="6">
-        <v>6337.3</v>
-      </c>
-      <c r="J79" s="18">
-        <f>G79*I79</f>
-        <v>26204.78378786955</v>
-      </c>
-      <c r="K79" s="5"/>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A80" s="16"/>
-      <c r="B80" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="18">
-        <f>0.13*G79*2577.63</f>
-        <v>1385.6075597756783</v>
-      </c>
-      <c r="K80" s="17"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A81" s="16"/>
-      <c r="B81" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="18">
-        <f>0.13*G79*257.76</f>
-        <v>138.55914332459616</v>
-      </c>
-      <c r="K81" s="17"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A82" s="16"/>
-      <c r="B82" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="17"/>
-      <c r="G82" s="17"/>
-      <c r="H82" s="17"/>
-      <c r="I82" s="17"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="16"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="17"/>
+      <c r="H79" s="17"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="18"/>
+      <c r="K79" s="17"/>
+    </row>
+    <row r="80" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>7</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="7">
+        <f t="shared" ref="G80" si="31">PRODUCT(C80:F80)</f>
+        <v>1</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J80" s="7">
+        <f>G80*I80</f>
+        <v>1000</v>
+      </c>
+      <c r="K80" s="5"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="5"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82" s="21"/>
+      <c r="B82" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="23"/>
+      <c r="D82" s="24"/>
+      <c r="E82" s="24"/>
+      <c r="F82" s="24"/>
+      <c r="G82" s="18"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="18"/>
       <c r="J82" s="18">
-        <f>0.13*G79*133.56</f>
-        <v>71.795310298079855</v>
-      </c>
-      <c r="K82" s="17"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A83" s="16"/>
-      <c r="B83" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="17"/>
-      <c r="G83" s="17"/>
-      <c r="H83" s="17"/>
-      <c r="I83" s="17"/>
-      <c r="J83" s="18">
-        <f>0.13*G79*19.6</f>
-        <v>10.535999414812558</v>
-      </c>
-      <c r="K83" s="17"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A84" s="16"/>
-      <c r="B84" s="32"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17"/>
-      <c r="G84" s="17"/>
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="18"/>
-      <c r="K84" s="17"/>
-    </row>
-    <row r="85" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
-        <v>7</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" s="3">
-        <v>1</v>
-      </c>
-      <c r="D85" s="4"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
-      <c r="G85" s="7">
-        <f t="shared" ref="G85" si="32">PRODUCT(C85:F85)</f>
-        <v>1</v>
-      </c>
-      <c r="H85" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I85" s="6">
-        <v>1000</v>
-      </c>
-      <c r="J85" s="7">
-        <f>G85*I85</f>
-        <v>1000</v>
-      </c>
-      <c r="K85" s="5"/>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A86" s="2"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="7"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="18"/>
-      <c r="K86" s="5"/>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A87" s="21"/>
-      <c r="B87" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C87" s="23"/>
-      <c r="D87" s="24"/>
-      <c r="E87" s="24"/>
-      <c r="F87" s="24"/>
-      <c r="G87" s="18"/>
-      <c r="H87" s="18"/>
-      <c r="I87" s="18"/>
-      <c r="J87" s="18">
-        <f>SUM(J9:J85)</f>
+        <f>SUM(J9:J80)</f>
         <v>240974.86130219698</v>
       </c>
-      <c r="K87" s="25"/>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="M88" s="20"/>
-      <c r="N88" s="20"/>
-      <c r="O88" s="20"/>
-      <c r="P88" s="20"/>
-      <c r="Q88" s="20"/>
-      <c r="R88" s="20"/>
-      <c r="S88" s="20"/>
-    </row>
-    <row r="89" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="26"/>
+      <c r="K82" s="25"/>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M83" s="20"/>
+      <c r="N83" s="20"/>
+      <c r="O83" s="20"/>
+      <c r="P83" s="20"/>
+      <c r="Q83" s="20"/>
+      <c r="R83" s="20"/>
+      <c r="S83" s="20"/>
+    </row>
+    <row r="84" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="26"/>
+      <c r="B84" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C84" s="65">
+        <f>J82</f>
+        <v>240974.86130219698</v>
+      </c>
+      <c r="D84" s="66"/>
+      <c r="E84" s="9">
+        <v>100</v>
+      </c>
+      <c r="F84" s="26"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="29"/>
+      <c r="J84" s="30"/>
+      <c r="K84" s="31"/>
+      <c r="M84" s="19"/>
+      <c r="N84" s="19"/>
+      <c r="O84" s="19"/>
+      <c r="P84" s="19"/>
+      <c r="Q84" s="19"/>
+      <c r="R84" s="19"/>
+      <c r="S84" s="19"/>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B85" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" s="68">
+        <v>200000</v>
+      </c>
+      <c r="D85" s="69"/>
+      <c r="E85" s="9"/>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B86" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" s="68">
+        <f>C85-C88-C89</f>
+        <v>190000</v>
+      </c>
+      <c r="D86" s="69"/>
+      <c r="E86" s="9">
+        <f>C86/C84*100</f>
+        <v>78.846398737720847</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B87" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="70">
+        <f>C84-C86</f>
+        <v>50974.86130219698</v>
+      </c>
+      <c r="D87" s="70"/>
+      <c r="E87" s="9">
+        <f>100-E86</f>
+        <v>21.153601262279153</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B88" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" s="65">
+        <f>C85*0.03</f>
+        <v>6000</v>
+      </c>
+      <c r="D88" s="66"/>
+      <c r="E88" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B89" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C89" s="59">
-        <f>J87</f>
-        <v>240974.86130219698</v>
-      </c>
-      <c r="D89" s="60"/>
+        <v>24</v>
+      </c>
+      <c r="C89" s="65">
+        <f>C85*0.02</f>
+        <v>4000</v>
+      </c>
+      <c r="D89" s="66"/>
       <c r="E89" s="9">
-        <v>100</v>
-      </c>
-      <c r="F89" s="26"/>
-      <c r="G89" s="28"/>
-      <c r="H89" s="26"/>
-      <c r="I89" s="29"/>
-      <c r="J89" s="30"/>
-      <c r="K89" s="31"/>
-      <c r="M89" s="19"/>
-      <c r="N89" s="19"/>
-      <c r="O89" s="19"/>
-      <c r="P89" s="19"/>
-      <c r="Q89" s="19"/>
-      <c r="R89" s="19"/>
-      <c r="S89" s="19"/>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B90" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C90" s="63">
-        <v>200000</v>
-      </c>
-      <c r="D90" s="64"/>
-      <c r="E90" s="9"/>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B91" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C91" s="63">
-        <f>C90-C93-C94</f>
-        <v>190000</v>
-      </c>
-      <c r="D91" s="64"/>
-      <c r="E91" s="9">
-        <f>C91/C89*100</f>
-        <v>78.846398737720847</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B92" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C92" s="65">
-        <f>C89-C91</f>
-        <v>50974.86130219698</v>
-      </c>
-      <c r="D92" s="65"/>
-      <c r="E92" s="9">
-        <f>100-E91</f>
-        <v>21.153601262279153</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B93" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C93" s="59">
-        <f>C90*0.03</f>
-        <v>6000</v>
-      </c>
-      <c r="D93" s="60"/>
-      <c r="E93" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B94" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C94" s="59">
-        <f>C90*0.02</f>
-        <v>4000</v>
-      </c>
-      <c r="D94" s="60"/>
-      <c r="E94" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -5211,229 +5093,226 @@
   <headerFooter>
     <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="66" max="10" man="1"/>
-  </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="2" max="2" width="39.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-    </row>
-    <row r="2" spans="1:13" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="A2" s="67" t="s">
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+    </row>
+    <row r="2" spans="1:13" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-    </row>
-    <row r="3" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="68" t="s">
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+    </row>
+    <row r="3" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-    </row>
-    <row r="4" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="68" t="s">
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+    </row>
+    <row r="4" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-    </row>
-    <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="69" t="s">
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
+    </row>
+    <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="69"/>
-    </row>
-    <row r="6" spans="1:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="70" t="s">
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+    </row>
+    <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="71">
+      <c r="B6" s="47"/>
+      <c r="C6" s="78">
         <f>F42</f>
         <v>234835.07491669987</v>
       </c>
-      <c r="D6" s="72"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70" t="s">
+      <c r="D6" s="79"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71">
+      <c r="I6" s="47"/>
+      <c r="J6" s="78">
         <f>I42</f>
         <v>240974.86130219698</v>
       </c>
-      <c r="K6" s="72"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="74" t="s">
+      <c r="K6" s="79"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="I7" s="76" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="I7" s="85" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="76"/>
-      <c r="K7" s="76"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="53" t="s">
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="I8" s="77" t="s">
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="I8" s="86" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="78" t="str">
-        <f>[4]estimate!A7</f>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="87" t="str">
+        <f>[7]estimate!A7</f>
         <v>Location:- Shankharapur Municipality 1</v>
       </c>
-      <c r="B9" s="78"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="I9" s="77" t="s">
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="I9" s="86" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="89" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="79" t="s">
+      <c r="B11" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="C11" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="90" t="s">
         <v>82</v>
       </c>
-      <c r="C11" s="79" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="80" t="s">
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80" t="s">
+      <c r="H11" s="90"/>
+      <c r="I11" s="90"/>
+      <c r="J11" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="79" t="s">
+      <c r="K11" s="88" t="s">
         <v>85</v>
       </c>
-      <c r="K11" s="81" t="s">
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="89"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
+      <c r="D12" s="50" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="79"/>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="82" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="82" t="s">
+      <c r="E12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="82" t="s">
+      <c r="F12" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="82" t="s">
-        <v>87</v>
-      </c>
-      <c r="H12" s="82" t="s">
+      <c r="G12" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="82" t="s">
+      <c r="I12" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="79"/>
-      <c r="K12" s="81"/>
-    </row>
-    <row r="13" spans="1:13" s="35" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="83">
+      <c r="J12" s="89"/>
+      <c r="K12" s="88"/>
+    </row>
+    <row r="13" spans="1:13" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="51">
         <f>estimate!A9</f>
         <v>1</v>
       </c>
@@ -5441,88 +5320,88 @@
         <f>estimate!B9</f>
         <v>sfnf] kmnfd] kfO{ksf] 6«; agfO{ h8fg ug]{ sfd</v>
       </c>
-      <c r="C13" s="84" t="str">
+      <c r="C13" s="52" t="str">
         <f>estimate!H17</f>
         <v>Kg</v>
       </c>
-      <c r="D13" s="84">
+      <c r="D13" s="52">
         <f>estimate!G17</f>
         <v>506.57726302956416</v>
       </c>
-      <c r="E13" s="84">
+      <c r="E13" s="52">
         <f>estimate!I17</f>
         <v>182.51</v>
       </c>
-      <c r="F13" s="84">
+      <c r="F13" s="52">
         <f>D13*E13</f>
         <v>92455.416275525757</v>
       </c>
-      <c r="G13" s="84">
-        <f>V!G28</f>
+      <c r="G13" s="52">
+        <f>V!G27</f>
         <v>495.88546019506242</v>
       </c>
-      <c r="H13" s="84">
-        <f>V!I28</f>
+      <c r="H13" s="52">
+        <f>V!I27</f>
         <v>182.51</v>
       </c>
-      <c r="I13" s="84">
+      <c r="I13" s="52">
         <f>G13*H13</f>
         <v>90504.055340200837</v>
       </c>
-      <c r="J13" s="85">
+      <c r="J13" s="53">
         <f>I13-F13</f>
         <v>-1951.3609353249194</v>
       </c>
-      <c r="K13" s="86"/>
+      <c r="K13" s="54"/>
       <c r="M13" s="35">
         <f>1.25*F13</f>
         <v>115569.2703444072</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="83"/>
-      <c r="B14" s="87" t="str">
+    <row r="14" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="51"/>
+      <c r="B14" s="55" t="str">
         <f>estimate!B18</f>
         <v>-VAT 13% for materials</v>
       </c>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84">
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52">
         <f>estimate!J18</f>
         <v>6506.9929675418325</v>
       </c>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84">
-        <f>V!J29</f>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52">
+        <f>V!J28</f>
         <v>6369.6565907799195</v>
       </c>
-      <c r="J14" s="85">
+      <c r="J14" s="53">
         <f>I14-F14</f>
         <v>-137.33637676191302</v>
       </c>
-      <c r="K14" s="86"/>
+      <c r="K14" s="54"/>
       <c r="M14" s="35">
         <f t="shared" ref="M14:M38" si="0">1.25*F14</f>
         <v>8133.7412094272904</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="89"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="85"/>
-      <c r="K15" s="86"/>
-    </row>
-    <row r="16" spans="1:13" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A16" s="83">
+    <row r="15" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="56"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="54"/>
+    </row>
+    <row r="16" spans="1:13" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="51">
         <f>estimate!A20</f>
         <v>2</v>
       </c>
@@ -5530,175 +5409,175 @@
         <f>estimate!B20</f>
         <v>).#^ lblv ).$ dL.dL.afSnf] sf]?u]6]8 /+lug ss{6 kftfsf] 5fgf 5fpg] sfd</v>
       </c>
-      <c r="C16" s="84" t="str">
+      <c r="C16" s="52" t="str">
         <f>estimate!H23</f>
         <v>sqm</v>
       </c>
-      <c r="D16" s="84">
+      <c r="D16" s="52">
         <f>estimate!G23</f>
         <v>51.92773108978286</v>
       </c>
-      <c r="E16" s="84">
+      <c r="E16" s="52">
         <f>estimate!I23</f>
         <v>1074.98</v>
       </c>
-      <c r="F16" s="84">
+      <c r="F16" s="52">
         <f>D16*E16</f>
         <v>55821.27236689478</v>
       </c>
-      <c r="G16" s="84">
-        <f>V!G36</f>
+      <c r="G16" s="52">
+        <f>V!G34</f>
         <v>53.456394314851664</v>
       </c>
-      <c r="H16" s="84">
-        <f>V!I36</f>
+      <c r="H16" s="52">
+        <f>V!I34</f>
         <v>1074.98</v>
       </c>
-      <c r="I16" s="84">
+      <c r="I16" s="52">
         <f>G16*H16</f>
         <v>57464.554760579245</v>
       </c>
-      <c r="J16" s="85">
+      <c r="J16" s="53">
         <f>I16-F16</f>
         <v>1643.2823936844652</v>
       </c>
-      <c r="K16" s="86"/>
+      <c r="K16" s="54"/>
       <c r="M16" s="35">
         <f t="shared" si="0"/>
         <v>69776.590458618477</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="83"/>
-      <c r="B17" s="87" t="str">
+    <row r="17" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="51"/>
+      <c r="B17" s="55" t="str">
         <f>estimate!B24</f>
         <v>-13% VAT for sheet</v>
       </c>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84">
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52">
         <f>estimate!J24</f>
         <v>4505.7993447444915</v>
       </c>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="84">
-        <f>V!J37</f>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52">
+        <f>V!J35</f>
         <v>4638.4423394083815</v>
       </c>
-      <c r="J17" s="85">
+      <c r="J17" s="53">
         <f t="shared" ref="J17:J20" si="1">I17-F17</f>
         <v>132.64299466389002</v>
       </c>
-      <c r="K17" s="86"/>
+      <c r="K17" s="54"/>
       <c r="M17" s="35">
         <f t="shared" si="0"/>
         <v>5632.2491809306139</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="83"/>
-      <c r="B18" s="87" t="str">
+    <row r="18" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="51"/>
+      <c r="B18" s="55" t="str">
         <f>estimate!B25</f>
         <v>-13% VAT for nut bolt</v>
       </c>
-      <c r="C18" s="84"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84">
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52">
         <f>estimate!J25</f>
         <v>691.09319114114771</v>
       </c>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="84">
-        <f>V!J38</f>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52">
+        <f>V!J36</f>
         <v>711.43778783778214</v>
       </c>
-      <c r="J18" s="85">
+      <c r="J18" s="53">
         <f t="shared" si="1"/>
         <v>20.344596696634426</v>
       </c>
-      <c r="K18" s="86"/>
+      <c r="K18" s="54"/>
       <c r="M18" s="35">
         <f t="shared" si="0"/>
         <v>863.86648892643461</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="83"/>
-      <c r="B19" s="87" t="str">
+    <row r="19" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="51"/>
+      <c r="B19" s="55" t="str">
         <f>estimate!B26</f>
         <v>-13% VAT for j-hook</v>
       </c>
-      <c r="C19" s="84"/>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="84">
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52">
         <f>estimate!J26</f>
         <v>235.06281815605274</v>
       </c>
-      <c r="G19" s="84"/>
-      <c r="H19" s="84"/>
-      <c r="I19" s="84">
-        <f>V!J39</f>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52">
+        <f>V!J37</f>
         <v>241.98266383686845</v>
       </c>
-      <c r="J19" s="85">
+      <c r="J19" s="53">
         <f t="shared" si="1"/>
         <v>6.9198456808157118</v>
       </c>
-      <c r="K19" s="86"/>
+      <c r="K19" s="54"/>
       <c r="M19" s="35">
         <f t="shared" si="0"/>
         <v>293.82852269506594</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="83"/>
-      <c r="B20" s="87" t="str">
+    <row r="20" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="51"/>
+      <c r="B20" s="55" t="str">
         <f>estimate!B27</f>
         <v>-13% VAT for bitumen washer</v>
       </c>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="84">
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52">
         <f>estimate!J27</f>
         <v>111.38498318758425</v>
       </c>
-      <c r="G20" s="84"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="84">
-        <f>V!J40</f>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52">
+        <f>V!J38</f>
         <v>114.66396580535684</v>
       </c>
-      <c r="J20" s="85">
+      <c r="J20" s="53">
         <f t="shared" si="1"/>
         <v>3.2789826177725843</v>
       </c>
-      <c r="K20" s="86"/>
+      <c r="K20" s="54"/>
       <c r="M20" s="35">
         <f t="shared" si="0"/>
         <v>139.23122898448031</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="84"/>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84"/>
-      <c r="F21" s="84"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="84"/>
-      <c r="I21" s="84"/>
-      <c r="J21" s="85"/>
-      <c r="K21" s="86"/>
-    </row>
-    <row r="22" spans="1:13" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.3">
-      <c r="A22" s="83">
+    <row r="21" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="56"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="54"/>
+    </row>
+    <row r="22" spans="1:13" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="51">
         <f>estimate!A29</f>
         <v>3</v>
       </c>
@@ -5706,59 +5585,59 @@
         <f>estimate!B29</f>
         <v>g/d k|sf/sf] Sn] / l;N6L df6f]df ;j} lsl;dsf] vGg] sfd</v>
       </c>
-      <c r="C22" s="84" t="str">
+      <c r="C22" s="52" t="str">
         <f>estimate!H32</f>
         <v>cum</v>
       </c>
-      <c r="D22" s="84">
+      <c r="D22" s="52">
         <f>estimate!G32</f>
         <v>5.6780152392563235</v>
       </c>
-      <c r="E22" s="84">
+      <c r="E22" s="52">
         <f>estimate!I32</f>
         <v>674.12</v>
       </c>
-      <c r="F22" s="84">
+      <c r="F22" s="52">
         <f>D22*E22</f>
         <v>3827.6636330874726</v>
       </c>
-      <c r="G22" s="84">
-        <f>V!G49</f>
+      <c r="G22" s="52">
+        <f>V!G46</f>
         <v>5.9193849876000471</v>
       </c>
-      <c r="H22" s="84">
-        <f>V!I49</f>
+      <c r="H22" s="52">
+        <f>V!I46</f>
         <v>674.12</v>
       </c>
-      <c r="I22" s="84">
+      <c r="I22" s="52">
         <f>G22*H22</f>
         <v>3990.3758078409437</v>
       </c>
-      <c r="J22" s="85">
+      <c r="J22" s="53">
         <f>I22-F22</f>
         <v>162.71217475347112</v>
       </c>
-      <c r="K22" s="86"/>
+      <c r="K22" s="54"/>
       <c r="M22" s="35">
         <f t="shared" si="0"/>
         <v>4784.5795413593405</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="85"/>
-      <c r="K23" s="86"/>
-    </row>
-    <row r="24" spans="1:13" s="35" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A24" s="83">
+    <row r="23" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="56"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="54"/>
+    </row>
+    <row r="24" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="51">
         <f>estimate!A34</f>
         <v>4</v>
       </c>
@@ -5766,117 +5645,117 @@
         <f>estimate!B34</f>
         <v>husf] vf8ndf 9'+uf eg]{ / n]en ug]{ sfddf</v>
       </c>
-      <c r="C24" s="84" t="str">
+      <c r="C24" s="52" t="str">
         <f>estimate!H38</f>
         <v>cum</v>
       </c>
-      <c r="D24" s="84">
+      <c r="D24" s="52">
         <f>estimate!G38</f>
         <v>2.6789565844223686</v>
       </c>
-      <c r="E24" s="84">
+      <c r="E24" s="52">
         <f>estimate!I38</f>
         <v>4495.6400000000003</v>
       </c>
-      <c r="F24" s="84">
+      <c r="F24" s="52">
         <f>D24*E24</f>
         <v>12043.624379192579</v>
       </c>
-      <c r="G24" s="84">
-        <f>V!G58</f>
+      <c r="G24" s="52">
+        <f>V!G55</f>
         <v>2.9002499999999998</v>
       </c>
-      <c r="H24" s="84">
-        <f>V!I58</f>
+      <c r="H24" s="52">
+        <f>V!I55</f>
         <v>4495.6400000000003</v>
       </c>
-      <c r="I24" s="84">
+      <c r="I24" s="52">
         <f>G24*H24</f>
         <v>13038.47991</v>
       </c>
-      <c r="J24" s="85">
+      <c r="J24" s="53">
         <f>I24-F24</f>
         <v>994.85553080742102</v>
       </c>
-      <c r="K24" s="86"/>
+      <c r="K24" s="54"/>
       <c r="M24" s="35">
         <f t="shared" si="0"/>
         <v>15054.530473990724</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="83"/>
-      <c r="B25" s="87" t="str">
+    <row r="25" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="51"/>
+      <c r="B25" s="55" t="str">
         <f>estimate!B39</f>
         <v>-13% VAT for block stone</v>
       </c>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="84"/>
-      <c r="F25" s="84">
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52">
         <f>estimate!J39</f>
         <v>897.69665189160207</v>
       </c>
-      <c r="G25" s="84"/>
-      <c r="H25" s="84"/>
-      <c r="I25" s="84">
-        <f>V!J59</f>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52">
+        <f>V!J56</f>
         <v>971.85028297500003</v>
       </c>
-      <c r="J25" s="85">
+      <c r="J25" s="53">
         <f>I25-F25</f>
         <v>74.153631083397954</v>
       </c>
-      <c r="K25" s="86"/>
+      <c r="K25" s="54"/>
       <c r="M25" s="35">
         <f t="shared" si="0"/>
         <v>1122.1208148645026</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="83"/>
-      <c r="B26" s="87" t="str">
+    <row r="26" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="51"/>
+      <c r="B26" s="55" t="str">
         <f>estimate!B40</f>
         <v>-13% VAT for bond stone</v>
       </c>
-      <c r="C26" s="84"/>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="84">
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52">
         <f>estimate!J40</f>
         <v>179.53724079218455</v>
       </c>
-      <c r="G26" s="84"/>
-      <c r="H26" s="84"/>
-      <c r="I26" s="84">
-        <f>V!J60</f>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52">
+        <f>V!J57</f>
         <v>194.36779439999998</v>
       </c>
-      <c r="J26" s="85">
+      <c r="J26" s="53">
         <f t="shared" ref="J26" si="2">I26-F26</f>
         <v>14.830553607815432</v>
       </c>
-      <c r="K26" s="86"/>
+      <c r="K26" s="54"/>
       <c r="M26" s="35">
         <f t="shared" si="0"/>
         <v>224.42155099023068</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="88"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="84"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="84"/>
-      <c r="F27" s="84"/>
-      <c r="G27" s="84"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="86"/>
-    </row>
-    <row r="28" spans="1:13" s="35" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A28" s="83">
+    <row r="27" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="56"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="54"/>
+    </row>
+    <row r="28" spans="1:13" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="51">
         <f>estimate!A42</f>
         <v>5</v>
       </c>
@@ -5884,175 +5763,175 @@
         <f>estimate!B42</f>
         <v>hu leQf kvf{ndf l;d]G6 s+lqm6 ug]{ sfd -lk=;L=;L= !M@M$_</v>
       </c>
-      <c r="C28" s="84" t="str">
+      <c r="C28" s="52" t="str">
         <f>estimate!H47</f>
         <v>cum</v>
       </c>
-      <c r="D28" s="84">
+      <c r="D28" s="52">
         <f>estimate!G47</f>
         <v>2.0772289044985861</v>
       </c>
-      <c r="E28" s="84">
+      <c r="E28" s="52">
         <f>estimate!I47</f>
         <v>13351.1</v>
       </c>
-      <c r="F28" s="84">
+      <c r="F28" s="52">
         <f>D28*E28</f>
         <v>27733.290826851073</v>
       </c>
-      <c r="G28" s="84">
-        <f>V!G69</f>
+      <c r="G28" s="52">
+        <f>V!G65</f>
         <v>2.3494999999999999</v>
       </c>
-      <c r="H28" s="84">
-        <f>V!I69</f>
+      <c r="H28" s="52">
+        <f>V!I65</f>
         <v>13351.1</v>
       </c>
-      <c r="I28" s="84">
+      <c r="I28" s="52">
         <f>G28*H28</f>
         <v>31368.409449999999</v>
       </c>
-      <c r="J28" s="85">
+      <c r="J28" s="53">
         <f>I28-F28</f>
         <v>3635.1186231489264</v>
       </c>
-      <c r="K28" s="86"/>
+      <c r="K28" s="54"/>
       <c r="M28" s="35">
         <f t="shared" si="0"/>
         <v>34666.613533563839</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="83"/>
-      <c r="B29" s="87" t="str">
+    <row r="29" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="51"/>
+      <c r="B29" s="55" t="str">
         <f>estimate!B48</f>
         <v>-13% VAT for cement</v>
       </c>
-      <c r="C29" s="84"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="84">
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52">
         <f>estimate!J48</f>
         <v>1126.0441859480768</v>
       </c>
-      <c r="G29" s="84"/>
-      <c r="H29" s="84"/>
-      <c r="I29" s="84">
-        <f>V!J70</f>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52">
+        <f>V!J66</f>
         <v>1273.6395152</v>
       </c>
-      <c r="J29" s="85">
+      <c r="J29" s="53">
         <f>I29-F29</f>
         <v>147.5953292519232</v>
       </c>
-      <c r="K29" s="86"/>
+      <c r="K29" s="54"/>
       <c r="M29" s="35">
         <f t="shared" si="0"/>
         <v>1407.5552324350961</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="83"/>
-      <c r="B30" s="87" t="str">
+    <row r="30" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="51"/>
+      <c r="B30" s="55" t="str">
         <f>estimate!B49</f>
         <v>-13% VAT for sand</v>
       </c>
-      <c r="C30" s="84"/>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84">
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52">
         <f>estimate!J49</f>
         <v>381.87942358614367</v>
       </c>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84">
-        <f>V!J71</f>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52">
+        <f>V!J67</f>
         <v>431.93395960000004</v>
       </c>
-      <c r="J30" s="85">
+      <c r="J30" s="53">
         <f t="shared" ref="J30:J32" si="3">I30-F30</f>
         <v>50.054536013856364</v>
       </c>
-      <c r="K30" s="86"/>
+      <c r="K30" s="54"/>
       <c r="M30" s="35">
         <f t="shared" si="0"/>
         <v>477.34927948267961</v>
       </c>
     </row>
-    <row r="31" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="83"/>
-      <c r="B31" s="87" t="str">
+    <row r="31" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="51"/>
+      <c r="B31" s="55" t="str">
         <f>estimate!B50</f>
         <v>-13% VAT for aggregate</v>
       </c>
-      <c r="C31" s="84"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="84">
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52">
         <f>estimate!J50</f>
         <v>739.91703697512401</v>
       </c>
-      <c r="G31" s="84"/>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84">
-        <f>V!J72</f>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52">
+        <f>V!J68</f>
         <v>836.90106305000006</v>
       </c>
-      <c r="J31" s="85">
+      <c r="J31" s="53">
         <f t="shared" si="3"/>
         <v>96.984026074876056</v>
       </c>
-      <c r="K31" s="86"/>
+      <c r="K31" s="54"/>
       <c r="M31" s="35">
         <f t="shared" si="0"/>
         <v>924.89629621890504</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="83"/>
-      <c r="B32" s="87" t="str">
+    <row r="32" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="51"/>
+      <c r="B32" s="55" t="str">
         <f>estimate!B51</f>
         <v>-13% VAT for water</v>
       </c>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="84">
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52">
         <f>estimate!J51</f>
         <v>11.341669818562281</v>
       </c>
-      <c r="G32" s="84"/>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84">
-        <f>V!J73</f>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52">
+        <f>V!J69</f>
         <v>12.82827</v>
       </c>
-      <c r="J32" s="85">
+      <c r="J32" s="53">
         <f t="shared" si="3"/>
         <v>1.4866001814377192</v>
       </c>
-      <c r="K32" s="86"/>
+      <c r="K32" s="54"/>
       <c r="M32" s="35">
         <f t="shared" si="0"/>
         <v>14.177087273202851</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="88"/>
-      <c r="B33" s="89"/>
-      <c r="C33" s="84"/>
-      <c r="D33" s="84"/>
-      <c r="E33" s="84"/>
-      <c r="F33" s="84"/>
-      <c r="G33" s="84"/>
-      <c r="H33" s="84"/>
-      <c r="I33" s="84"/>
-      <c r="J33" s="85"/>
-      <c r="K33" s="86"/>
-    </row>
-    <row r="34" spans="1:13" s="35" customFormat="1" ht="15" x14ac:dyDescent="0.3">
-      <c r="A34" s="83">
+    <row r="33" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="56"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="54"/>
+    </row>
+    <row r="34" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="51">
         <f>estimate!A53</f>
         <v>6</v>
       </c>
@@ -6060,253 +5939,253 @@
         <f>estimate!B53</f>
         <v>9'Ëfsf] uf/f] df6f] nufpg] sfd</v>
       </c>
-      <c r="C34" s="84" t="str">
+      <c r="C34" s="52" t="str">
         <f>estimate!H55</f>
         <v>cum</v>
       </c>
-      <c r="D34" s="84">
+      <c r="D34" s="52">
         <f>estimate!G55</f>
         <v>3.9500152392563237</v>
       </c>
-      <c r="E34" s="84">
+      <c r="E34" s="52">
         <f>estimate!I55</f>
         <v>6337.3</v>
       </c>
-      <c r="F34" s="84">
+      <c r="F34" s="52">
         <f>D34*E34</f>
         <v>25032.431575739101</v>
       </c>
-      <c r="G34" s="84">
-        <f>V!G79</f>
+      <c r="G34" s="52">
+        <f>V!G74</f>
         <v>4.135007619628162</v>
       </c>
-      <c r="H34" s="84">
-        <f>V!I79</f>
+      <c r="H34" s="52">
+        <f>V!I74</f>
         <v>6337.3</v>
       </c>
-      <c r="I34" s="84">
+      <c r="I34" s="52">
         <f>G34*H34</f>
         <v>26204.78378786955</v>
       </c>
-      <c r="J34" s="85">
+      <c r="J34" s="53">
         <f>I34-F34</f>
         <v>1172.3522121304486</v>
       </c>
-      <c r="K34" s="86"/>
+      <c r="K34" s="54"/>
       <c r="M34" s="35">
         <f t="shared" si="0"/>
         <v>31290.539469673877</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="83"/>
-      <c r="B35" s="87" t="str">
+    <row r="35" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="51"/>
+      <c r="B35" s="55" t="str">
         <f>estimate!B56</f>
         <v>-13% VAT for block stone</v>
       </c>
-      <c r="C35" s="84"/>
-      <c r="D35" s="84"/>
-      <c r="E35" s="84"/>
-      <c r="F35" s="84">
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52">
         <f>estimate!J56</f>
         <v>1323.6181115513564</v>
       </c>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="84">
-        <f>V!J80</f>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52">
+        <f>V!J75</f>
         <v>1385.6075597756783</v>
       </c>
-      <c r="J35" s="85">
+      <c r="J35" s="53">
         <f>I35-F35</f>
         <v>61.989448224321904</v>
       </c>
-      <c r="K35" s="86"/>
+      <c r="K35" s="54"/>
       <c r="M35" s="35">
         <f t="shared" si="0"/>
         <v>1654.5226394391955</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="83"/>
-      <c r="B36" s="87" t="str">
+    <row r="36" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="51"/>
+      <c r="B36" s="55" t="str">
         <f>estimate!B57</f>
         <v>-13% VAT for bond stone</v>
       </c>
-      <c r="C36" s="84"/>
-      <c r="D36" s="84"/>
-      <c r="E36" s="84"/>
-      <c r="F36" s="84">
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52">
         <f>estimate!J57</f>
         <v>132.3602706491923</v>
       </c>
-      <c r="G36" s="84"/>
-      <c r="H36" s="84"/>
-      <c r="I36" s="84">
-        <f>V!J81</f>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52">
+        <f>V!J76</f>
         <v>138.55914332459616</v>
       </c>
-      <c r="J36" s="85">
+      <c r="J36" s="53">
         <f t="shared" ref="J36:J38" si="4">I36-F36</f>
         <v>6.1988726754038623</v>
       </c>
-      <c r="K36" s="86"/>
+      <c r="K36" s="54"/>
       <c r="M36" s="35">
         <f t="shared" si="0"/>
         <v>165.45033831149038</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="88"/>
-      <c r="B37" s="87" t="str">
+    <row r="37" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="56"/>
+      <c r="B37" s="55" t="str">
         <f>estimate!B58</f>
         <v>-13% VAT for stone</v>
       </c>
-      <c r="C37" s="84"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="84"/>
-      <c r="F37" s="84">
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52">
         <f>estimate!J58</f>
         <v>68.583324596159699</v>
       </c>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
-      <c r="I37" s="84">
-        <f>V!J82</f>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52">
+        <f>V!J77</f>
         <v>71.795310298079855</v>
       </c>
-      <c r="J37" s="85">
+      <c r="J37" s="53">
         <f t="shared" si="4"/>
         <v>3.2119857019201561</v>
       </c>
-      <c r="K37" s="86"/>
+      <c r="K37" s="54"/>
       <c r="M37" s="35">
         <f t="shared" si="0"/>
         <v>85.72915574519962</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="35" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="83"/>
-      <c r="B38" s="87" t="str">
+    <row r="38" spans="1:13" s="35" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="51"/>
+      <c r="B38" s="55" t="str">
         <f>estimate!B59</f>
         <v>-13% VAT for water</v>
       </c>
-      <c r="C38" s="84"/>
-      <c r="D38" s="84"/>
-      <c r="E38" s="84"/>
-      <c r="F38" s="84">
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52">
         <f>estimate!J59</f>
         <v>10.064638829625114</v>
       </c>
-      <c r="G38" s="84"/>
-      <c r="H38" s="84"/>
-      <c r="I38" s="84">
-        <f>V!J83</f>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52">
+        <f>V!J78</f>
         <v>10.535999414812558</v>
       </c>
-      <c r="J38" s="85">
+      <c r="J38" s="53">
         <f t="shared" si="4"/>
         <v>0.47136058518744406</v>
       </c>
-      <c r="K38" s="86"/>
+      <c r="K38" s="54"/>
       <c r="M38" s="35">
         <f t="shared" si="0"/>
         <v>12.580798537031392</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="88"/>
-      <c r="B39" s="89"/>
-      <c r="C39" s="84"/>
-      <c r="D39" s="84"/>
-      <c r="E39" s="84"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="84"/>
-      <c r="H39" s="84"/>
-      <c r="I39" s="84"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="86"/>
-      <c r="M39" s="90"/>
-    </row>
-    <row r="40" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="83">
+    <row r="39" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="56"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="54"/>
+      <c r="M39" s="58"/>
+    </row>
+    <row r="40" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="51">
         <f>estimate!A61</f>
         <v>7</v>
       </c>
-      <c r="B40" s="91" t="str">
+      <c r="B40" s="59" t="str">
         <f>estimate!B61</f>
         <v>Information board (सुचना पाटि)</v>
       </c>
-      <c r="C40" s="84" t="str">
+      <c r="C40" s="52" t="str">
         <f>estimate!H61</f>
         <v>no.</v>
       </c>
-      <c r="D40" s="84">
+      <c r="D40" s="52">
         <f>estimate!G61</f>
         <v>1</v>
       </c>
-      <c r="E40" s="84">
+      <c r="E40" s="52">
         <f>estimate!I61</f>
         <v>1000</v>
       </c>
-      <c r="F40" s="84">
+      <c r="F40" s="52">
         <f>D40*E40</f>
         <v>1000</v>
       </c>
-      <c r="G40" s="84">
-        <f>V!G85</f>
+      <c r="G40" s="52">
+        <f>V!G80</f>
         <v>1</v>
       </c>
-      <c r="H40" s="84">
-        <f>V!I85</f>
+      <c r="H40" s="52">
+        <f>V!I80</f>
         <v>1000</v>
       </c>
-      <c r="I40" s="84">
+      <c r="I40" s="52">
         <f>G40*H40</f>
         <v>1000</v>
       </c>
-      <c r="J40" s="85">
+      <c r="J40" s="53">
         <f>I40-F40</f>
         <v>0</v>
       </c>
-      <c r="K40" s="86"/>
-    </row>
-    <row r="41" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="89"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="84"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="85"/>
-      <c r="K41" s="86"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="92"/>
-      <c r="B42" s="93" t="s">
+      <c r="K40" s="54"/>
+    </row>
+    <row r="41" spans="1:13" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="54"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="60"/>
+      <c r="B42" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="C42" s="93"/>
-      <c r="D42" s="94"/>
-      <c r="E42" s="94"/>
-      <c r="F42" s="94">
+      <c r="C42" s="61"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62">
         <f>SUM(F13:F40)</f>
         <v>234835.07491669987</v>
       </c>
-      <c r="G42" s="94"/>
-      <c r="H42" s="94"/>
-      <c r="I42" s="94">
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62">
         <f>SUM(I13:I40)</f>
         <v>240974.86130219698</v>
       </c>
-      <c r="J42" s="95">
+      <c r="J42" s="63">
         <f>I42-F42</f>
         <v>6139.7863854971074</v>
       </c>
-      <c r="K42" s="92"/>
+      <c r="K42" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -6323,22 +6202,2016 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="I9:K9"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J6:K6"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="80" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup scale="85" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;LPrepared By:
 &amp;CChecked By:
 &amp;RApproved By:
 </oddFooter>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="33" max="10" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE1607E-06B8-49E3-AB39-BC5343C62098}">
+  <dimension ref="A1:S89"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
+    <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="19" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
+    <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="73" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="73" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="75" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="67" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="11"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="46" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="38"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="16"/>
+      <c r="B10" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="41">
+        <v>2</v>
+      </c>
+      <c r="D10" s="9">
+        <f>(15.5+1)/3.281</f>
+        <v>5.0289545870161536</v>
+      </c>
+      <c r="E10" s="9">
+        <v>3.54</v>
+      </c>
+      <c r="F10" s="9">
+        <f t="shared" ref="F10:F11" si="0">PRODUCT(C10:E10)</f>
+        <v>35.604998476074371</v>
+      </c>
+      <c r="G10" s="9">
+        <f t="shared" ref="G10:G11" si="1">F10</f>
+        <v>35.604998476074371</v>
+      </c>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="27"/>
+    </row>
+    <row r="11" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="41">
+        <v>2</v>
+      </c>
+      <c r="D11" s="9">
+        <f>(15.5-1.5+2)/3.281</f>
+        <v>4.8765620237732392</v>
+      </c>
+      <c r="E11" s="9">
+        <v>3.54</v>
+      </c>
+      <c r="F11" s="9">
+        <f t="shared" si="0"/>
+        <v>34.526059128314536</v>
+      </c>
+      <c r="G11" s="9">
+        <f t="shared" si="1"/>
+        <v>34.526059128314536</v>
+      </c>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="27"/>
+    </row>
+    <row r="12" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="41">
+        <v>2</v>
+      </c>
+      <c r="D12" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="E12" s="9">
+        <v>2.14</v>
+      </c>
+      <c r="F12" s="9">
+        <f>PRODUCT(C12:E12)</f>
+        <v>16.692</v>
+      </c>
+      <c r="G12" s="9">
+        <f>F12</f>
+        <v>16.692</v>
+      </c>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="27"/>
+    </row>
+    <row r="13" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="16"/>
+      <c r="B13" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="41">
+        <v>9</v>
+      </c>
+      <c r="D13" s="9">
+        <v>3.09</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2.14</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" ref="F13:F26" si="2">PRODUCT(C13:E13)</f>
+        <v>59.513399999999997</v>
+      </c>
+      <c r="G13" s="9">
+        <f t="shared" ref="G13:G26" si="3">F13</f>
+        <v>59.513399999999997</v>
+      </c>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="27"/>
+    </row>
+    <row r="14" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="41">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9">
+        <v>3.9</v>
+      </c>
+      <c r="E14" s="9">
+        <v>2.35</v>
+      </c>
+      <c r="F14" s="9">
+        <f t="shared" si="2"/>
+        <v>9.1650000000000009</v>
+      </c>
+      <c r="G14" s="9">
+        <f t="shared" si="3"/>
+        <v>9.1650000000000009</v>
+      </c>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="27"/>
+    </row>
+    <row r="15" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="41">
+        <v>3</v>
+      </c>
+      <c r="D15" s="9">
+        <f>(7+1)/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E15" s="9">
+        <v>3.54</v>
+      </c>
+      <c r="F15" s="9">
+        <f t="shared" si="2"/>
+        <v>25.8945443462359</v>
+      </c>
+      <c r="G15" s="9">
+        <f t="shared" si="3"/>
+        <v>25.8945443462359</v>
+      </c>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="27"/>
+    </row>
+    <row r="16" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41">
+        <v>3</v>
+      </c>
+      <c r="D16" s="9">
+        <v>2.6</v>
+      </c>
+      <c r="E16" s="9">
+        <v>3.54</v>
+      </c>
+      <c r="F16" s="9">
+        <f t="shared" si="2"/>
+        <v>27.612000000000002</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" si="3"/>
+        <v>27.612000000000002</v>
+      </c>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="27"/>
+    </row>
+    <row r="17" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="41">
+        <v>5</v>
+      </c>
+      <c r="D17" s="9">
+        <v>3.09</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1.39</v>
+      </c>
+      <c r="F17" s="9">
+        <f t="shared" si="2"/>
+        <v>21.475499999999997</v>
+      </c>
+      <c r="G17" s="9">
+        <f t="shared" si="3"/>
+        <v>21.475499999999997</v>
+      </c>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="27"/>
+    </row>
+    <row r="18" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="41">
+        <v>5</v>
+      </c>
+      <c r="D18" s="9">
+        <f>1.8+1.9</f>
+        <v>3.7</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1.39</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" si="2"/>
+        <v>25.715</v>
+      </c>
+      <c r="G18" s="9">
+        <f t="shared" si="3"/>
+        <v>25.715</v>
+      </c>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="27"/>
+    </row>
+    <row r="19" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="41">
+        <v>3</v>
+      </c>
+      <c r="D19" s="9">
+        <f>13/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.39</v>
+      </c>
+      <c r="F19" s="9">
+        <f t="shared" si="2"/>
+        <v>16.522401706796707</v>
+      </c>
+      <c r="G19" s="9">
+        <f t="shared" si="3"/>
+        <v>16.522401706796707</v>
+      </c>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="27"/>
+    </row>
+    <row r="20" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="41">
+        <v>3</v>
+      </c>
+      <c r="D20" s="9">
+        <f>(13)/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E20" s="9">
+        <v>3.54</v>
+      </c>
+      <c r="F20" s="9">
+        <f t="shared" si="2"/>
+        <v>42.078634562633347</v>
+      </c>
+      <c r="G20" s="9">
+        <f t="shared" si="3"/>
+        <v>42.078634562633347</v>
+      </c>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="27"/>
+    </row>
+    <row r="21" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41">
+        <v>3</v>
+      </c>
+      <c r="D21" s="9">
+        <f>(9)/3.281</f>
+        <v>2.7430661383724475</v>
+      </c>
+      <c r="E21" s="9">
+        <v>3.54</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="2"/>
+        <v>29.131362389515388</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="3"/>
+        <v>29.131362389515388</v>
+      </c>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="27"/>
+    </row>
+    <row r="22" spans="1:11" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+      <c r="B22" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="41">
+        <v>5</v>
+      </c>
+      <c r="D22" s="9">
+        <f>3.8+7-11.33/3.281+0.6</f>
+        <v>7.9467845169155744</v>
+      </c>
+      <c r="E22" s="9">
+        <v>1.39</v>
+      </c>
+      <c r="F22" s="9">
+        <f t="shared" si="2"/>
+        <v>55.230152392563234</v>
+      </c>
+      <c r="G22" s="9">
+        <f t="shared" si="3"/>
+        <v>55.230152392563234</v>
+      </c>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="27"/>
+    </row>
+    <row r="23" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="16"/>
+      <c r="B23" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="41">
+        <v>3</v>
+      </c>
+      <c r="D23" s="9">
+        <f>11.25/3.281</f>
+        <v>3.4288326729655592</v>
+      </c>
+      <c r="E23" s="9">
+        <v>2.35</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="2"/>
+        <v>24.173270344407193</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="3"/>
+        <v>24.173270344407193</v>
+      </c>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="27"/>
+    </row>
+    <row r="24" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
+      <c r="B24" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="41">
+        <v>3</v>
+      </c>
+      <c r="D24" s="9">
+        <f>(11.667*2)/3.281</f>
+        <v>7.1118561414202981</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.39</v>
+      </c>
+      <c r="F24" s="9">
+        <f t="shared" si="2"/>
+        <v>29.656440109722642</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="3"/>
+        <v>29.656440109722642</v>
+      </c>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="27"/>
+    </row>
+    <row r="25" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="41">
+        <v>3</v>
+      </c>
+      <c r="D25" s="9">
+        <f>11.25/3.281</f>
+        <v>3.4288326729655592</v>
+      </c>
+      <c r="E25" s="9">
+        <v>1.39</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="2"/>
+        <v>14.298232246266382</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="3"/>
+        <v>14.298232246266382</v>
+      </c>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="27"/>
+    </row>
+    <row r="26" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41">
+        <v>6</v>
+      </c>
+      <c r="D26" s="9">
+        <f>11.25/3.281</f>
+        <v>3.4288326729655592</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.39</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="2"/>
+        <v>28.596464492532764</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="shared" si="3"/>
+        <v>28.596464492532764</v>
+      </c>
+      <c r="H26" s="39"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="39"/>
+      <c r="K26" s="27"/>
+    </row>
+    <row r="27" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="39">
+        <f>SUM(G10:G26)</f>
+        <v>495.88546019506242</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" s="6">
+        <v>182.51</v>
+      </c>
+      <c r="J27" s="39">
+        <f>G27*I27</f>
+        <v>90504.055340200837</v>
+      </c>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" spans="1:11" s="35" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="39">
+        <f>0.13*G27*(1871.42/18.94)</f>
+        <v>6369.6565907799195</v>
+      </c>
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="5"/>
+    </row>
+    <row r="30" spans="1:11" s="35" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>2</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="5"/>
+    </row>
+    <row r="31" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4">
+        <f>(10+3)/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E31" s="5">
+        <f>(7)/3.281</f>
+        <v>2.1334958854007922</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="33">
+        <f t="shared" ref="G31:G33" si="4">PRODUCT(C31:F31)</f>
+        <v>8.4533515727553485</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="5"/>
+    </row>
+    <row r="32" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="4">
+        <f>(13)/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E32" s="5">
+        <f>1.75+1.75</f>
+        <v>3.5</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="33">
+        <f t="shared" si="4"/>
+        <v>13.867723255105151</v>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="3">
+        <v>1</v>
+      </c>
+      <c r="D33" s="4">
+        <f>3.75+7-11.33/3.281</f>
+        <v>7.2967845169155741</v>
+      </c>
+      <c r="E33" s="5">
+        <f>14/3.281</f>
+        <v>4.2669917708015843</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="33">
+        <f t="shared" si="4"/>
+        <v>31.135319486991168</v>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="5"/>
+    </row>
+    <row r="34" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="39">
+        <f>SUM(G31:G33)</f>
+        <v>53.456394314851664</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I34" s="6">
+        <v>1074.98</v>
+      </c>
+      <c r="J34" s="39">
+        <f>G34*I34</f>
+        <v>57464.554760579245</v>
+      </c>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16"/>
+      <c r="B35" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="18">
+        <f>0.13*G34*6674.66/10</f>
+        <v>4638.4423394083815</v>
+      </c>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16"/>
+      <c r="B36" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="18">
+        <f>0.13*G34*1023.75/10</f>
+        <v>711.43778783778214</v>
+      </c>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="16"/>
+      <c r="B37" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="18">
+        <f>0.13*G34*348.21/10</f>
+        <v>241.98266383686845</v>
+      </c>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16"/>
+      <c r="B38" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="18">
+        <f>0.13*G34*165/10</f>
+        <v>114.66396580535684</v>
+      </c>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="16"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>3</v>
+      </c>
+      <c r="B40" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="16"/>
+      <c r="B41" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="17">
+        <v>2</v>
+      </c>
+      <c r="D41" s="33">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E41" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F41" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="G41" s="33">
+        <f t="shared" ref="G41:G45" si="5">PRODUCT(C41:F41)</f>
+        <v>1.9750076196281618</v>
+      </c>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="16"/>
+      <c r="B42" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="17">
+        <f>2*6</f>
+        <v>12</v>
+      </c>
+      <c r="D42" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E42" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F42" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="G42" s="33">
+        <f t="shared" si="5"/>
+        <v>1.0935000000000001</v>
+      </c>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="16"/>
+      <c r="B43" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="17">
+        <v>1</v>
+      </c>
+      <c r="D43" s="33">
+        <f>13/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E43" s="33">
+        <f>10/3.281</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="F43" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="G43" s="33">
+        <f t="shared" si="5"/>
+        <v>1.2076216532507642</v>
+      </c>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="17"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="16"/>
+      <c r="B44" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" s="17">
+        <v>6</v>
+      </c>
+      <c r="D44" s="33">
+        <f>0.3</f>
+        <v>0.3</v>
+      </c>
+      <c r="E44" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="F44" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G44" s="33">
+        <f t="shared" si="5"/>
+        <v>0.16199999999999998</v>
+      </c>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="17"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="17">
+        <v>1</v>
+      </c>
+      <c r="D45" s="33">
+        <f>9/3.281</f>
+        <v>2.7430661383724475</v>
+      </c>
+      <c r="E45" s="33">
+        <v>0.6</v>
+      </c>
+      <c r="F45" s="17">
+        <v>0.9</v>
+      </c>
+      <c r="G45" s="33">
+        <f t="shared" si="5"/>
+        <v>1.4812557147211216</v>
+      </c>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2"/>
+      <c r="B46" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="39">
+        <f>SUM(G41:G45)</f>
+        <v>5.9193849876000471</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="6">
+        <v>674.12</v>
+      </c>
+      <c r="J46" s="39">
+        <f>G46*I46</f>
+        <v>3990.3758078409437</v>
+      </c>
+      <c r="K46" s="5"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="16">
+        <v>4</v>
+      </c>
+      <c r="B48" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="16"/>
+      <c r="B49" s="32" t="str">
+        <f>B42</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C49" s="17">
+        <f>C42</f>
+        <v>12</v>
+      </c>
+      <c r="D49" s="33">
+        <f>D42</f>
+        <v>0.45</v>
+      </c>
+      <c r="E49" s="33">
+        <f>E42</f>
+        <v>0.45</v>
+      </c>
+      <c r="F49" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G49" s="33">
+        <f t="shared" ref="G49:G54" si="6">PRODUCT(C49:F49)</f>
+        <v>0.18225</v>
+      </c>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="16"/>
+      <c r="B50" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="17">
+        <f t="shared" ref="C50:E52" si="7">C61</f>
+        <v>1</v>
+      </c>
+      <c r="D50" s="33">
+        <f t="shared" si="7"/>
+        <v>3.5</v>
+      </c>
+      <c r="E50" s="33">
+        <f t="shared" si="7"/>
+        <v>3.5</v>
+      </c>
+      <c r="F50" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G50" s="33">
+        <f t="shared" si="6"/>
+        <v>0.91874999999999996</v>
+      </c>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="16"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="17">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="D51" s="33">
+        <f t="shared" si="7"/>
+        <v>4.2</v>
+      </c>
+      <c r="E51" s="33">
+        <f t="shared" si="7"/>
+        <v>3.2</v>
+      </c>
+      <c r="F51" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G51" s="33">
+        <f t="shared" si="6"/>
+        <v>1.008</v>
+      </c>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="16"/>
+      <c r="B52" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="17">
+        <f t="shared" si="7"/>
+        <v>-1</v>
+      </c>
+      <c r="D52" s="33">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="E52" s="33">
+        <f t="shared" si="7"/>
+        <v>1.5</v>
+      </c>
+      <c r="F52" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G52" s="33">
+        <f t="shared" si="6"/>
+        <v>-0.33749999999999997</v>
+      </c>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="16"/>
+      <c r="B53" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="17">
+        <v>1</v>
+      </c>
+      <c r="D53" s="33">
+        <v>3.5</v>
+      </c>
+      <c r="E53" s="33">
+        <v>3.65</v>
+      </c>
+      <c r="F53" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G53" s="33">
+        <f t="shared" si="6"/>
+        <v>0.958125</v>
+      </c>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="16"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="17">
+        <v>1</v>
+      </c>
+      <c r="D54" s="33">
+        <v>3.5</v>
+      </c>
+      <c r="E54" s="33">
+        <v>0.65</v>
+      </c>
+      <c r="F54" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G54" s="33">
+        <f t="shared" si="6"/>
+        <v>0.170625</v>
+      </c>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="17"/>
+    </row>
+    <row r="55" spans="1:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+      <c r="B55" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="39">
+        <f>SUM(G49:G54)</f>
+        <v>2.9002499999999998</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I55" s="6">
+        <v>4495.6400000000003</v>
+      </c>
+      <c r="J55" s="39">
+        <f>G55*I55</f>
+        <v>13038.47991</v>
+      </c>
+      <c r="K55" s="5"/>
+    </row>
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="16"/>
+      <c r="B56" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="18">
+        <f>0.13*G55*2577.63</f>
+        <v>971.85028297500003</v>
+      </c>
+      <c r="K56" s="17"/>
+    </row>
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="16"/>
+      <c r="B57" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C57" s="17"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="18">
+        <f>0.13*G55*515.52</f>
+        <v>194.36779439999998</v>
+      </c>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="16"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="17"/>
+    </row>
+    <row r="59" spans="1:11" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="16">
+        <v>5</v>
+      </c>
+      <c r="B59" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" s="17"/>
+      <c r="D59" s="17"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="16"/>
+      <c r="B60" s="32" t="str">
+        <f>B49</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C60" s="17">
+        <f>C42</f>
+        <v>12</v>
+      </c>
+      <c r="D60" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E60" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F60" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G60" s="33">
+        <f t="shared" ref="G60:G64" si="8">PRODUCT(C60:F60)</f>
+        <v>0.12150000000000001</v>
+      </c>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="17"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="16"/>
+      <c r="B61" s="32" t="str">
+        <f>B50</f>
+        <v>-for flooring</v>
+      </c>
+      <c r="C61" s="17">
+        <v>1</v>
+      </c>
+      <c r="D61" s="33">
+        <v>3.5</v>
+      </c>
+      <c r="E61" s="33">
+        <v>3.5</v>
+      </c>
+      <c r="F61" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G61" s="33">
+        <f t="shared" si="8"/>
+        <v>0.91874999999999996</v>
+      </c>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="17"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="16"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="17">
+        <v>1</v>
+      </c>
+      <c r="D62" s="33">
+        <v>4.2</v>
+      </c>
+      <c r="E62" s="33">
+        <v>3.2</v>
+      </c>
+      <c r="F62" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G62" s="33">
+        <f t="shared" si="8"/>
+        <v>1.008</v>
+      </c>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="17"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="16"/>
+      <c r="B63" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D63" s="33">
+        <v>3</v>
+      </c>
+      <c r="E63" s="33">
+        <f>0.6+0.45+0.45</f>
+        <v>1.5</v>
+      </c>
+      <c r="F63" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G63" s="33">
+        <f t="shared" si="8"/>
+        <v>-0.33749999999999997</v>
+      </c>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="17"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="16"/>
+      <c r="B64" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C64" s="17">
+        <v>1</v>
+      </c>
+      <c r="D64" s="33">
+        <v>3.5</v>
+      </c>
+      <c r="E64" s="33">
+        <v>3.65</v>
+      </c>
+      <c r="F64" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G64" s="33">
+        <f t="shared" si="8"/>
+        <v>0.63875000000000004</v>
+      </c>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="17"/>
+    </row>
+    <row r="65" spans="1:16" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2"/>
+      <c r="B65" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="3"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="39">
+        <f>SUM(G60:G64)</f>
+        <v>2.3494999999999999</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I65" s="6">
+        <v>13351.1</v>
+      </c>
+      <c r="J65" s="39">
+        <f>G65*I65</f>
+        <v>31368.409449999999</v>
+      </c>
+      <c r="K65" s="5"/>
+    </row>
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="16"/>
+      <c r="B66" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="18">
+        <f>0.13*G65*4169.92</f>
+        <v>1273.6395152</v>
+      </c>
+      <c r="K66" s="17"/>
+    </row>
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="16"/>
+      <c r="B67" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="18">
+        <f>0.13*G65*1414.16</f>
+        <v>431.93395960000004</v>
+      </c>
+      <c r="K67" s="17"/>
+    </row>
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="16"/>
+      <c r="B68" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="18">
+        <f>0.13*G65*(1652.5+737.97+349.56)</f>
+        <v>836.90106305000006</v>
+      </c>
+      <c r="K68" s="17"/>
+    </row>
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="16"/>
+      <c r="B69" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="18">
+        <f>0.13*G65*42</f>
+        <v>12.82827</v>
+      </c>
+      <c r="K69" s="17"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="16"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="17"/>
+    </row>
+    <row r="71" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="16">
+        <v>6</v>
+      </c>
+      <c r="B71" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="16"/>
+      <c r="B72" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C72" s="17">
+        <v>2</v>
+      </c>
+      <c r="D72" s="33">
+        <v>3</v>
+      </c>
+      <c r="E72" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F72" s="33">
+        <v>0.8</v>
+      </c>
+      <c r="G72" s="33">
+        <f>PRODUCT(C72:F72)</f>
+        <v>2.16</v>
+      </c>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="17"/>
+      <c r="K72" s="17"/>
+      <c r="M72" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N72" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O72" s="33"/>
+      <c r="P72" s="33">
+        <f>PI()*M72*SQRT(M72^2+N72^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="16"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="17">
+        <v>2</v>
+      </c>
+      <c r="D73" s="33">
+        <f>9/3.281</f>
+        <v>2.7430661383724475</v>
+      </c>
+      <c r="E73" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F73" s="33">
+        <v>0.8</v>
+      </c>
+      <c r="G73" s="33">
+        <f t="shared" ref="G73" si="9">PRODUCT(C73:F73)</f>
+        <v>1.9750076196281623</v>
+      </c>
+      <c r="H73" s="17"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="17"/>
+      <c r="K73" s="17"/>
+      <c r="M73" s="44"/>
+      <c r="N73" s="44"/>
+      <c r="O73" s="44"/>
+      <c r="P73" s="44"/>
+    </row>
+    <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="6">
+        <f>SUM(G72:G73)</f>
+        <v>4.135007619628162</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I74" s="6">
+        <v>6337.3</v>
+      </c>
+      <c r="J74" s="18">
+        <f>G74*I74</f>
+        <v>26204.78378786955</v>
+      </c>
+      <c r="K74" s="5"/>
+    </row>
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="16"/>
+      <c r="B75" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="18">
+        <f>0.13*G74*2577.63</f>
+        <v>1385.6075597756783</v>
+      </c>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="16"/>
+      <c r="B76" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="17"/>
+      <c r="G76" s="17"/>
+      <c r="H76" s="17"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="18">
+        <f>0.13*G74*257.76</f>
+        <v>138.55914332459616</v>
+      </c>
+      <c r="K76" s="17"/>
+    </row>
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="16"/>
+      <c r="B77" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="18">
+        <f>0.13*G74*133.56</f>
+        <v>71.795310298079855</v>
+      </c>
+      <c r="K77" s="17"/>
+    </row>
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="16"/>
+      <c r="B78" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="17"/>
+      <c r="H78" s="17"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="18">
+        <f>0.13*G74*19.6</f>
+        <v>10.535999414812558</v>
+      </c>
+      <c r="K78" s="17"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="16"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="17"/>
+      <c r="H79" s="17"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="18"/>
+      <c r="K79" s="17"/>
+    </row>
+    <row r="80" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>7</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="7">
+        <f t="shared" ref="G80" si="10">PRODUCT(C80:F80)</f>
+        <v>1</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" s="6">
+        <v>1000</v>
+      </c>
+      <c r="J80" s="7">
+        <f>G80*I80</f>
+        <v>1000</v>
+      </c>
+      <c r="K80" s="5"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="5"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A82" s="21"/>
+      <c r="B82" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="23"/>
+      <c r="D82" s="24"/>
+      <c r="E82" s="24"/>
+      <c r="F82" s="24"/>
+      <c r="G82" s="18"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="18"/>
+      <c r="J82" s="18">
+        <f>SUM(J9:J80)</f>
+        <v>240974.86130219698</v>
+      </c>
+      <c r="K82" s="25"/>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M83" s="20"/>
+      <c r="N83" s="20"/>
+      <c r="O83" s="20"/>
+      <c r="P83" s="20"/>
+      <c r="Q83" s="20"/>
+      <c r="R83" s="20"/>
+      <c r="S83" s="20"/>
+    </row>
+    <row r="84" spans="1:19" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="26"/>
+      <c r="B84" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C84" s="65">
+        <f>J82</f>
+        <v>240974.86130219698</v>
+      </c>
+      <c r="D84" s="66"/>
+      <c r="E84" s="9">
+        <v>100</v>
+      </c>
+      <c r="F84" s="26"/>
+      <c r="G84" s="28"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="29"/>
+      <c r="J84" s="30"/>
+      <c r="K84" s="31"/>
+      <c r="M84" s="19"/>
+      <c r="N84" s="19"/>
+      <c r="O84" s="19"/>
+      <c r="P84" s="19"/>
+      <c r="Q84" s="19"/>
+      <c r="R84" s="19"/>
+      <c r="S84" s="19"/>
+    </row>
+    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" s="68">
+        <v>200000</v>
+      </c>
+      <c r="D85" s="69"/>
+      <c r="E85" s="9"/>
+    </row>
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" s="68">
+        <f>C85-C88-C89</f>
+        <v>190000</v>
+      </c>
+      <c r="D86" s="69"/>
+      <c r="E86" s="9">
+        <f>C86/C84*100</f>
+        <v>78.846398737720847</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" s="70">
+        <f>C84-C86</f>
+        <v>50974.86130219698</v>
+      </c>
+      <c r="D87" s="70"/>
+      <c r="E87" s="9">
+        <f>100-E86</f>
+        <v>21.153601262279153</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" s="65">
+        <f>C85*0.03</f>
+        <v>6000</v>
+      </c>
+      <c r="D88" s="66"/>
+      <c r="E88" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C89" s="65">
+        <f>C85*0.02</f>
+        <v>4000</v>
+      </c>
+      <c r="D89" s="66"/>
+      <c r="E89" s="9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>